--- a/.claude/skills/syscohada/liasse/exemples/exemple-etats-smt.xlsx
+++ b/.claude/skills/syscohada/liasse/exemples/exemple-etats-smt.xlsx
@@ -614,8 +614,24 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -623,10 +639,10 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -753,23 +769,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -787,12 +791,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -823,6 +821,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1209,21 +1209,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16.5" customWidth="1" min="3" max="3"/>
+    <col width="16.5" customWidth="1" min="4" max="4"/>
+    <col width="16.5" customWidth="1" min="5" max="5"/>
+    <col width="16.5" customWidth="1" min="6" max="6"/>
+    <col width="16.5" customWidth="1" min="7" max="7"/>
+    <col width="16.5" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Compte</t>
@@ -1236,349 +1235,272 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Préfixe 2</t>
+          <t>Solde d'ouverture débit</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Préfixe 3</t>
+          <t>Solde d'ouverture crédit</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Préfixe 4</t>
+          <t>Mouvement débit</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Solde final débit</t>
+          <t>Mouvement crédit</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Solde final crédit</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Mouvement débit</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Mouvement crédit</t>
+          <t>Solde de clôture débit</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Solde de clôture crédit</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Matériel et mobilier</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
+          <t>Capital personnel</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>162</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Amortissements du matériel et mobilier</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2844</t>
-        </is>
+          <t>Emprunt établissement de crédit</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Stocks d'autres approvisionnements</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+          <t>Matériel et mobilier</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Banque locale</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
+          <t>Amortissements du matériel et mobilier</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2500000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Caisse</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
+          <t>Stocks d'autres approvisionnements</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>401</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Capital personnel</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+          <t>Fournisseurs</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>521</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Emprunt établissement de crédit</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
+          <t>Banque locale</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1500000</v>
+        <v>2500000</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>571</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Fournisseurs</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
+          <t>Caisse</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1593,109 +1515,82 @@
           <t>Achats de marchandises</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
         <v>5200000</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>616</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Locations et charges locatives</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
+          <t>Transports de plis</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>622</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Salaires</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
+          <t>Locations et charges locatives</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1800000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1710,109 +1605,82 @@
           <t>Impôts et taxes directs</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>661</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Charges d'intérêts</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
+          <t>Salaires</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0</v>
+        <v>1800000</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>671</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Transports de plis</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
+          <t>Charges d'intérêts</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1827,31 +1695,22 @@
           <t>Dotations aux amortissements</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
         <v>600000</v>
       </c>
-      <c r="G16" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1866,32 +1725,23 @@
           <t>Ventes de marchandises</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>10200000</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1905,33 +1755,79 @@
           <t>Produits accessoires</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="H18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL GENERAL</t>
+        </is>
+      </c>
+      <c r="C19" s="7">
+        <f>SUM(C2:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="7">
+        <f>SUM(D2:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="7">
+        <f>SUM(E2:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="7">
+        <f>SUM(F2:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="7">
+        <f>SUM(G2:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="7">
+        <f>SUM(H2:H18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Contrôle d'équilibre par solde (débit - crédit, doit être 0)</t>
+        </is>
+      </c>
+      <c r="C20" s="9">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9">
+        <f>E19-F19</f>
+        <v/>
+      </c>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9">
+        <f>G19-H19</f>
+        <v/>
+      </c>
+      <c r="H20" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1955,61 +1851,61 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 6 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>COMPTE DE RESULTAT
 SYSCOHADA - SMT</t>
         </is>
       </c>
-      <c r="E2" s="50" t="n"/>
+      <c r="E2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr"/>
+      <c r="E4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
@@ -2021,10 +1917,10 @@
           <t>COMPTE DE RESULTAT</t>
         </is>
       </c>
-      <c r="B7" s="65" t="n"/>
-      <c r="C7" s="65" t="n"/>
-      <c r="D7" s="65" t="n"/>
-      <c r="E7" s="65" t="n"/>
+      <c r="B7" s="69" t="n"/>
+      <c r="C7" s="69" t="n"/>
+      <c r="D7" s="69" t="n"/>
+      <c r="E7" s="69" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -2054,48 +1950,48 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="B9" s="73" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Recettes sur ventes ou prestations de services</t>
         </is>
       </c>
-      <c r="C9" s="73" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"70*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"70*",'BALANCE N'!$F$2:$F$50)</f>
-        <v/>
-      </c>
-      <c r="E9" s="75" t="n"/>
+      <c r="D9" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"70*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"70*",'BALANCE N'!$G$2:$G$50)</f>
+        <v/>
+      </c>
+      <c r="E9" s="77" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="72" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
       </c>
-      <c r="B10" s="73" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Autres recettes sur activités</t>
         </is>
       </c>
-      <c r="C10" s="73" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$F$2:$F$50)</f>
-        <v/>
-      </c>
-      <c r="E10" s="75" t="n"/>
+      <c r="D10" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$G$2:$G$50)</f>
+        <v/>
+      </c>
+      <c r="E10" s="77" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="81" t="inlineStr">
@@ -2116,132 +2012,132 @@
       <c r="E11" s="84" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="72" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>JA</t>
         </is>
       </c>
-      <c r="B12" s="73" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Dépenses sur achats</t>
         </is>
       </c>
-      <c r="C12" s="73" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D12" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"60*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"60*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"603*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"603*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="E12" s="75" t="n"/>
+      <c r="D12" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"60*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"60*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"603*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"603*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="E12" s="77" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="72" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr">
         <is>
           <t>JB</t>
         </is>
       </c>
-      <c r="B13" s="73" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Dépenses sur loyers</t>
         </is>
       </c>
-      <c r="C13" s="73" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="E13" s="75" t="n"/>
+      <c r="D13" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="E13" s="77" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="72" t="inlineStr">
+      <c r="A14" s="76" t="inlineStr">
         <is>
           <t>JC</t>
         </is>
       </c>
-      <c r="B14" s="73" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Dépenses sur salaires</t>
         </is>
       </c>
-      <c r="C14" s="73" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"66*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"66*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="E14" s="75" t="n"/>
+      <c r="D14" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"66*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"66*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="E14" s="77" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>JD</t>
         </is>
       </c>
-      <c r="B15" s="73" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Dépenses sur impôts et taxes</t>
         </is>
       </c>
-      <c r="C15" s="73" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D15" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="E15" s="75" t="n"/>
+      <c r="D15" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="E15" s="77" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="72" t="inlineStr">
+      <c r="A16" s="76" t="inlineStr">
         <is>
           <t>JE</t>
         </is>
       </c>
-      <c r="B16" s="73" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Charges d'intérêts</t>
         </is>
       </c>
-      <c r="C16" s="73" t="inlineStr"/>
-      <c r="D16" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"67*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"67*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="E16" s="75" t="n"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"67*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"67*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="E16" s="77" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="72" t="inlineStr">
+      <c r="A17" s="76" t="inlineStr">
         <is>
           <t>JF</t>
         </is>
       </c>
-      <c r="B17" s="73" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Autres dépenses sur activités</t>
         </is>
       </c>
-      <c r="C17" s="73" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D17" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="E17" s="75" t="n"/>
+      <c r="D17" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="E17" s="77" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="81" t="inlineStr">
@@ -2267,121 +2163,121 @@
           <t>KZ</t>
         </is>
       </c>
-      <c r="B19" s="85" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>SOLDE : Excédent (+) ou insuffisance (-) de recettes (C = A - B)</t>
         </is>
       </c>
-      <c r="C19" s="85" t="inlineStr"/>
-      <c r="D19" s="86">
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="9">
         <f>D11-D18</f>
         <v/>
       </c>
-      <c r="E19" s="87" t="n"/>
+      <c r="E19" s="85" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="72" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="B20" s="73" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Variation des stocks [N - (N-1)] (D)</t>
         </is>
       </c>
-      <c r="C20" s="73" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="74">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$50,"603*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"603*",'BALANCE N'!$F$2:$F$50))+(SUMIF('BALANCE N'!$A$2:$A$50,"73*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"73*",'BALANCE N'!$F$2:$F$50))</f>
-        <v/>
-      </c>
-      <c r="E20" s="75" t="n"/>
+      <c r="D20" s="5">
+        <f>(SUMIF('BALANCE N'!$A$2:$A$50,"603*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"603*",'BALANCE N'!$G$2:$G$50))+(SUMIF('BALANCE N'!$A$2:$A$50,"73*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"73*",'BALANCE N'!$G$2:$G$50))</f>
+        <v/>
+      </c>
+      <c r="E20" s="77" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="72" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>VB</t>
         </is>
       </c>
-      <c r="B21" s="73" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Variation des créances [N - (N-1)] (D) - à saisir depuis la NOTE 3</t>
         </is>
       </c>
-      <c r="C21" s="73" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D21" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="75" t="n"/>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="77" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="72" t="inlineStr">
+      <c r="A22" s="76" t="inlineStr">
         <is>
           <t>VC</t>
         </is>
       </c>
-      <c r="B22" s="73" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Variation des dettes d'exploitation [N - (N-1)] (E) - à saisir depuis la NOTE 3</t>
         </is>
       </c>
-      <c r="C22" s="73" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="75" t="n"/>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="77" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="72" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="B23" s="73" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>DOTATIONS AUX AMORTISSEMENTS (F)</t>
         </is>
       </c>
-      <c r="C23" s="73" t="inlineStr"/>
-      <c r="D23" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="E23" s="75" t="n"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="E23" s="77" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="76" t="inlineStr">
+      <c r="A24" s="78" t="inlineStr">
         <is>
           <t>KZC</t>
         </is>
       </c>
-      <c r="B24" s="88" t="inlineStr">
+      <c r="B24" s="86" t="inlineStr">
         <is>
           <t>RÉSULTAT DE L'EXERCICE (G = C + D stocks + D créances - E dettes - F)</t>
         </is>
       </c>
-      <c r="C24" s="88" t="inlineStr"/>
-      <c r="D24" s="89">
+      <c r="C24" s="86" t="inlineStr"/>
+      <c r="D24" s="87">
         <f>D19+D20+D21-D22-D23</f>
         <v/>
       </c>
-      <c r="E24" s="90" t="n"/>
+      <c r="E24" s="88" t="n"/>
     </row>
     <row r="25"/>
     <row r="26">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t>Lecture (AUDCIF Titre X) : G = C - D + E - F. Les variations sont ici affichées en N - (N-1) : une hausse des stocks ou des créances augmente le résultat, une hausse des dettes le diminue. VB et VC se saisissent depuis la NOTE 3 (inventaire extra-comptable).</t>
         </is>
@@ -2418,72 +2314,72 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 7 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="I2" s="49" t="inlineStr">
+      <c r="I2" s="53" t="inlineStr">
         <is>
           <t>NOTES ANNEXES</t>
         </is>
       </c>
-      <c r="J2" s="50" t="n"/>
+      <c r="J2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="C4" s="39" t="n"/>
-      <c r="D4" s="39" t="n"/>
-      <c r="E4" s="39" t="n"/>
-      <c r="F4" s="39" t="n"/>
-      <c r="G4" s="39" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="43" t="n"/>
+      <c r="I4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr"/>
+      <c r="J4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="G5" s="37" t="inlineStr">
+      <c r="G5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="I5" s="37" t="inlineStr">
+      <c r="I5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="89" t="inlineStr">
         <is>
           <t>FICHE RECAPITULATIVE NOTES ANNEXES PRESENTEES (1)</t>
         </is>
@@ -2518,159 +2414,159 @@
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="92" t="inlineStr">
+      <c r="A9" s="90" t="inlineStr">
         <is>
           <t>Partie 1 : Notes sur le bilan</t>
         </is>
       </c>
-      <c r="B9" s="93" t="n"/>
-      <c r="C9" s="93" t="n"/>
-      <c r="D9" s="93" t="n"/>
-      <c r="E9" s="93" t="n"/>
-      <c r="F9" s="93" t="n"/>
-      <c r="G9" s="93" t="n"/>
-      <c r="H9" s="93" t="n"/>
-      <c r="I9" s="93" t="n"/>
-      <c r="J9" s="93" t="n"/>
+      <c r="B9" s="91" t="n"/>
+      <c r="C9" s="91" t="n"/>
+      <c r="D9" s="91" t="n"/>
+      <c r="E9" s="91" t="n"/>
+      <c r="F9" s="91" t="n"/>
+      <c r="G9" s="91" t="n"/>
+      <c r="H9" s="91" t="n"/>
+      <c r="I9" s="91" t="n"/>
+      <c r="J9" s="91" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="94" t="inlineStr">
+      <c r="A10" s="92" t="inlineStr">
         <is>
           <t>NOTE 1</t>
         </is>
       </c>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="B10" s="93" t="inlineStr">
         <is>
           <t>Tableau SMT de suivi du matériel, du mobilier et des cautions</t>
         </is>
       </c>
-      <c r="C10" s="45" t="n"/>
-      <c r="D10" s="45" t="n"/>
-      <c r="E10" s="45" t="n"/>
-      <c r="F10" s="45" t="n"/>
-      <c r="G10" s="45" t="n"/>
-      <c r="H10" s="45" t="n"/>
-      <c r="I10" s="45" t="n"/>
-      <c r="J10" s="45" t="n"/>
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="49" t="n"/>
+      <c r="I10" s="49" t="n"/>
+      <c r="J10" s="49" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="94" t="inlineStr">
+      <c r="A11" s="92" t="inlineStr">
         <is>
           <t>NOTE 2</t>
         </is>
       </c>
-      <c r="B11" s="95" t="inlineStr">
+      <c r="B11" s="93" t="inlineStr">
         <is>
           <t>État des stocks</t>
         </is>
       </c>
-      <c r="C11" s="45" t="n"/>
-      <c r="D11" s="45" t="n"/>
-      <c r="E11" s="45" t="n"/>
-      <c r="F11" s="45" t="n"/>
-      <c r="G11" s="45" t="n"/>
-      <c r="H11" s="45" t="n"/>
-      <c r="I11" s="45" t="n"/>
-      <c r="J11" s="45" t="n"/>
+      <c r="C11" s="49" t="n"/>
+      <c r="D11" s="49" t="n"/>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="49" t="n"/>
+      <c r="I11" s="49" t="n"/>
+      <c r="J11" s="49" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="94" t="inlineStr">
+      <c r="A12" s="92" t="inlineStr">
         <is>
           <t>NOTE 3</t>
         </is>
       </c>
-      <c r="B12" s="95" t="inlineStr">
+      <c r="B12" s="93" t="inlineStr">
         <is>
           <t>État des créances et des dettes non échues</t>
         </is>
       </c>
-      <c r="C12" s="45" t="n"/>
-      <c r="D12" s="45" t="n"/>
-      <c r="E12" s="45" t="n"/>
-      <c r="F12" s="45" t="n"/>
-      <c r="G12" s="45" t="n"/>
-      <c r="H12" s="45" t="n"/>
-      <c r="I12" s="45" t="n"/>
-      <c r="J12" s="45" t="n"/>
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="49" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="92" t="inlineStr">
+      <c r="A13" s="90" t="inlineStr">
         <is>
           <t>Partie 2 : Notes sur le compte de résultat et pièces de tenue</t>
         </is>
       </c>
-      <c r="B13" s="93" t="n"/>
-      <c r="C13" s="93" t="n"/>
-      <c r="D13" s="93" t="n"/>
-      <c r="E13" s="93" t="n"/>
-      <c r="F13" s="93" t="n"/>
-      <c r="G13" s="93" t="n"/>
-      <c r="H13" s="93" t="n"/>
-      <c r="I13" s="93" t="n"/>
-      <c r="J13" s="93" t="n"/>
+      <c r="B13" s="91" t="n"/>
+      <c r="C13" s="91" t="n"/>
+      <c r="D13" s="91" t="n"/>
+      <c r="E13" s="91" t="n"/>
+      <c r="F13" s="91" t="n"/>
+      <c r="G13" s="91" t="n"/>
+      <c r="H13" s="91" t="n"/>
+      <c r="I13" s="91" t="n"/>
+      <c r="J13" s="91" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="94" t="inlineStr">
+      <c r="A14" s="92" t="inlineStr">
         <is>
           <t>NOTE 4</t>
         </is>
       </c>
-      <c r="B14" s="95" t="inlineStr">
+      <c r="B14" s="93" t="inlineStr">
         <is>
           <t>Journal de trésorerie SMT</t>
         </is>
       </c>
-      <c r="C14" s="45" t="n"/>
-      <c r="D14" s="45" t="n"/>
-      <c r="E14" s="45" t="n"/>
-      <c r="F14" s="45" t="n"/>
-      <c r="G14" s="45" t="n"/>
-      <c r="H14" s="45" t="n"/>
-      <c r="I14" s="45" t="n"/>
-      <c r="J14" s="45" t="n"/>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="49" t="n"/>
+      <c r="F14" s="49" t="n"/>
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="49" t="n"/>
+      <c r="I14" s="49" t="n"/>
+      <c r="J14" s="49" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="94" t="inlineStr"/>
-      <c r="B15" s="95" t="inlineStr">
+      <c r="A15" s="92" t="inlineStr"/>
+      <c r="B15" s="93" t="inlineStr">
         <is>
           <t>Journal de suivi des créances impayées</t>
         </is>
       </c>
-      <c r="C15" s="45" t="n"/>
-      <c r="D15" s="45" t="n"/>
-      <c r="E15" s="45" t="n"/>
-      <c r="F15" s="45" t="n"/>
-      <c r="G15" s="45" t="n"/>
-      <c r="H15" s="45" t="n"/>
-      <c r="I15" s="45" t="n"/>
-      <c r="J15" s="45" t="n"/>
+      <c r="C15" s="49" t="n"/>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="49" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="49" t="n"/>
+      <c r="I15" s="49" t="n"/>
+      <c r="J15" s="49" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="94" t="inlineStr"/>
-      <c r="B16" s="95" t="inlineStr">
+      <c r="A16" s="92" t="inlineStr"/>
+      <c r="B16" s="93" t="inlineStr">
         <is>
           <t>Journal de suivi des dettes à payer</t>
         </is>
       </c>
-      <c r="C16" s="45" t="n"/>
-      <c r="D16" s="45" t="n"/>
-      <c r="E16" s="45" t="n"/>
-      <c r="F16" s="45" t="n"/>
-      <c r="G16" s="45" t="n"/>
-      <c r="H16" s="45" t="n"/>
-      <c r="I16" s="45" t="n"/>
-      <c r="J16" s="45" t="n"/>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="49" t="n"/>
+      <c r="I16" s="49" t="n"/>
+      <c r="J16" s="49" t="n"/>
     </row>
     <row r="17"/>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="96" t="inlineStr">
+      <c r="A18" s="94" t="inlineStr">
         <is>
           <t>(1) A : applicable ; N/A : non applicable. Ne pas joindre les notes non documentées ; supprimer les lignes non chiffrées avant remise.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="96" t="inlineStr">
+      <c r="A19" s="94" t="inlineStr">
         <is>
           <t>(2) A : applicable ; N/A : non applicable. Cocher la colonne correspondante pour chaque note.</t>
         </is>
@@ -2716,70 +2612,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 8 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="F2" s="49" t="inlineStr">
+      <c r="F2" s="53" t="inlineStr">
         <is>
           <t>NOTE 1
 SYSCOHADA - SMT</t>
         </is>
       </c>
-      <c r="G2" s="50" t="n"/>
+      <c r="G2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="C4" s="39" t="n"/>
-      <c r="D4" s="39" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="F4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="G4" s="51" t="inlineStr"/>
+      <c r="G4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="F5" s="37" t="inlineStr">
+      <c r="F5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="89" t="inlineStr">
         <is>
           <t>NOTE 1 : TABLEAU SMT DE SUIVI DU MATERIEL, DU MOBILIER ET DES CAUTIONS</t>
         </is>
@@ -2823,71 +2719,71 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="95" t="inlineStr">
         <is>
           <t>2441</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="95" t="inlineStr">
         <is>
           <t>Matériel et mobilier</t>
         </is>
       </c>
-      <c r="C9" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"2441*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"2441*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="5" t="n"/>
+      <c r="C9" s="96">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"2441*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"2441*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="D9" s="95" t="n"/>
+      <c r="E9" s="95" t="n"/>
+      <c r="F9" s="95" t="n"/>
+      <c r="G9" s="96" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="95" t="n"/>
+      <c r="B10" s="95" t="inlineStr">
         <is>
           <t>TOTAL IMMOBILISATIONS BRUTES</t>
         </is>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="96">
         <f>SUM(C9:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="D10" s="95" t="n"/>
+      <c r="E10" s="95" t="n"/>
+      <c r="F10" s="95" t="n"/>
+      <c r="G10" s="96" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="95" t="n"/>
+      <c r="B11" s="95" t="inlineStr">
         <is>
           <t>Amortissements et dépréciations cumulés (28/29)</t>
         </is>
       </c>
-      <c r="C11" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$F$2:$F$50)</f>
-        <v/>
-      </c>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="5" t="n"/>
+      <c r="C11" s="96">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$G$2:$G$50)</f>
+        <v/>
+      </c>
+      <c r="D11" s="95" t="n"/>
+      <c r="E11" s="95" t="n"/>
+      <c r="F11" s="95" t="n"/>
+      <c r="G11" s="96" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="85" t="n"/>
-      <c r="B12" s="85" t="inlineStr">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>VALEUR NETTE (= poste Immobilisations du bilan)</t>
         </is>
       </c>
-      <c r="C12" s="86">
+      <c r="C12" s="9">
         <f>C10-C11</f>
         <v/>
       </c>
-      <c r="D12" s="85" t="n"/>
-      <c r="E12" s="85" t="n"/>
-      <c r="F12" s="85" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
       <c r="G12" s="97" t="n"/>
     </row>
     <row r="13"/>
@@ -2925,68 +2821,68 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 9 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>NOTE 2
 SYSCOHADA - SMT</t>
         </is>
       </c>
-      <c r="E2" s="50" t="n"/>
+      <c r="E2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr"/>
+      <c r="E4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="89" t="inlineStr">
         <is>
           <t>NOTE 2 : ETAT DES STOCKS</t>
         </is>
@@ -3020,81 +2916,81 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="95" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="95" t="inlineStr">
         <is>
           <t>Stocks d'autres approvisionnements</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"33*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"33*",'BALANCE N'!$G$2:$G$50)</f>
+      <c r="C9" s="95" t="n"/>
+      <c r="D9" s="95" t="n"/>
+      <c r="E9" s="96">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"33*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"33*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="5" t="n"/>
+      <c r="A10" s="95" t="n"/>
+      <c r="B10" s="95" t="n"/>
+      <c r="C10" s="95" t="n"/>
+      <c r="D10" s="95" t="n"/>
+      <c r="E10" s="96" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="A11" s="95" t="n"/>
+      <c r="B11" s="95" t="n"/>
+      <c r="C11" s="95" t="n"/>
+      <c r="D11" s="95" t="n"/>
+      <c r="E11" s="96" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="A12" s="95" t="n"/>
+      <c r="B12" s="95" t="n"/>
+      <c r="C12" s="95" t="n"/>
+      <c r="D12" s="95" t="n"/>
+      <c r="E12" s="96" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="85" t="n"/>
-      <c r="B13" s="85" t="inlineStr">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>VALEUR DU STOCK FINAL</t>
         </is>
       </c>
-      <c r="C13" s="85" t="n"/>
-      <c r="D13" s="85" t="n"/>
-      <c r="E13" s="86">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"3*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"3*",'BALANCE N'!$G$2:$G$50)</f>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"3*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"3*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="85" t="n"/>
-      <c r="B14" s="85" t="inlineStr">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>VALEUR DU STOCK INITIAL</t>
         </is>
       </c>
-      <c r="C14" s="85" t="n"/>
-      <c r="D14" s="85" t="n"/>
-      <c r="E14" s="86" t="n">
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="85" t="n"/>
-      <c r="B15" s="85" t="inlineStr">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>VARIATION DES STOCKS [final - initial]</t>
         </is>
       </c>
-      <c r="C15" s="85" t="n"/>
-      <c r="D15" s="85" t="n"/>
-      <c r="E15" s="86">
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="9">
         <f>E13-E14</f>
         <v/>
       </c>
@@ -3126,76 +3022,76 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 10 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="E2" s="49" t="inlineStr">
+      <c r="E2" s="53" t="inlineStr">
         <is>
           <t>NOTE 3
 SYSCOHADA - SMT</t>
         </is>
       </c>
-      <c r="F2" s="50" t="n"/>
+      <c r="F2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="C4" s="39" t="n"/>
-      <c r="E4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="E4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="F4" s="51" t="inlineStr"/>
+      <c r="F4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="89" t="inlineStr">
         <is>
           <t>NOTE 3 : ETAT DES CREANCES ET DES DETTES NON ECHUES</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>CRÉANCES - clients-usagers et autres débiteurs</t>
         </is>
@@ -3234,109 +3130,109 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
+      <c r="A10" s="95" t="n"/>
+      <c r="B10" s="95" t="n"/>
+      <c r="C10" s="96" t="n"/>
+      <c r="D10" s="96" t="n"/>
+      <c r="E10" s="96">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="95">
         <f>IF(D10=0,"",(C10-D10)/D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
+      <c r="A11" s="95" t="n"/>
+      <c r="B11" s="95" t="n"/>
+      <c r="C11" s="96" t="n"/>
+      <c r="D11" s="96" t="n"/>
+      <c r="E11" s="96">
         <f>C11-D11</f>
         <v/>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="95">
         <f>IF(D11=0,"",(C11-D11)/D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
+      <c r="A12" s="95" t="n"/>
+      <c r="B12" s="95" t="n"/>
+      <c r="C12" s="96" t="n"/>
+      <c r="D12" s="96" t="n"/>
+      <c r="E12" s="96">
         <f>C12-D12</f>
         <v/>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="95">
         <f>IF(D12=0,"",(C12-D12)/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
+      <c r="A13" s="95" t="n"/>
+      <c r="B13" s="95" t="n"/>
+      <c r="C13" s="96" t="n"/>
+      <c r="D13" s="96" t="n"/>
+      <c r="E13" s="96">
         <f>C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="95">
         <f>IF(D13=0,"",(C13-D13)/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
+      <c r="A14" s="95" t="n"/>
+      <c r="B14" s="95" t="n"/>
+      <c r="C14" s="96" t="n"/>
+      <c r="D14" s="96" t="n"/>
+      <c r="E14" s="96">
         <f>C14-D14</f>
         <v/>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="95">
         <f>IF(D14=0,"",(C14-D14)/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
+      <c r="A15" s="95" t="n"/>
+      <c r="B15" s="95" t="n"/>
+      <c r="C15" s="96" t="n"/>
+      <c r="D15" s="96" t="n"/>
+      <c r="E15" s="96">
         <f>C15-D15</f>
         <v/>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="95">
         <f>IF(D15=0,"",(C15-D15)/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="85" t="n"/>
-      <c r="B16" s="85" t="inlineStr">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>TOTAL DES CRÉANCES</t>
         </is>
       </c>
-      <c r="C16" s="86">
+      <c r="C16" s="9">
         <f>SUM(C10:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="86">
+      <c r="D16" s="9">
         <f>SUM(D10:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="86">
+      <c r="E16" s="9">
         <f>SUM(E10:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="85" t="n"/>
+      <c r="F16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="98" t="inlineStr">
@@ -3345,7 +3241,7 @@
         </is>
       </c>
       <c r="C17" s="99">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$F$2:$F$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="D17" s="99">
@@ -3356,7 +3252,7 @@
     <row r="18"/>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>DETTES - fournisseurs et autres créditeurs</t>
         </is>
@@ -3395,109 +3291,109 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
+      <c r="A22" s="95" t="n"/>
+      <c r="B22" s="95" t="n"/>
+      <c r="C22" s="96" t="n"/>
+      <c r="D22" s="96" t="n"/>
+      <c r="E22" s="96">
         <f>C22-D22</f>
         <v/>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="95">
         <f>IF(D22=0,"",(C22-D22)/D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
+      <c r="A23" s="95" t="n"/>
+      <c r="B23" s="95" t="n"/>
+      <c r="C23" s="96" t="n"/>
+      <c r="D23" s="96" t="n"/>
+      <c r="E23" s="96">
         <f>C23-D23</f>
         <v/>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="95">
         <f>IF(D23=0,"",(C23-D23)/D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
+      <c r="A24" s="95" t="n"/>
+      <c r="B24" s="95" t="n"/>
+      <c r="C24" s="96" t="n"/>
+      <c r="D24" s="96" t="n"/>
+      <c r="E24" s="96">
         <f>C24-D24</f>
         <v/>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="95">
         <f>IF(D24=0,"",(C24-D24)/D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
+      <c r="A25" s="95" t="n"/>
+      <c r="B25" s="95" t="n"/>
+      <c r="C25" s="96" t="n"/>
+      <c r="D25" s="96" t="n"/>
+      <c r="E25" s="96">
         <f>C25-D25</f>
         <v/>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="95">
         <f>IF(D25=0,"",(C25-D25)/D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5">
+      <c r="A26" s="95" t="n"/>
+      <c r="B26" s="95" t="n"/>
+      <c r="C26" s="96" t="n"/>
+      <c r="D26" s="96" t="n"/>
+      <c r="E26" s="96">
         <f>C26-D26</f>
         <v/>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="95">
         <f>IF(D26=0,"",(C26-D26)/D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5">
+      <c r="A27" s="95" t="n"/>
+      <c r="B27" s="95" t="n"/>
+      <c r="C27" s="96" t="n"/>
+      <c r="D27" s="96" t="n"/>
+      <c r="E27" s="96">
         <f>C27-D27</f>
         <v/>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="95">
         <f>IF(D27=0,"",(C27-D27)/D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="85" t="n"/>
-      <c r="B28" s="85" t="inlineStr">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>TOTAL DES DETTES</t>
         </is>
       </c>
-      <c r="C28" s="86">
+      <c r="C28" s="9">
         <f>SUM(C22:C27)</f>
         <v/>
       </c>
-      <c r="D28" s="86">
+      <c r="D28" s="9">
         <f>SUM(D22:D27)</f>
         <v/>
       </c>
-      <c r="E28" s="86">
+      <c r="E28" s="9">
         <f>SUM(E22:E27)</f>
         <v/>
       </c>
-      <c r="F28" s="85" t="n"/>
+      <c r="F28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="98" t="inlineStr">
@@ -3506,7 +3402,7 @@
         </is>
       </c>
       <c r="C29" s="99">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="D29" s="99">
@@ -3556,74 +3452,74 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 11 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="J2" s="49" t="inlineStr">
+      <c r="J2" s="53" t="inlineStr">
         <is>
           <t>NOTE 4
 SYSCOHADA - SMT</t>
         </is>
       </c>
-      <c r="K2" s="50" t="n"/>
+      <c r="K2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="C4" s="39" t="n"/>
-      <c r="D4" s="39" t="n"/>
-      <c r="E4" s="39" t="n"/>
-      <c r="F4" s="39" t="n"/>
-      <c r="G4" s="39" t="n"/>
-      <c r="H4" s="39" t="n"/>
-      <c r="J4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="43" t="n"/>
+      <c r="H4" s="43" t="n"/>
+      <c r="J4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="K4" s="51" t="inlineStr"/>
+      <c r="K4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="H5" s="37" t="inlineStr">
+      <c r="H5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="J5" s="37" t="inlineStr">
+      <c r="J5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="89" t="inlineStr">
         <is>
           <t>NOTE 4 : JOURNAL DE TRESORERIE SMT</t>
         </is>
@@ -3687,256 +3583,256 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="95" t="n"/>
+      <c r="B9" s="95" t="inlineStr">
         <is>
           <t>Report à nouveau</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
+      <c r="C9" s="96" t="n"/>
+      <c r="D9" s="96" t="n"/>
+      <c r="E9" s="96" t="n"/>
+      <c r="F9" s="96" t="n"/>
+      <c r="G9" s="96" t="n"/>
+      <c r="H9" s="96" t="n"/>
+      <c r="I9" s="96" t="n"/>
+      <c r="J9" s="96" t="n"/>
+      <c r="K9" s="96" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
+      <c r="A10" s="95" t="n"/>
+      <c r="B10" s="95" t="n"/>
+      <c r="C10" s="96" t="n"/>
+      <c r="D10" s="96" t="n"/>
+      <c r="E10" s="96">
         <f>E9+C10-D10</f>
         <v/>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
+      <c r="F10" s="96" t="n"/>
+      <c r="G10" s="96" t="n"/>
+      <c r="H10" s="96" t="n"/>
+      <c r="I10" s="96" t="n"/>
+      <c r="J10" s="96" t="n"/>
+      <c r="K10" s="96" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
+      <c r="A11" s="95" t="n"/>
+      <c r="B11" s="95" t="n"/>
+      <c r="C11" s="96" t="n"/>
+      <c r="D11" s="96" t="n"/>
+      <c r="E11" s="96">
         <f>E10+C11-D11</f>
         <v/>
       </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
+      <c r="F11" s="96" t="n"/>
+      <c r="G11" s="96" t="n"/>
+      <c r="H11" s="96" t="n"/>
+      <c r="I11" s="96" t="n"/>
+      <c r="J11" s="96" t="n"/>
+      <c r="K11" s="96" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
+      <c r="A12" s="95" t="n"/>
+      <c r="B12" s="95" t="n"/>
+      <c r="C12" s="96" t="n"/>
+      <c r="D12" s="96" t="n"/>
+      <c r="E12" s="96">
         <f>E11+C12-D12</f>
         <v/>
       </c>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
+      <c r="F12" s="96" t="n"/>
+      <c r="G12" s="96" t="n"/>
+      <c r="H12" s="96" t="n"/>
+      <c r="I12" s="96" t="n"/>
+      <c r="J12" s="96" t="n"/>
+      <c r="K12" s="96" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
+      <c r="A13" s="95" t="n"/>
+      <c r="B13" s="95" t="n"/>
+      <c r="C13" s="96" t="n"/>
+      <c r="D13" s="96" t="n"/>
+      <c r="E13" s="96">
         <f>E12+C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
+      <c r="F13" s="96" t="n"/>
+      <c r="G13" s="96" t="n"/>
+      <c r="H13" s="96" t="n"/>
+      <c r="I13" s="96" t="n"/>
+      <c r="J13" s="96" t="n"/>
+      <c r="K13" s="96" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
+      <c r="A14" s="95" t="n"/>
+      <c r="B14" s="95" t="n"/>
+      <c r="C14" s="96" t="n"/>
+      <c r="D14" s="96" t="n"/>
+      <c r="E14" s="96">
         <f>E13+C14-D14</f>
         <v/>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="F14" s="96" t="n"/>
+      <c r="G14" s="96" t="n"/>
+      <c r="H14" s="96" t="n"/>
+      <c r="I14" s="96" t="n"/>
+      <c r="J14" s="96" t="n"/>
+      <c r="K14" s="96" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
+      <c r="A15" s="95" t="n"/>
+      <c r="B15" s="95" t="n"/>
+      <c r="C15" s="96" t="n"/>
+      <c r="D15" s="96" t="n"/>
+      <c r="E15" s="96">
         <f>E14+C15-D15</f>
         <v/>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
+      <c r="F15" s="96" t="n"/>
+      <c r="G15" s="96" t="n"/>
+      <c r="H15" s="96" t="n"/>
+      <c r="I15" s="96" t="n"/>
+      <c r="J15" s="96" t="n"/>
+      <c r="K15" s="96" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
+      <c r="A16" s="95" t="n"/>
+      <c r="B16" s="95" t="n"/>
+      <c r="C16" s="96" t="n"/>
+      <c r="D16" s="96" t="n"/>
+      <c r="E16" s="96">
         <f>E15+C16-D16</f>
         <v/>
       </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
+      <c r="F16" s="96" t="n"/>
+      <c r="G16" s="96" t="n"/>
+      <c r="H16" s="96" t="n"/>
+      <c r="I16" s="96" t="n"/>
+      <c r="J16" s="96" t="n"/>
+      <c r="K16" s="96" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
+      <c r="A17" s="95" t="n"/>
+      <c r="B17" s="95" t="n"/>
+      <c r="C17" s="96" t="n"/>
+      <c r="D17" s="96" t="n"/>
+      <c r="E17" s="96">
         <f>E16+C17-D17</f>
         <v/>
       </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
+      <c r="F17" s="96" t="n"/>
+      <c r="G17" s="96" t="n"/>
+      <c r="H17" s="96" t="n"/>
+      <c r="I17" s="96" t="n"/>
+      <c r="J17" s="96" t="n"/>
+      <c r="K17" s="96" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
+      <c r="A18" s="95" t="n"/>
+      <c r="B18" s="95" t="n"/>
+      <c r="C18" s="96" t="n"/>
+      <c r="D18" s="96" t="n"/>
+      <c r="E18" s="96">
         <f>E17+C18-D18</f>
         <v/>
       </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
+      <c r="F18" s="96" t="n"/>
+      <c r="G18" s="96" t="n"/>
+      <c r="H18" s="96" t="n"/>
+      <c r="I18" s="96" t="n"/>
+      <c r="J18" s="96" t="n"/>
+      <c r="K18" s="96" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
+      <c r="A19" s="95" t="n"/>
+      <c r="B19" s="95" t="n"/>
+      <c r="C19" s="96" t="n"/>
+      <c r="D19" s="96" t="n"/>
+      <c r="E19" s="96">
         <f>E18+C19-D19</f>
         <v/>
       </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
+      <c r="F19" s="96" t="n"/>
+      <c r="G19" s="96" t="n"/>
+      <c r="H19" s="96" t="n"/>
+      <c r="I19" s="96" t="n"/>
+      <c r="J19" s="96" t="n"/>
+      <c r="K19" s="96" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
+      <c r="A20" s="95" t="n"/>
+      <c r="B20" s="95" t="n"/>
+      <c r="C20" s="96" t="n"/>
+      <c r="D20" s="96" t="n"/>
+      <c r="E20" s="96">
         <f>E19+C20-D20</f>
         <v/>
       </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
+      <c r="F20" s="96" t="n"/>
+      <c r="G20" s="96" t="n"/>
+      <c r="H20" s="96" t="n"/>
+      <c r="I20" s="96" t="n"/>
+      <c r="J20" s="96" t="n"/>
+      <c r="K20" s="96" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
+      <c r="A21" s="95" t="n"/>
+      <c r="B21" s="95" t="n"/>
+      <c r="C21" s="96" t="n"/>
+      <c r="D21" s="96" t="n"/>
+      <c r="E21" s="96">
         <f>E20+C21-D21</f>
         <v/>
       </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
+      <c r="F21" s="96" t="n"/>
+      <c r="G21" s="96" t="n"/>
+      <c r="H21" s="96" t="n"/>
+      <c r="I21" s="96" t="n"/>
+      <c r="J21" s="96" t="n"/>
+      <c r="K21" s="96" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
+      <c r="A22" s="95" t="n"/>
+      <c r="B22" s="95" t="n"/>
+      <c r="C22" s="96" t="n"/>
+      <c r="D22" s="96" t="n"/>
+      <c r="E22" s="96">
         <f>E21+C22-D22</f>
         <v/>
       </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
+      <c r="F22" s="96" t="n"/>
+      <c r="G22" s="96" t="n"/>
+      <c r="H22" s="96" t="n"/>
+      <c r="I22" s="96" t="n"/>
+      <c r="J22" s="96" t="n"/>
+      <c r="K22" s="96" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
+      <c r="A23" s="95" t="n"/>
+      <c r="B23" s="95" t="n"/>
+      <c r="C23" s="96" t="n"/>
+      <c r="D23" s="96" t="n"/>
+      <c r="E23" s="96">
         <f>E22+C23-D23</f>
         <v/>
       </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
+      <c r="F23" s="96" t="n"/>
+      <c r="G23" s="96" t="n"/>
+      <c r="H23" s="96" t="n"/>
+      <c r="I23" s="96" t="n"/>
+      <c r="J23" s="96" t="n"/>
+      <c r="K23" s="96" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="85" t="n"/>
-      <c r="B24" s="85" t="inlineStr">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Solde à reporter</t>
         </is>
       </c>
       <c r="C24" s="97" t="n"/>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="86">
+      <c r="E24" s="9">
         <f>E23</f>
         <v/>
       </c>
@@ -3974,75 +3870,75 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 12 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>JOURNAUX DE SUIVI
 SYSCOHADA - SMT</t>
         </is>
       </c>
-      <c r="E2" s="50" t="n"/>
+      <c r="E2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr"/>
+      <c r="E4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="89" t="inlineStr">
         <is>
           <t>JOURNAUX DE SUIVI SMT : CREANCES IMPAYEES ET DETTES A PAYER</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>JOURNAL DE SUIVI DES CRÉANCES IMPAYÉES</t>
         </is>
@@ -4076,72 +3972,72 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="4" t="n"/>
+      <c r="A10" s="95" t="n"/>
+      <c r="B10" s="95" t="n"/>
+      <c r="C10" s="95" t="n"/>
+      <c r="D10" s="96" t="n"/>
+      <c r="E10" s="95" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="4" t="n"/>
+      <c r="A11" s="95" t="n"/>
+      <c r="B11" s="95" t="n"/>
+      <c r="C11" s="95" t="n"/>
+      <c r="D11" s="96" t="n"/>
+      <c r="E11" s="95" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="4" t="n"/>
+      <c r="A12" s="95" t="n"/>
+      <c r="B12" s="95" t="n"/>
+      <c r="C12" s="95" t="n"/>
+      <c r="D12" s="96" t="n"/>
+      <c r="E12" s="95" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="4" t="n"/>
+      <c r="A13" s="95" t="n"/>
+      <c r="B13" s="95" t="n"/>
+      <c r="C13" s="95" t="n"/>
+      <c r="D13" s="96" t="n"/>
+      <c r="E13" s="95" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="4" t="n"/>
+      <c r="A14" s="95" t="n"/>
+      <c r="B14" s="95" t="n"/>
+      <c r="C14" s="95" t="n"/>
+      <c r="D14" s="96" t="n"/>
+      <c r="E14" s="95" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="4" t="n"/>
+      <c r="A15" s="95" t="n"/>
+      <c r="B15" s="95" t="n"/>
+      <c r="C15" s="95" t="n"/>
+      <c r="D15" s="96" t="n"/>
+      <c r="E15" s="95" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="4" t="n"/>
+      <c r="A16" s="95" t="n"/>
+      <c r="B16" s="95" t="n"/>
+      <c r="C16" s="95" t="n"/>
+      <c r="D16" s="96" t="n"/>
+      <c r="E16" s="95" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="85" t="n"/>
-      <c r="B17" s="85" t="n"/>
-      <c r="C17" s="85" t="inlineStr">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D17" s="86">
+      <c r="D17" s="9">
         <f>SUM(D10:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="85" t="n"/>
+      <c r="E17" s="8" t="n"/>
     </row>
     <row r="18"/>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>JOURNAL DE SUIVI DES DETTES À PAYER</t>
         </is>
@@ -4175,67 +4071,67 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="4" t="n"/>
+      <c r="A22" s="95" t="n"/>
+      <c r="B22" s="95" t="n"/>
+      <c r="C22" s="95" t="n"/>
+      <c r="D22" s="96" t="n"/>
+      <c r="E22" s="95" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="4" t="n"/>
+      <c r="A23" s="95" t="n"/>
+      <c r="B23" s="95" t="n"/>
+      <c r="C23" s="95" t="n"/>
+      <c r="D23" s="96" t="n"/>
+      <c r="E23" s="95" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="4" t="n"/>
+      <c r="A24" s="95" t="n"/>
+      <c r="B24" s="95" t="n"/>
+      <c r="C24" s="95" t="n"/>
+      <c r="D24" s="96" t="n"/>
+      <c r="E24" s="95" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="4" t="n"/>
+      <c r="A25" s="95" t="n"/>
+      <c r="B25" s="95" t="n"/>
+      <c r="C25" s="95" t="n"/>
+      <c r="D25" s="96" t="n"/>
+      <c r="E25" s="95" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="4" t="n"/>
+      <c r="A26" s="95" t="n"/>
+      <c r="B26" s="95" t="n"/>
+      <c r="C26" s="95" t="n"/>
+      <c r="D26" s="96" t="n"/>
+      <c r="E26" s="95" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="4" t="n"/>
+      <c r="A27" s="95" t="n"/>
+      <c r="B27" s="95" t="n"/>
+      <c r="C27" s="95" t="n"/>
+      <c r="D27" s="96" t="n"/>
+      <c r="E27" s="95" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="4" t="n"/>
+      <c r="A28" s="95" t="n"/>
+      <c r="B28" s="95" t="n"/>
+      <c r="C28" s="95" t="n"/>
+      <c r="D28" s="96" t="n"/>
+      <c r="E28" s="95" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="85" t="n"/>
-      <c r="B29" s="85" t="n"/>
-      <c r="C29" s="85" t="inlineStr">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D29" s="86">
+      <c r="D29" s="9">
         <f>SUM(D22:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="85" t="n"/>
+      <c r="E29" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4266,7 +4162,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>TABLE DES COMMENTAIRES</t>
         </is>
@@ -4277,46 +4173,46 @@
 PAGE 1/2</t>
         </is>
       </c>
-      <c r="H1" s="50" t="n"/>
+      <c r="H1" s="54" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="63" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">Adresse : </t>
         </is>
       </c>
-      <c r="F3" s="63" t="inlineStr">
+      <c r="F3" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">Sigle usuel : </t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="E4" s="63" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="G4" s="63" t="inlineStr">
+      <c r="G4" s="67" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="63" t="inlineStr">
+      <c r="A5" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">N° de télédéclarant (NTD) : </t>
         </is>
@@ -4347,22 +4243,22 @@
           <t>Tableau SMT de suivi du matériel, du mobilier et des cautions</t>
         </is>
       </c>
-      <c r="C7" s="45" t="n"/>
-      <c r="D7" s="45" t="n"/>
-      <c r="E7" s="45" t="n"/>
-      <c r="F7" s="45" t="n"/>
-      <c r="G7" s="45" t="n"/>
-      <c r="H7" s="45" t="n"/>
+      <c r="C7" s="49" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="49" t="n"/>
     </row>
     <row r="8" ht="110" customHeight="1">
       <c r="A8" s="105" t="n"/>
-      <c r="B8" s="45" t="n"/>
-      <c r="C8" s="45" t="n"/>
-      <c r="D8" s="45" t="n"/>
-      <c r="E8" s="45" t="n"/>
-      <c r="F8" s="45" t="n"/>
-      <c r="G8" s="45" t="n"/>
-      <c r="H8" s="45" t="n"/>
+      <c r="B8" s="49" t="n"/>
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="49" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="103" t="inlineStr">
@@ -4375,22 +4271,22 @@
           <t>État des stocks</t>
         </is>
       </c>
-      <c r="C9" s="45" t="n"/>
-      <c r="D9" s="45" t="n"/>
-      <c r="E9" s="45" t="n"/>
-      <c r="F9" s="45" t="n"/>
-      <c r="G9" s="45" t="n"/>
-      <c r="H9" s="45" t="n"/>
+      <c r="C9" s="49" t="n"/>
+      <c r="D9" s="49" t="n"/>
+      <c r="E9" s="49" t="n"/>
+      <c r="F9" s="49" t="n"/>
+      <c r="G9" s="49" t="n"/>
+      <c r="H9" s="49" t="n"/>
     </row>
     <row r="10" ht="110" customHeight="1">
       <c r="A10" s="105" t="n"/>
-      <c r="B10" s="45" t="n"/>
-      <c r="C10" s="45" t="n"/>
-      <c r="D10" s="45" t="n"/>
-      <c r="E10" s="45" t="n"/>
-      <c r="F10" s="45" t="n"/>
-      <c r="G10" s="45" t="n"/>
-      <c r="H10" s="45" t="n"/>
+      <c r="B10" s="49" t="n"/>
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="49" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="103" t="inlineStr">
@@ -4403,22 +4299,22 @@
           <t>État des créances et des dettes non échues</t>
         </is>
       </c>
-      <c r="C11" s="45" t="n"/>
-      <c r="D11" s="45" t="n"/>
-      <c r="E11" s="45" t="n"/>
-      <c r="F11" s="45" t="n"/>
-      <c r="G11" s="45" t="n"/>
-      <c r="H11" s="45" t="n"/>
+      <c r="C11" s="49" t="n"/>
+      <c r="D11" s="49" t="n"/>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="49" t="n"/>
     </row>
     <row r="12" ht="110" customHeight="1">
       <c r="A12" s="105" t="n"/>
-      <c r="B12" s="45" t="n"/>
-      <c r="C12" s="45" t="n"/>
-      <c r="D12" s="45" t="n"/>
-      <c r="E12" s="45" t="n"/>
-      <c r="F12" s="45" t="n"/>
-      <c r="G12" s="45" t="n"/>
-      <c r="H12" s="45" t="n"/>
+      <c r="B12" s="49" t="n"/>
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="49" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="101" t="inlineStr">
@@ -4445,25 +4341,25 @@
           <t>Journal de trésorerie SMT</t>
         </is>
       </c>
-      <c r="C14" s="45" t="n"/>
-      <c r="D14" s="45" t="n"/>
-      <c r="E14" s="45" t="n"/>
-      <c r="F14" s="45" t="n"/>
-      <c r="G14" s="45" t="n"/>
-      <c r="H14" s="45" t="n"/>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="49" t="n"/>
+      <c r="F14" s="49" t="n"/>
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="49" t="n"/>
     </row>
     <row r="15" ht="110" customHeight="1">
       <c r="A15" s="105" t="n"/>
-      <c r="B15" s="45" t="n"/>
-      <c r="C15" s="45" t="n"/>
-      <c r="D15" s="45" t="n"/>
-      <c r="E15" s="45" t="n"/>
-      <c r="F15" s="45" t="n"/>
-      <c r="G15" s="45" t="n"/>
-      <c r="H15" s="45" t="n"/>
+      <c r="B15" s="49" t="n"/>
+      <c r="C15" s="49" t="n"/>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="49" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="49" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="A16" s="57" t="inlineStr">
         <is>
           <t>TABLE DES COMMENTAIRES</t>
         </is>
@@ -4474,46 +4370,46 @@
 PAGE 2/2</t>
         </is>
       </c>
-      <c r="H16" s="50" t="n"/>
+      <c r="H16" s="54" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="63" t="inlineStr">
+      <c r="A17" s="67" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="63" t="inlineStr">
+      <c r="A18" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">Adresse : </t>
         </is>
       </c>
-      <c r="F18" s="63" t="inlineStr">
+      <c r="F18" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">Sigle usuel : </t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="63" t="inlineStr">
+      <c r="A19" s="67" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="E19" s="63" t="inlineStr">
+      <c r="E19" s="67" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="G19" s="63" t="inlineStr">
+      <c r="G19" s="67" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="63" t="inlineStr">
+      <c r="A20" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">N° de télédéclarant (NTD) : </t>
         </is>
@@ -4526,22 +4422,22 @@
           <t>Journal de suivi des créances impayées</t>
         </is>
       </c>
-      <c r="C21" s="45" t="n"/>
-      <c r="D21" s="45" t="n"/>
-      <c r="E21" s="45" t="n"/>
-      <c r="F21" s="45" t="n"/>
-      <c r="G21" s="45" t="n"/>
-      <c r="H21" s="45" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="49" t="n"/>
     </row>
     <row r="22" ht="110" customHeight="1">
       <c r="A22" s="105" t="n"/>
-      <c r="B22" s="45" t="n"/>
-      <c r="C22" s="45" t="n"/>
-      <c r="D22" s="45" t="n"/>
-      <c r="E22" s="45" t="n"/>
-      <c r="F22" s="45" t="n"/>
-      <c r="G22" s="45" t="n"/>
-      <c r="H22" s="45" t="n"/>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="49" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="103" t="inlineStr"/>
@@ -4550,22 +4446,22 @@
           <t>Journal de suivi des dettes à payer</t>
         </is>
       </c>
-      <c r="C23" s="45" t="n"/>
-      <c r="D23" s="45" t="n"/>
-      <c r="E23" s="45" t="n"/>
-      <c r="F23" s="45" t="n"/>
-      <c r="G23" s="45" t="n"/>
-      <c r="H23" s="45" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="49" t="n"/>
     </row>
     <row r="24" ht="110" customHeight="1">
       <c r="A24" s="105" t="n"/>
-      <c r="B24" s="45" t="n"/>
-      <c r="C24" s="45" t="n"/>
-      <c r="D24" s="45" t="n"/>
-      <c r="E24" s="45" t="n"/>
-      <c r="F24" s="45" t="n"/>
-      <c r="G24" s="45" t="n"/>
-      <c r="H24" s="45" t="n"/>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="49" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4624,92 +4520,92 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Total solde débit balance</t>
-        </is>
-      </c>
-      <c r="B2" s="5">
-        <f>SUM('BALANCE N'!F2:F18)</f>
-        <v/>
-      </c>
-      <c r="C2" s="4" t="inlineStr"/>
+      <c r="A2" s="95" t="inlineStr">
+        <is>
+          <t>Total solde de clôture débit balance</t>
+        </is>
+      </c>
+      <c r="B2" s="96">
+        <f>SUM('BALANCE N'!G2:G18)</f>
+        <v/>
+      </c>
+      <c r="C2" s="95" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Total solde crédit balance</t>
-        </is>
-      </c>
-      <c r="B3" s="5">
-        <f>SUM('BALANCE N'!G2:G18)</f>
-        <v/>
-      </c>
-      <c r="C3" s="4" t="inlineStr"/>
+      <c r="A3" s="95" t="inlineStr">
+        <is>
+          <t>Total solde de clôture crédit balance</t>
+        </is>
+      </c>
+      <c r="B3" s="96">
+        <f>SUM('BALANCE N'!H2:H18)</f>
+        <v/>
+      </c>
+      <c r="C3" s="95" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="95" t="inlineStr">
         <is>
           <t>Écart balance (doit être 0)</t>
         </is>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="96">
         <f>B2-B3</f>
         <v/>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="95" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="95" t="inlineStr">
         <is>
           <t>Total actif</t>
         </is>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="96">
         <f>'Bilan-Actif'!D14</f>
         <v/>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
+      <c r="C5" s="95" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="95" t="inlineStr">
         <is>
           <t>Total passif</t>
         </is>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="96">
         <f>'Bilan-Passif'!D13</f>
         <v/>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="C6" s="95" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="95" t="inlineStr">
         <is>
           <t>Écart actif - passif (doit être 0)</t>
         </is>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="96">
         <f>B5-B6</f>
         <v/>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="95" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="95" t="inlineStr">
         <is>
           <t>Résultat (compte de résultat, G)</t>
         </is>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="96">
         <f>'Résultat'!D24</f>
         <v/>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="C8" s="95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4760,46 +4656,46 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="95" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="95" t="inlineStr"/>
+      <c r="C2" s="95" t="inlineStr">
         <is>
           <t>Classe 4</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="95" t="inlineStr">
         <is>
           <t>La balance porte des comptes de tiers : recettes et dépenses incluent alors des montants non encaissés/décaissés (base engagement).</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="95" t="inlineStr">
         <is>
           <t>Dans ce cas, laisser VB et VC à zéro : le résultat est déjà en base engagement. Ne les servir que pour une balance de trésorerie pure, depuis l'inventaire extra-comptable (NOTE 3).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="95" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="95" t="inlineStr"/>
+      <c r="C3" s="95" t="inlineStr">
         <is>
           <t>SMT - seuils</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="95" t="inlineStr">
         <is>
           <t>Vérifier l'assujettissement au SMT : CA HT ≤ 60 M FCFA (négoce), 40 M (artisanat), 30 M (services) - AUDCIF art. 13.</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="95" t="inlineStr">
         <is>
           <t>Au-delà des seuils, monter la liasse du Système normal (monter_liasse.py).</t>
         </is>
@@ -4816,7 +4712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -4824,84 +4720,112 @@
     <col width="20.7" customWidth="1" min="3" max="3"/>
     <col width="20.7" customWidth="1" min="4" max="4"/>
     <col width="20.7" customWidth="1" min="5" max="5"/>
+    <col width="20.7" customWidth="1" min="6" max="6"/>
+    <col width="20.7" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>EQUILIBRE DE LA BALANCE</t>
         </is>
       </c>
-      <c r="B1" s="7" t="n"/>
-      <c r="C1" s="7" t="n"/>
-      <c r="D1" s="7" t="n"/>
-      <c r="E1" s="7" t="n"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="11" t="n"/>
     </row>
     <row r="2" ht="50" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>BALANCE N</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Solde d'ouverture Débit</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Solde d'ouverture Crédit</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>Mouvements Débit</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>Mouvements Crédit</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>Solde Final Débit</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>Solde Final Crédit</t>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Solde de clôture Débit</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>Solde de clôture Crédit</t>
         </is>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
-      <c r="A3" s="12" t="n"/>
-      <c r="B3" s="13">
+      <c r="A3" s="16" t="n"/>
+      <c r="B3" s="17">
+        <f>SUM('BALANCE N'!C2:C18)</f>
+        <v/>
+      </c>
+      <c r="C3" s="17">
+        <f>SUM('BALANCE N'!D2:D18)</f>
+        <v/>
+      </c>
+      <c r="D3" s="17">
+        <f>SUM('BALANCE N'!E2:E18)</f>
+        <v/>
+      </c>
+      <c r="E3" s="17">
+        <f>SUM('BALANCE N'!F2:F18)</f>
+        <v/>
+      </c>
+      <c r="F3" s="17">
+        <f>SUM('BALANCE N'!G2:G18)</f>
+        <v/>
+      </c>
+      <c r="G3" s="18">
         <f>SUM('BALANCE N'!H2:H18)</f>
         <v/>
       </c>
-      <c r="C3" s="13">
-        <f>SUM('BALANCE N'!I2:I18)</f>
-        <v/>
-      </c>
-      <c r="D3" s="13">
-        <f>SUM('BALANCE N'!F2:F18)</f>
-        <v/>
-      </c>
-      <c r="E3" s="14">
-        <f>SUM('BALANCE N'!G2:G18)</f>
-        <v/>
-      </c>
     </row>
     <row r="4" ht="54" customHeight="1">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="16">
+      <c r="A4" s="19" t="n"/>
+      <c r="B4" s="20">
         <f>IF(ROUND(B3-C3,0)=0,"Equilibre","Déséquilibre : écart de "&amp;TEXT(B3-C3,"#,##0"))</f>
         <v/>
       </c>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="16">
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="20">
         <f>IF(ROUND(D3-E3,0)=0,"Equilibre","Déséquilibre : écart de "&amp;TEXT(D3-E3,"#,##0"))</f>
         <v/>
       </c>
-      <c r="E4" s="18" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="20">
+        <f>IF(ROUND(F3-G3,0)=0,"Equilibre","Déséquilibre : écart de "&amp;TEXT(F3-G3,"#,##0"))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D4:E4"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4933,281 +4857,281 @@
   <sheetData>
     <row r="1" ht="4" customHeight="1"/>
     <row r="2" ht="4" customHeight="1">
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="20" t="n"/>
-      <c r="H2" s="20" t="n"/>
-      <c r="I2" s="20" t="n"/>
-      <c r="J2" s="20" t="n"/>
-      <c r="K2" s="20" t="n"/>
-      <c r="L2" s="20" t="n"/>
-      <c r="M2" s="21" t="n"/>
+      <c r="B2" s="23" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+      <c r="G2" s="24" t="n"/>
+      <c r="H2" s="24" t="n"/>
+      <c r="I2" s="24" t="n"/>
+      <c r="J2" s="24" t="n"/>
+      <c r="K2" s="24" t="n"/>
+      <c r="L2" s="24" t="n"/>
+      <c r="M2" s="25" t="n"/>
     </row>
     <row r="3" ht="13" customHeight="1">
-      <c r="B3" s="12" t="n"/>
-      <c r="C3" s="22" t="n"/>
-      <c r="D3" s="22" t="n"/>
-      <c r="M3" s="23" t="n"/>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="26" t="n"/>
+      <c r="M3" s="27" t="n"/>
     </row>
     <row r="4" ht="13" customHeight="1">
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n"/>
-      <c r="M4" s="23" t="n"/>
+      <c r="B4" s="16" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="M4" s="27" t="n"/>
     </row>
     <row r="5" ht="13" customHeight="1">
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="M5" s="23" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="M5" s="27" t="n"/>
     </row>
     <row r="6" ht="13" customHeight="1">
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="22" t="n"/>
-      <c r="M6" s="23" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="M6" s="27" t="n"/>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="M7" s="23" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26" t="n"/>
+      <c r="M7" s="27" t="n"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="M8" s="23" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="M8" s="27" t="n"/>
     </row>
     <row r="9" ht="13" customHeight="1">
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="M9" s="23" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26" t="n"/>
+      <c r="M9" s="27" t="n"/>
     </row>
     <row r="10" ht="13" customHeight="1">
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="M10" s="23" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="M10" s="27" t="n"/>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="M11" s="23" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="M11" s="27" t="n"/>
     </row>
     <row r="12" ht="13" customHeight="1">
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="M12" s="23" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="M12" s="27" t="n"/>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="M13" s="23" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="M13" s="27" t="n"/>
     </row>
     <row r="14" ht="13" customHeight="1">
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="M14" s="23" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="M14" s="27" t="n"/>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="M15" s="23" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26" t="n"/>
+      <c r="M15" s="27" t="n"/>
     </row>
     <row r="16" ht="13" customHeight="1">
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="M16" s="23" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="M16" s="27" t="n"/>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="M17" s="23" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="26" t="n"/>
+      <c r="M17" s="27" t="n"/>
     </row>
     <row r="18" ht="13" customHeight="1">
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="M18" s="23" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="M18" s="27" t="n"/>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="B19" s="12" t="n"/>
-      <c r="M19" s="23" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="M19" s="27" t="n"/>
     </row>
     <row r="20" ht="13" customHeight="1">
-      <c r="B20" s="12" t="n"/>
-      <c r="M20" s="23" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="M20" s="27" t="n"/>
     </row>
     <row r="21" ht="13" customHeight="1">
-      <c r="B21" s="12" t="n"/>
-      <c r="M21" s="23" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="M21" s="27" t="n"/>
     </row>
     <row r="22" ht="13" customHeight="1">
-      <c r="B22" s="12" t="n"/>
-      <c r="M22" s="23" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="M22" s="27" t="n"/>
     </row>
     <row r="23" ht="13" customHeight="1">
-      <c r="B23" s="12" t="n"/>
-      <c r="M23" s="23" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="M23" s="27" t="n"/>
     </row>
     <row r="24" ht="13" customHeight="1">
-      <c r="B24" s="12" t="n"/>
-      <c r="M24" s="23" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="M24" s="27" t="n"/>
     </row>
     <row r="25" ht="13" customHeight="1">
-      <c r="B25" s="12" t="n"/>
-      <c r="M25" s="23" t="n"/>
+      <c r="B25" s="16" t="n"/>
+      <c r="M25" s="27" t="n"/>
     </row>
     <row r="26" ht="13" customHeight="1">
-      <c r="B26" s="12" t="n"/>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="B26" s="16" t="n"/>
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
-      <c r="M26" s="23" t="n"/>
+      <c r="M26" s="27" t="n"/>
     </row>
     <row r="27" ht="13" customHeight="1">
-      <c r="B27" s="12" t="n"/>
-      <c r="M27" s="23" t="n"/>
+      <c r="B27" s="16" t="n"/>
+      <c r="M27" s="27" t="n"/>
     </row>
     <row r="28" ht="13" customHeight="1">
-      <c r="B28" s="12" t="n"/>
-      <c r="M28" s="23" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="M28" s="27" t="n"/>
     </row>
     <row r="29" ht="13" customHeight="1">
-      <c r="B29" s="12" t="n"/>
-      <c r="M29" s="23" t="n"/>
+      <c r="B29" s="16" t="n"/>
+      <c r="M29" s="27" t="n"/>
     </row>
     <row r="30" ht="13" customHeight="1">
-      <c r="B30" s="12" t="n"/>
-      <c r="M30" s="23" t="n"/>
+      <c r="B30" s="16" t="n"/>
+      <c r="M30" s="27" t="n"/>
     </row>
     <row r="31" ht="33" customHeight="1">
-      <c r="B31" s="12" t="n"/>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="B31" s="16" t="n"/>
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>LIASSE SMT</t>
         </is>
       </c>
-      <c r="F31" s="26" t="n"/>
-      <c r="G31" s="26" t="n"/>
-      <c r="H31" s="26" t="n"/>
-      <c r="I31" s="26" t="n"/>
-      <c r="J31" s="26" t="n"/>
-      <c r="K31" s="26" t="n"/>
-      <c r="M31" s="23" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+      <c r="H31" s="30" t="n"/>
+      <c r="I31" s="30" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="M31" s="27" t="n"/>
     </row>
     <row r="32" ht="13" customHeight="1">
-      <c r="B32" s="12" t="n"/>
-      <c r="M32" s="23" t="n"/>
+      <c r="B32" s="16" t="n"/>
+      <c r="M32" s="27" t="n"/>
     </row>
     <row r="33" ht="13" customHeight="1">
-      <c r="B33" s="12" t="n"/>
-      <c r="M33" s="23" t="n"/>
+      <c r="B33" s="16" t="n"/>
+      <c r="M33" s="27" t="n"/>
     </row>
     <row r="34" ht="13" customHeight="1">
-      <c r="B34" s="12" t="n"/>
-      <c r="E34" s="27" t="inlineStr">
+      <c r="B34" s="16" t="n"/>
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="M34" s="23" t="n"/>
+      <c r="M34" s="27" t="n"/>
     </row>
     <row r="35" ht="13" customHeight="1">
-      <c r="B35" s="12" t="n"/>
-      <c r="M35" s="23" t="n"/>
+      <c r="B35" s="16" t="n"/>
+      <c r="M35" s="27" t="n"/>
     </row>
     <row r="36" ht="13" customHeight="1">
-      <c r="B36" s="12" t="n"/>
-      <c r="M36" s="23" t="n"/>
+      <c r="B36" s="16" t="n"/>
+      <c r="M36" s="27" t="n"/>
     </row>
     <row r="37" ht="13" customHeight="1">
-      <c r="B37" s="12" t="n"/>
-      <c r="M37" s="23" t="n"/>
+      <c r="B37" s="16" t="n"/>
+      <c r="M37" s="27" t="n"/>
     </row>
     <row r="38" ht="13" customHeight="1">
-      <c r="B38" s="12" t="n"/>
-      <c r="M38" s="23" t="n"/>
+      <c r="B38" s="16" t="n"/>
+      <c r="M38" s="27" t="n"/>
     </row>
     <row r="39" ht="13" customHeight="1">
-      <c r="B39" s="12" t="n"/>
-      <c r="M39" s="23" t="n"/>
+      <c r="B39" s="16" t="n"/>
+      <c r="M39" s="27" t="n"/>
     </row>
     <row r="40" ht="13" customHeight="1">
-      <c r="B40" s="12" t="n"/>
-      <c r="M40" s="23" t="n"/>
+      <c r="B40" s="16" t="n"/>
+      <c r="M40" s="27" t="n"/>
     </row>
     <row r="41" ht="13" customHeight="1">
-      <c r="B41" s="12" t="n"/>
-      <c r="M41" s="23" t="n"/>
+      <c r="B41" s="16" t="n"/>
+      <c r="M41" s="27" t="n"/>
     </row>
     <row r="42" ht="13" customHeight="1">
-      <c r="B42" s="12" t="n"/>
-      <c r="M42" s="23" t="n"/>
+      <c r="B42" s="16" t="n"/>
+      <c r="M42" s="27" t="n"/>
     </row>
     <row r="43" ht="13" customHeight="1">
-      <c r="B43" s="12" t="n"/>
-      <c r="M43" s="23" t="n"/>
+      <c r="B43" s="16" t="n"/>
+      <c r="M43" s="27" t="n"/>
     </row>
     <row r="44" ht="13" customHeight="1">
-      <c r="B44" s="12" t="n"/>
-      <c r="M44" s="23" t="n"/>
+      <c r="B44" s="16" t="n"/>
+      <c r="M44" s="27" t="n"/>
     </row>
     <row r="45" ht="13" customHeight="1">
-      <c r="B45" s="12" t="n"/>
-      <c r="M45" s="23" t="n"/>
+      <c r="B45" s="16" t="n"/>
+      <c r="M45" s="27" t="n"/>
     </row>
     <row r="46" ht="13" customHeight="1">
-      <c r="B46" s="12" t="n"/>
-      <c r="M46" s="23" t="n"/>
+      <c r="B46" s="16" t="n"/>
+      <c r="M46" s="27" t="n"/>
     </row>
     <row r="47" ht="13" customHeight="1">
-      <c r="B47" s="12" t="n"/>
-      <c r="M47" s="23" t="n"/>
+      <c r="B47" s="16" t="n"/>
+      <c r="M47" s="27" t="n"/>
     </row>
     <row r="48" ht="13" customHeight="1">
-      <c r="B48" s="12" t="n"/>
-      <c r="M48" s="23" t="n"/>
+      <c r="B48" s="16" t="n"/>
+      <c r="M48" s="27" t="n"/>
     </row>
     <row r="49" ht="13" customHeight="1">
-      <c r="B49" s="12" t="n"/>
-      <c r="M49" s="23" t="n"/>
+      <c r="B49" s="16" t="n"/>
+      <c r="M49" s="27" t="n"/>
     </row>
     <row r="50" ht="13" customHeight="1">
-      <c r="B50" s="12" t="n"/>
-      <c r="M50" s="23" t="n"/>
+      <c r="B50" s="16" t="n"/>
+      <c r="M50" s="27" t="n"/>
     </row>
     <row r="51" ht="13" customHeight="1">
-      <c r="B51" s="12" t="n"/>
-      <c r="M51" s="23" t="n"/>
+      <c r="B51" s="16" t="n"/>
+      <c r="M51" s="27" t="n"/>
     </row>
     <row r="52" ht="13" customHeight="1">
-      <c r="B52" s="15" t="n"/>
-      <c r="C52" s="28" t="n"/>
-      <c r="D52" s="28" t="n"/>
-      <c r="E52" s="28" t="n"/>
-      <c r="F52" s="28" t="n"/>
-      <c r="G52" s="28" t="n"/>
-      <c r="H52" s="28" t="n"/>
-      <c r="I52" s="28" t="n"/>
-      <c r="J52" s="28" t="n"/>
-      <c r="K52" s="28" t="n"/>
-      <c r="L52" s="28" t="n"/>
-      <c r="M52" s="29" t="n"/>
+      <c r="B52" s="19" t="n"/>
+      <c r="C52" s="32" t="n"/>
+      <c r="D52" s="32" t="n"/>
+      <c r="E52" s="32" t="n"/>
+      <c r="F52" s="32" t="n"/>
+      <c r="G52" s="32" t="n"/>
+      <c r="H52" s="32" t="n"/>
+      <c r="I52" s="32" t="n"/>
+      <c r="J52" s="32" t="n"/>
+      <c r="K52" s="32" t="n"/>
+      <c r="L52" s="32" t="n"/>
+      <c r="M52" s="33" t="n"/>
     </row>
     <row r="53" ht="5" customHeight="1"/>
   </sheetData>
@@ -5255,42 +5179,42 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12" ht="44" customHeight="1">
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>ETATS FINANCIERS NORMALISES
 DU SYSTEME COMPTABLE OHADA (SYSCOHADA REVISE - AUDCIF)</t>
         </is>
       </c>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="31" t="n"/>
-      <c r="E12" s="31" t="n"/>
-      <c r="F12" s="31" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="31" t="n"/>
-      <c r="I12" s="31" t="n"/>
-      <c r="J12" s="31" t="n"/>
-      <c r="K12" s="31" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="35" t="n"/>
+      <c r="E12" s="35" t="n"/>
+      <c r="F12" s="35" t="n"/>
+      <c r="G12" s="35" t="n"/>
+      <c r="H12" s="35" t="n"/>
+      <c r="I12" s="35" t="n"/>
+      <c r="J12" s="35" t="n"/>
+      <c r="K12" s="35" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Entités relevant du Système minimal de trésorerie</t>
         </is>
       </c>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="33" t="n"/>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="33" t="n"/>
-      <c r="H13" s="33" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="33" t="n"/>
-      <c r="K13" s="33" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="37" t="n"/>
     </row>
     <row r="14"/>
     <row r="15"/>
     <row r="16" ht="18" customHeight="1">
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025   -   Durée (en mois) : 12</t>
         </is>
@@ -5300,300 +5224,300 @@
     <row r="18"/>
     <row r="19"/>
     <row r="20" ht="16" customHeight="1">
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>DESIGNATION DE L'ENTITE</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n"/>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
-      <c r="F20" s="36" t="n"/>
-      <c r="G20" s="36" t="n"/>
-      <c r="H20" s="36" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="J20" s="36" t="n"/>
-      <c r="K20" s="36" t="n"/>
+      <c r="C20" s="40" t="n"/>
+      <c r="D20" s="40" t="n"/>
+      <c r="E20" s="40" t="n"/>
+      <c r="F20" s="40" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="40" t="n"/>
+      <c r="I20" s="40" t="n"/>
+      <c r="J20" s="40" t="n"/>
+      <c r="K20" s="40" t="n"/>
     </row>
     <row r="21"/>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>DENOMINATION SOCIALE :</t>
         </is>
       </c>
-      <c r="E22" s="38" t="inlineStr">
+      <c r="E22" s="42" t="inlineStr">
         <is>
           <t>ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
-      <c r="F22" s="39" t="n"/>
-      <c r="G22" s="39" t="n"/>
-      <c r="H22" s="39" t="n"/>
-      <c r="I22" s="39" t="n"/>
-      <c r="J22" s="39" t="n"/>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="43" t="n"/>
+      <c r="H22" s="43" t="n"/>
+      <c r="I22" s="43" t="n"/>
+      <c r="J22" s="43" t="n"/>
     </row>
     <row r="23"/>
     <row r="24">
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>SIGLE USUEL :</t>
         </is>
       </c>
-      <c r="E24" s="38" t="inlineStr"/>
-      <c r="F24" s="39" t="n"/>
-      <c r="G24" s="39" t="n"/>
-      <c r="H24" s="39" t="n"/>
-      <c r="I24" s="39" t="n"/>
-      <c r="J24" s="39" t="n"/>
+      <c r="E24" s="42" t="inlineStr"/>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="43" t="n"/>
+      <c r="H24" s="43" t="n"/>
+      <c r="I24" s="43" t="n"/>
+      <c r="J24" s="43" t="n"/>
     </row>
     <row r="25"/>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>ADRESSE COMPLETE :</t>
         </is>
       </c>
-      <c r="E26" s="38" t="inlineStr"/>
-      <c r="F26" s="39" t="n"/>
-      <c r="G26" s="39" t="n"/>
-      <c r="H26" s="39" t="n"/>
-      <c r="I26" s="39" t="n"/>
-      <c r="J26" s="39" t="n"/>
+      <c r="E26" s="42" t="inlineStr"/>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="43" t="n"/>
+      <c r="H26" s="43" t="n"/>
+      <c r="I26" s="43" t="n"/>
+      <c r="J26" s="43" t="n"/>
     </row>
     <row r="27"/>
     <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="40" t="inlineStr">
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) :</t>
         </is>
       </c>
-      <c r="E28" s="38" t="inlineStr">
+      <c r="E28" s="42" t="inlineStr">
         <is>
           <t>RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="F28" s="39" t="n"/>
-      <c r="G28" s="39" t="n"/>
-      <c r="H28" s="39" t="n"/>
-      <c r="I28" s="39" t="n"/>
-      <c r="J28" s="39" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="43" t="n"/>
+      <c r="H28" s="43" t="n"/>
+      <c r="I28" s="43" t="n"/>
+      <c r="J28" s="43" t="n"/>
     </row>
     <row r="29"/>
     <row r="30" ht="14" customHeight="1">
-      <c r="B30" s="40" t="inlineStr">
+      <c r="B30" s="44" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
-      <c r="E30" s="38" t="inlineStr"/>
-      <c r="F30" s="39" t="n"/>
-      <c r="G30" s="39" t="n"/>
-      <c r="H30" s="39" t="n"/>
-      <c r="I30" s="39" t="n"/>
-      <c r="J30" s="39" t="n"/>
+      <c r="E30" s="42" t="inlineStr"/>
+      <c r="F30" s="43" t="n"/>
+      <c r="G30" s="43" t="n"/>
+      <c r="H30" s="43" t="n"/>
+      <c r="I30" s="43" t="n"/>
+      <c r="J30" s="43" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1"/>
     <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="41" t="inlineStr">
+      <c r="B32" s="45" t="inlineStr">
         <is>
           <t>SYSTEME MINIMAL DE TRESORERIE</t>
         </is>
       </c>
-      <c r="C32" s="42" t="n"/>
-      <c r="D32" s="42" t="n"/>
-      <c r="E32" s="42" t="n"/>
-      <c r="F32" s="42" t="n"/>
-      <c r="G32" s="42" t="n"/>
-      <c r="H32" s="42" t="n"/>
-      <c r="I32" s="42" t="n"/>
-      <c r="J32" s="42" t="n"/>
-      <c r="K32" s="42" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
+      <c r="E32" s="46" t="n"/>
+      <c r="F32" s="46" t="n"/>
+      <c r="G32" s="46" t="n"/>
+      <c r="H32" s="46" t="n"/>
+      <c r="I32" s="46" t="n"/>
+      <c r="J32" s="46" t="n"/>
+      <c r="K32" s="46" t="n"/>
     </row>
     <row r="33" ht="14" customHeight="1"/>
     <row r="34">
-      <c r="B34" s="43" t="inlineStr">
+      <c r="B34" s="47" t="inlineStr">
         <is>
           <t>Documents déposés</t>
         </is>
       </c>
-      <c r="H34" s="43" t="inlineStr">
+      <c r="H34" s="47" t="inlineStr">
         <is>
           <t>Réservé à l'administration</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="44" t="inlineStr">
+      <c r="B35" s="48" t="inlineStr">
         <is>
           <t>Fiche d'identification et renseignements divers</t>
         </is>
       </c>
-      <c r="C35" s="45" t="n"/>
-      <c r="D35" s="45" t="n"/>
-      <c r="E35" s="45" t="n"/>
-      <c r="F35" s="46" t="inlineStr">
+      <c r="C35" s="49" t="n"/>
+      <c r="D35" s="49" t="n"/>
+      <c r="E35" s="49" t="n"/>
+      <c r="F35" s="50" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H35" s="47" t="inlineStr">
+      <c r="H35" s="51" t="inlineStr">
         <is>
           <t>Date de dépôt</t>
         </is>
       </c>
-      <c r="I35" s="45" t="n"/>
-      <c r="J35" s="45" t="n"/>
-      <c r="K35" s="45" t="n"/>
+      <c r="I35" s="49" t="n"/>
+      <c r="J35" s="49" t="n"/>
+      <c r="K35" s="49" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="44" t="inlineStr">
+      <c r="B36" s="48" t="inlineStr">
         <is>
           <t>Bilan (actif et passif)</t>
         </is>
       </c>
-      <c r="C36" s="45" t="n"/>
-      <c r="D36" s="45" t="n"/>
-      <c r="E36" s="45" t="n"/>
-      <c r="F36" s="46" t="inlineStr">
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+      <c r="E36" s="49" t="n"/>
+      <c r="F36" s="50" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H36" s="45" t="n"/>
-      <c r="I36" s="45" t="n"/>
-      <c r="J36" s="45" t="n"/>
-      <c r="K36" s="45" t="n"/>
+      <c r="H36" s="49" t="n"/>
+      <c r="I36" s="49" t="n"/>
+      <c r="J36" s="49" t="n"/>
+      <c r="K36" s="49" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="44" t="inlineStr">
+      <c r="B37" s="48" t="inlineStr">
         <is>
           <t>Compte de résultat</t>
         </is>
       </c>
-      <c r="C37" s="45" t="n"/>
-      <c r="D37" s="45" t="n"/>
-      <c r="E37" s="45" t="n"/>
-      <c r="F37" s="46" t="inlineStr">
+      <c r="C37" s="49" t="n"/>
+      <c r="D37" s="49" t="n"/>
+      <c r="E37" s="49" t="n"/>
+      <c r="F37" s="50" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H37" s="45" t="n"/>
-      <c r="I37" s="45" t="n"/>
-      <c r="J37" s="45" t="n"/>
-      <c r="K37" s="45" t="n"/>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="49" t="n"/>
+      <c r="J37" s="49" t="n"/>
+      <c r="K37" s="49" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="44" t="inlineStr">
+      <c r="B38" s="48" t="inlineStr">
         <is>
           <t>Notes annexes 1 à 4</t>
         </is>
       </c>
-      <c r="C38" s="45" t="n"/>
-      <c r="D38" s="45" t="n"/>
-      <c r="E38" s="45" t="n"/>
-      <c r="F38" s="46" t="inlineStr">
+      <c r="C38" s="49" t="n"/>
+      <c r="D38" s="49" t="n"/>
+      <c r="E38" s="49" t="n"/>
+      <c r="F38" s="50" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H38" s="45" t="n"/>
-      <c r="I38" s="45" t="n"/>
-      <c r="J38" s="45" t="n"/>
-      <c r="K38" s="45" t="n"/>
+      <c r="H38" s="49" t="n"/>
+      <c r="I38" s="49" t="n"/>
+      <c r="J38" s="49" t="n"/>
+      <c r="K38" s="49" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="44" t="inlineStr">
+      <c r="B39" s="48" t="inlineStr">
         <is>
           <t>Journaux de suivi (créances impayées, dettes à payer)</t>
         </is>
       </c>
-      <c r="C39" s="45" t="n"/>
-      <c r="D39" s="45" t="n"/>
-      <c r="E39" s="45" t="n"/>
-      <c r="F39" s="46" t="inlineStr">
+      <c r="C39" s="49" t="n"/>
+      <c r="D39" s="49" t="n"/>
+      <c r="E39" s="49" t="n"/>
+      <c r="F39" s="50" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H39" s="47" t="inlineStr">
+      <c r="H39" s="51" t="inlineStr">
         <is>
           <t>Nom de l'agent ayant réceptionné le dépôt</t>
         </is>
       </c>
-      <c r="I39" s="45" t="n"/>
-      <c r="J39" s="45" t="n"/>
-      <c r="K39" s="45" t="n"/>
+      <c r="I39" s="49" t="n"/>
+      <c r="J39" s="49" t="n"/>
+      <c r="K39" s="49" t="n"/>
     </row>
     <row r="40">
-      <c r="H40" s="45" t="n"/>
-      <c r="I40" s="45" t="n"/>
-      <c r="J40" s="45" t="n"/>
-      <c r="K40" s="45" t="n"/>
+      <c r="H40" s="49" t="n"/>
+      <c r="I40" s="49" t="n"/>
+      <c r="J40" s="49" t="n"/>
+      <c r="K40" s="49" t="n"/>
     </row>
     <row r="41">
-      <c r="H41" s="45" t="n"/>
-      <c r="I41" s="45" t="n"/>
-      <c r="J41" s="45" t="n"/>
-      <c r="K41" s="45" t="n"/>
+      <c r="H41" s="49" t="n"/>
+      <c r="I41" s="49" t="n"/>
+      <c r="J41" s="49" t="n"/>
+      <c r="K41" s="49" t="n"/>
     </row>
     <row r="42">
-      <c r="H42" s="45" t="n"/>
-      <c r="I42" s="45" t="n"/>
-      <c r="J42" s="45" t="n"/>
-      <c r="K42" s="45" t="n"/>
+      <c r="H42" s="49" t="n"/>
+      <c r="I42" s="49" t="n"/>
+      <c r="J42" s="49" t="n"/>
+      <c r="K42" s="49" t="n"/>
     </row>
     <row r="43">
-      <c r="H43" s="47" t="inlineStr">
+      <c r="H43" s="51" t="inlineStr">
         <is>
           <t>Signature de l'agent et cachet du service</t>
         </is>
       </c>
-      <c r="I43" s="45" t="n"/>
-      <c r="J43" s="45" t="n"/>
-      <c r="K43" s="45" t="n"/>
+      <c r="I43" s="49" t="n"/>
+      <c r="J43" s="49" t="n"/>
+      <c r="K43" s="49" t="n"/>
     </row>
     <row r="44">
-      <c r="H44" s="45" t="n"/>
-      <c r="I44" s="45" t="n"/>
-      <c r="J44" s="45" t="n"/>
-      <c r="K44" s="45" t="n"/>
+      <c r="H44" s="49" t="n"/>
+      <c r="I44" s="49" t="n"/>
+      <c r="J44" s="49" t="n"/>
+      <c r="K44" s="49" t="n"/>
     </row>
     <row r="45">
-      <c r="H45" s="45" t="n"/>
-      <c r="I45" s="45" t="n"/>
-      <c r="J45" s="45" t="n"/>
-      <c r="K45" s="45" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
+      <c r="J45" s="49" t="n"/>
+      <c r="K45" s="49" t="n"/>
     </row>
     <row r="46">
-      <c r="H46" s="45" t="n"/>
-      <c r="I46" s="45" t="n"/>
-      <c r="J46" s="45" t="n"/>
-      <c r="K46" s="45" t="n"/>
+      <c r="H46" s="49" t="n"/>
+      <c r="I46" s="49" t="n"/>
+      <c r="J46" s="49" t="n"/>
+      <c r="K46" s="49" t="n"/>
     </row>
     <row r="47"/>
     <row r="48">
-      <c r="B48" s="44" t="inlineStr">
+      <c r="B48" s="48" t="inlineStr">
         <is>
           <t>Nombre de pages déposées par exemplaire :</t>
         </is>
       </c>
-      <c r="C48" s="45" t="n"/>
-      <c r="D48" s="45" t="n"/>
-      <c r="E48" s="45" t="n"/>
-      <c r="F48" s="45" t="n"/>
+      <c r="C48" s="49" t="n"/>
+      <c r="D48" s="49" t="n"/>
+      <c r="E48" s="49" t="n"/>
+      <c r="F48" s="49" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="44" t="inlineStr">
+      <c r="B49" s="48" t="inlineStr">
         <is>
           <t>Nombre d'exemplaires déposés :</t>
         </is>
       </c>
-      <c r="C49" s="45" t="n"/>
-      <c r="D49" s="45" t="n"/>
-      <c r="E49" s="45" t="n"/>
-      <c r="F49" s="45" t="n"/>
+      <c r="C49" s="49" t="n"/>
+      <c r="D49" s="49" t="n"/>
+      <c r="E49" s="49" t="n"/>
+      <c r="F49" s="49" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -5647,79 +5571,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 1 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="I2" s="49" t="inlineStr">
+      <c r="I2" s="53" t="inlineStr">
         <is>
           <t>FICHE 1</t>
         </is>
       </c>
-      <c r="J2" s="50" t="n"/>
+      <c r="J2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="C4" s="39" t="n"/>
-      <c r="D4" s="39" t="n"/>
-      <c r="E4" s="39" t="n"/>
-      <c r="F4" s="39" t="n"/>
-      <c r="G4" s="39" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="43" t="n"/>
+      <c r="I4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr"/>
+      <c r="J4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="G5" s="37" t="inlineStr">
+      <c r="G5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="I5" s="37" t="inlineStr">
+      <c r="I5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="53" t="inlineStr">
+      <c r="A7" s="57" t="inlineStr">
         <is>
           <t>FICHE D'IDENTIFICATION ET RENSEIGNEMENTS DIVERS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="54" t="inlineStr">
+      <c r="A8" s="58" t="inlineStr">
         <is>
           <t>SYSCOHADA révisé - Système minimal de trésorerie</t>
         </is>
@@ -5727,483 +5651,483 @@
     </row>
     <row r="9"/>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>ZA</t>
         </is>
       </c>
-      <c r="B10" s="56" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>EXERCICE COMPTABLE</t>
         </is>
       </c>
-      <c r="C10" s="57" t="n"/>
-      <c r="D10" s="57" t="n"/>
-      <c r="E10" s="57" t="n"/>
-      <c r="F10" s="57" t="n"/>
-      <c r="G10" s="58" t="inlineStr">
+      <c r="C10" s="61" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="61" t="n"/>
+      <c r="F10" s="61" t="n"/>
+      <c r="G10" s="62" t="inlineStr">
         <is>
           <t>DU : 01-01-2025    AU : 31-12-2025</t>
         </is>
       </c>
-      <c r="H10" s="57" t="n"/>
-      <c r="I10" s="57" t="n"/>
-      <c r="J10" s="57" t="n"/>
+      <c r="H10" s="61" t="n"/>
+      <c r="I10" s="61" t="n"/>
+      <c r="J10" s="61" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="55" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>ZB</t>
         </is>
       </c>
-      <c r="B11" s="56" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>DATE D'ARRETE EFFECTIF DES COMPTES</t>
         </is>
       </c>
-      <c r="C11" s="57" t="n"/>
-      <c r="D11" s="57" t="n"/>
-      <c r="E11" s="57" t="n"/>
-      <c r="F11" s="57" t="n"/>
-      <c r="G11" s="58" t="inlineStr"/>
-      <c r="H11" s="57" t="n"/>
-      <c r="I11" s="57" t="n"/>
-      <c r="J11" s="57" t="n"/>
+      <c r="C11" s="61" t="n"/>
+      <c r="D11" s="61" t="n"/>
+      <c r="E11" s="61" t="n"/>
+      <c r="F11" s="61" t="n"/>
+      <c r="G11" s="62" t="inlineStr"/>
+      <c r="H11" s="61" t="n"/>
+      <c r="I11" s="61" t="n"/>
+      <c r="J11" s="61" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>ZC</t>
         </is>
       </c>
-      <c r="B12" s="56" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>EXERCICE PRECEDENT CLOS LE</t>
         </is>
       </c>
-      <c r="C12" s="57" t="n"/>
-      <c r="D12" s="57" t="n"/>
-      <c r="E12" s="57" t="n"/>
-      <c r="F12" s="57" t="n"/>
-      <c r="G12" s="58" t="inlineStr"/>
-      <c r="H12" s="57" t="n"/>
-      <c r="I12" s="57" t="n"/>
-      <c r="J12" s="57" t="n"/>
+      <c r="C12" s="61" t="n"/>
+      <c r="D12" s="61" t="n"/>
+      <c r="E12" s="61" t="n"/>
+      <c r="F12" s="61" t="n"/>
+      <c r="G12" s="62" t="inlineStr"/>
+      <c r="H12" s="61" t="n"/>
+      <c r="I12" s="61" t="n"/>
+      <c r="J12" s="61" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>ZD</t>
         </is>
       </c>
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>DUREE DE L'EXERCICE PRECEDENT (EN MOIS)</t>
         </is>
       </c>
-      <c r="C13" s="57" t="n"/>
-      <c r="D13" s="57" t="n"/>
-      <c r="E13" s="57" t="n"/>
-      <c r="F13" s="57" t="n"/>
-      <c r="G13" s="58" t="inlineStr"/>
-      <c r="H13" s="57" t="n"/>
-      <c r="I13" s="57" t="n"/>
-      <c r="J13" s="57" t="n"/>
+      <c r="C13" s="61" t="n"/>
+      <c r="D13" s="61" t="n"/>
+      <c r="E13" s="61" t="n"/>
+      <c r="F13" s="61" t="n"/>
+      <c r="G13" s="62" t="inlineStr"/>
+      <c r="H13" s="61" t="n"/>
+      <c r="I13" s="61" t="n"/>
+      <c r="J13" s="61" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="55" t="inlineStr">
+      <c r="A14" s="59" t="inlineStr">
         <is>
           <t>ZE</t>
         </is>
       </c>
-      <c r="B14" s="56" t="inlineStr">
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>N° REGISTRE (RCCM, F92, CONVENTION...) ET GREFFE</t>
         </is>
       </c>
-      <c r="C14" s="57" t="n"/>
-      <c r="D14" s="57" t="n"/>
-      <c r="E14" s="57" t="n"/>
-      <c r="F14" s="57" t="n"/>
-      <c r="G14" s="58" t="inlineStr"/>
-      <c r="H14" s="57" t="n"/>
-      <c r="I14" s="57" t="n"/>
-      <c r="J14" s="57" t="n"/>
+      <c r="C14" s="61" t="n"/>
+      <c r="D14" s="61" t="n"/>
+      <c r="E14" s="61" t="n"/>
+      <c r="F14" s="61" t="n"/>
+      <c r="G14" s="62" t="inlineStr"/>
+      <c r="H14" s="61" t="n"/>
+      <c r="I14" s="61" t="n"/>
+      <c r="J14" s="61" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>ZF</t>
         </is>
       </c>
-      <c r="B15" s="56" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>N° REPERTOIRE DES ENTITES</t>
         </is>
       </c>
-      <c r="C15" s="57" t="n"/>
-      <c r="D15" s="57" t="n"/>
-      <c r="E15" s="57" t="n"/>
-      <c r="F15" s="57" t="n"/>
-      <c r="G15" s="58" t="inlineStr"/>
-      <c r="H15" s="57" t="n"/>
-      <c r="I15" s="57" t="n"/>
-      <c r="J15" s="57" t="n"/>
+      <c r="C15" s="61" t="n"/>
+      <c r="D15" s="61" t="n"/>
+      <c r="E15" s="61" t="n"/>
+      <c r="F15" s="61" t="n"/>
+      <c r="G15" s="62" t="inlineStr"/>
+      <c r="H15" s="61" t="n"/>
+      <c r="I15" s="61" t="n"/>
+      <c r="J15" s="61" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="55" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>ZG</t>
         </is>
       </c>
-      <c r="B16" s="56" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>N° DE CAISSE SOCIALE</t>
         </is>
       </c>
-      <c r="C16" s="57" t="n"/>
-      <c r="D16" s="57" t="n"/>
-      <c r="E16" s="57" t="n"/>
-      <c r="F16" s="57" t="n"/>
-      <c r="G16" s="58" t="inlineStr"/>
-      <c r="H16" s="57" t="n"/>
-      <c r="I16" s="57" t="n"/>
-      <c r="J16" s="57" t="n"/>
+      <c r="C16" s="61" t="n"/>
+      <c r="D16" s="61" t="n"/>
+      <c r="E16" s="61" t="n"/>
+      <c r="F16" s="61" t="n"/>
+      <c r="G16" s="62" t="inlineStr"/>
+      <c r="H16" s="61" t="n"/>
+      <c r="I16" s="61" t="n"/>
+      <c r="J16" s="61" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="55" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>ZH</t>
         </is>
       </c>
-      <c r="B17" s="56" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>N° CODE IMPORTATEUR</t>
         </is>
       </c>
-      <c r="C17" s="57" t="n"/>
-      <c r="D17" s="57" t="n"/>
-      <c r="E17" s="57" t="n"/>
-      <c r="F17" s="57" t="n"/>
-      <c r="G17" s="58" t="inlineStr"/>
-      <c r="H17" s="57" t="n"/>
-      <c r="I17" s="57" t="n"/>
-      <c r="J17" s="57" t="n"/>
+      <c r="C17" s="61" t="n"/>
+      <c r="D17" s="61" t="n"/>
+      <c r="E17" s="61" t="n"/>
+      <c r="F17" s="61" t="n"/>
+      <c r="G17" s="62" t="inlineStr"/>
+      <c r="H17" s="61" t="n"/>
+      <c r="I17" s="61" t="n"/>
+      <c r="J17" s="61" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="55" t="inlineStr">
+      <c r="A18" s="59" t="inlineStr">
         <is>
           <t>ZI</t>
         </is>
       </c>
-      <c r="B18" s="56" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>CODE ACTIVITE PRINCIPALE</t>
         </is>
       </c>
-      <c r="C18" s="57" t="n"/>
-      <c r="D18" s="57" t="n"/>
-      <c r="E18" s="57" t="n"/>
-      <c r="F18" s="57" t="n"/>
-      <c r="G18" s="58" t="inlineStr"/>
-      <c r="H18" s="57" t="n"/>
-      <c r="I18" s="57" t="n"/>
-      <c r="J18" s="57" t="n"/>
+      <c r="C18" s="61" t="n"/>
+      <c r="D18" s="61" t="n"/>
+      <c r="E18" s="61" t="n"/>
+      <c r="F18" s="61" t="n"/>
+      <c r="G18" s="62" t="inlineStr"/>
+      <c r="H18" s="61" t="n"/>
+      <c r="I18" s="61" t="n"/>
+      <c r="J18" s="61" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="55" t="inlineStr">
+      <c r="A19" s="59" t="inlineStr">
         <is>
           <t>ZJ</t>
         </is>
       </c>
-      <c r="B19" s="56" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>DESIGNATION DE L'ENTITE ET SIGLE</t>
         </is>
       </c>
-      <c r="C19" s="57" t="n"/>
-      <c r="D19" s="57" t="n"/>
-      <c r="E19" s="57" t="n"/>
-      <c r="F19" s="57" t="n"/>
-      <c r="G19" s="58" t="inlineStr">
+      <c r="C19" s="61" t="n"/>
+      <c r="D19" s="61" t="n"/>
+      <c r="E19" s="61" t="n"/>
+      <c r="F19" s="61" t="n"/>
+      <c r="G19" s="62" t="inlineStr">
         <is>
           <t>ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
-      <c r="H19" s="57" t="n"/>
-      <c r="I19" s="57" t="n"/>
-      <c r="J19" s="57" t="n"/>
+      <c r="H19" s="61" t="n"/>
+      <c r="I19" s="61" t="n"/>
+      <c r="J19" s="61" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="A20" s="59" t="inlineStr">
         <is>
           <t>ZK</t>
         </is>
       </c>
-      <c r="B20" s="56" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>N° DE TELEPHONE, ADRESSE E-MAIL, BOITE POSTALE, VILLE</t>
         </is>
       </c>
-      <c r="C20" s="57" t="n"/>
-      <c r="D20" s="57" t="n"/>
-      <c r="E20" s="57" t="n"/>
-      <c r="F20" s="57" t="n"/>
-      <c r="G20" s="58" t="inlineStr"/>
-      <c r="H20" s="57" t="n"/>
-      <c r="I20" s="57" t="n"/>
-      <c r="J20" s="57" t="n"/>
+      <c r="C20" s="61" t="n"/>
+      <c r="D20" s="61" t="n"/>
+      <c r="E20" s="61" t="n"/>
+      <c r="F20" s="61" t="n"/>
+      <c r="G20" s="62" t="inlineStr"/>
+      <c r="H20" s="61" t="n"/>
+      <c r="I20" s="61" t="n"/>
+      <c r="J20" s="61" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="55" t="inlineStr">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>ZL</t>
         </is>
       </c>
-      <c r="B21" s="56" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>ADRESSE GEOGRAPHIQUE COMPLETE (IMMEUBLE, RUE, QUARTIER, VILLE, PAYS)</t>
         </is>
       </c>
-      <c r="C21" s="57" t="n"/>
-      <c r="D21" s="57" t="n"/>
-      <c r="E21" s="57" t="n"/>
-      <c r="F21" s="57" t="n"/>
-      <c r="G21" s="58" t="inlineStr"/>
-      <c r="H21" s="57" t="n"/>
-      <c r="I21" s="57" t="n"/>
-      <c r="J21" s="57" t="n"/>
+      <c r="C21" s="61" t="n"/>
+      <c r="D21" s="61" t="n"/>
+      <c r="E21" s="61" t="n"/>
+      <c r="F21" s="61" t="n"/>
+      <c r="G21" s="62" t="inlineStr"/>
+      <c r="H21" s="61" t="n"/>
+      <c r="I21" s="61" t="n"/>
+      <c r="J21" s="61" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="A22" s="59" t="inlineStr">
         <is>
           <t>ZM</t>
         </is>
       </c>
-      <c r="B22" s="56" t="inlineStr">
+      <c r="B22" s="60" t="inlineStr">
         <is>
           <t>DESIGNATION PRECISE DE L'ACTIVITE PRINCIPALE EXERCEE</t>
         </is>
       </c>
-      <c r="C22" s="57" t="n"/>
-      <c r="D22" s="57" t="n"/>
-      <c r="E22" s="57" t="n"/>
-      <c r="F22" s="57" t="n"/>
-      <c r="G22" s="58" t="inlineStr"/>
-      <c r="H22" s="57" t="n"/>
-      <c r="I22" s="57" t="n"/>
-      <c r="J22" s="57" t="n"/>
+      <c r="C22" s="61" t="n"/>
+      <c r="D22" s="61" t="n"/>
+      <c r="E22" s="61" t="n"/>
+      <c r="F22" s="61" t="n"/>
+      <c r="G22" s="62" t="inlineStr"/>
+      <c r="H22" s="61" t="n"/>
+      <c r="I22" s="61" t="n"/>
+      <c r="J22" s="61" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="55" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>ZN</t>
         </is>
       </c>
-      <c r="B23" s="56" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>% DE CAPACITE DE PRODUCTION UTILE</t>
         </is>
       </c>
-      <c r="C23" s="57" t="n"/>
-      <c r="D23" s="57" t="n"/>
-      <c r="E23" s="57" t="n"/>
-      <c r="F23" s="57" t="n"/>
-      <c r="G23" s="58" t="inlineStr"/>
-      <c r="H23" s="57" t="n"/>
-      <c r="I23" s="57" t="n"/>
-      <c r="J23" s="57" t="n"/>
+      <c r="C23" s="61" t="n"/>
+      <c r="D23" s="61" t="n"/>
+      <c r="E23" s="61" t="n"/>
+      <c r="F23" s="61" t="n"/>
+      <c r="G23" s="62" t="inlineStr"/>
+      <c r="H23" s="61" t="n"/>
+      <c r="I23" s="61" t="n"/>
+      <c r="J23" s="61" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="59" t="inlineStr">
         <is>
           <t>ZO</t>
         </is>
       </c>
-      <c r="B24" s="56" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>NOM, ADRESSE, TELEPHONE, E-MAIL ET QUALITE DE LA PERSONNE A CONTACTER EN CAS DE DEMANDE</t>
         </is>
       </c>
-      <c r="C24" s="57" t="n"/>
-      <c r="D24" s="57" t="n"/>
-      <c r="E24" s="57" t="n"/>
-      <c r="F24" s="57" t="n"/>
-      <c r="G24" s="58" t="inlineStr"/>
-      <c r="H24" s="57" t="n"/>
-      <c r="I24" s="57" t="n"/>
-      <c r="J24" s="57" t="n"/>
+      <c r="C24" s="61" t="n"/>
+      <c r="D24" s="61" t="n"/>
+      <c r="E24" s="61" t="n"/>
+      <c r="F24" s="61" t="n"/>
+      <c r="G24" s="62" t="inlineStr"/>
+      <c r="H24" s="61" t="n"/>
+      <c r="I24" s="61" t="n"/>
+      <c r="J24" s="61" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="A25" s="59" t="inlineStr">
         <is>
           <t>ZP</t>
         </is>
       </c>
-      <c r="B25" s="56" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>NOM, ADRESSE, TELEPHONE ET E-MAIL DU SALARIE OU DU PROFESSIONNEL COMPTABLE AYANT ETABLI LES ETATS FINANCIERS</t>
         </is>
       </c>
-      <c r="C25" s="57" t="n"/>
-      <c r="D25" s="57" t="n"/>
-      <c r="E25" s="57" t="n"/>
-      <c r="F25" s="57" t="n"/>
-      <c r="G25" s="58" t="inlineStr"/>
-      <c r="H25" s="57" t="n"/>
-      <c r="I25" s="57" t="n"/>
-      <c r="J25" s="57" t="n"/>
+      <c r="C25" s="61" t="n"/>
+      <c r="D25" s="61" t="n"/>
+      <c r="E25" s="61" t="n"/>
+      <c r="F25" s="61" t="n"/>
+      <c r="G25" s="62" t="inlineStr"/>
+      <c r="H25" s="61" t="n"/>
+      <c r="I25" s="61" t="n"/>
+      <c r="J25" s="61" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="55" t="inlineStr">
+      <c r="A26" s="59" t="inlineStr">
         <is>
           <t>ZQ</t>
         </is>
       </c>
-      <c r="B26" s="56" t="inlineStr">
+      <c r="B26" s="60" t="inlineStr">
         <is>
           <t>NOM, ADRESSE, TELEPHONE, E-MAIL ET N° D'INSCRIPTION A L'ORDRE DE L'EXPERT-COMPTABLE AYANT DELIVRE L'ATTESTATION DE VISA</t>
         </is>
       </c>
-      <c r="C26" s="57" t="n"/>
-      <c r="D26" s="57" t="n"/>
-      <c r="E26" s="57" t="n"/>
-      <c r="F26" s="57" t="n"/>
-      <c r="G26" s="58" t="inlineStr"/>
-      <c r="H26" s="57" t="n"/>
-      <c r="I26" s="57" t="n"/>
-      <c r="J26" s="57" t="n"/>
+      <c r="C26" s="61" t="n"/>
+      <c r="D26" s="61" t="n"/>
+      <c r="E26" s="61" t="n"/>
+      <c r="F26" s="61" t="n"/>
+      <c r="G26" s="62" t="inlineStr"/>
+      <c r="H26" s="61" t="n"/>
+      <c r="I26" s="61" t="n"/>
+      <c r="J26" s="61" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="55" t="inlineStr">
+      <c r="A27" s="59" t="inlineStr">
         <is>
           <t>ZR</t>
         </is>
       </c>
-      <c r="B27" s="56" t="inlineStr">
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t>NOM, ADRESSE, TELEPHONE, E-MAIL ET N° D'INSCRIPTION DU COMMISSAIRE AUX COMPTES, LE CAS ECHEANT</t>
         </is>
       </c>
-      <c r="C27" s="57" t="n"/>
-      <c r="D27" s="57" t="n"/>
-      <c r="E27" s="57" t="n"/>
-      <c r="F27" s="57" t="n"/>
-      <c r="G27" s="58" t="inlineStr"/>
-      <c r="H27" s="57" t="n"/>
-      <c r="I27" s="57" t="n"/>
-      <c r="J27" s="57" t="n"/>
+      <c r="C27" s="61" t="n"/>
+      <c r="D27" s="61" t="n"/>
+      <c r="E27" s="61" t="n"/>
+      <c r="F27" s="61" t="n"/>
+      <c r="G27" s="62" t="inlineStr"/>
+      <c r="H27" s="61" t="n"/>
+      <c r="I27" s="61" t="n"/>
+      <c r="J27" s="61" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="55" t="inlineStr">
+      <c r="A28" s="59" t="inlineStr">
         <is>
           <t>ZS</t>
         </is>
       </c>
-      <c r="B28" s="56" t="inlineStr">
+      <c r="B28" s="60" t="inlineStr">
         <is>
           <t>ETATS FINANCIERS APPROUVES PAR L'ORGANE COMPETENT (OUI / NON)</t>
         </is>
       </c>
-      <c r="C28" s="57" t="n"/>
-      <c r="D28" s="57" t="n"/>
-      <c r="E28" s="57" t="n"/>
-      <c r="F28" s="57" t="n"/>
-      <c r="G28" s="58" t="inlineStr"/>
-      <c r="H28" s="57" t="n"/>
-      <c r="I28" s="57" t="n"/>
-      <c r="J28" s="57" t="n"/>
+      <c r="C28" s="61" t="n"/>
+      <c r="D28" s="61" t="n"/>
+      <c r="E28" s="61" t="n"/>
+      <c r="F28" s="61" t="n"/>
+      <c r="G28" s="62" t="inlineStr"/>
+      <c r="H28" s="61" t="n"/>
+      <c r="I28" s="61" t="n"/>
+      <c r="J28" s="61" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="55" t="inlineStr">
+      <c r="A29" s="59" t="inlineStr">
         <is>
           <t>ZT</t>
         </is>
       </c>
-      <c r="B29" s="56" t="inlineStr">
+      <c r="B29" s="60" t="inlineStr">
         <is>
           <t>NOM DU SIGNATAIRE DES ETATS FINANCIERS</t>
         </is>
       </c>
-      <c r="C29" s="57" t="n"/>
-      <c r="D29" s="57" t="n"/>
-      <c r="E29" s="57" t="n"/>
-      <c r="F29" s="57" t="n"/>
-      <c r="G29" s="58" t="inlineStr"/>
-      <c r="H29" s="57" t="n"/>
-      <c r="I29" s="57" t="n"/>
-      <c r="J29" s="57" t="n"/>
+      <c r="C29" s="61" t="n"/>
+      <c r="D29" s="61" t="n"/>
+      <c r="E29" s="61" t="n"/>
+      <c r="F29" s="61" t="n"/>
+      <c r="G29" s="62" t="inlineStr"/>
+      <c r="H29" s="61" t="n"/>
+      <c r="I29" s="61" t="n"/>
+      <c r="J29" s="61" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="55" t="inlineStr">
+      <c r="A30" s="59" t="inlineStr">
         <is>
           <t>ZU</t>
         </is>
       </c>
-      <c r="B30" s="56" t="inlineStr">
+      <c r="B30" s="60" t="inlineStr">
         <is>
           <t>QUALITE DU SIGNATAIRE DES ETATS FINANCIERS</t>
         </is>
       </c>
-      <c r="C30" s="57" t="n"/>
-      <c r="D30" s="57" t="n"/>
-      <c r="E30" s="57" t="n"/>
-      <c r="F30" s="57" t="n"/>
-      <c r="G30" s="58" t="inlineStr"/>
-      <c r="H30" s="57" t="n"/>
-      <c r="I30" s="57" t="n"/>
-      <c r="J30" s="57" t="n"/>
+      <c r="C30" s="61" t="n"/>
+      <c r="D30" s="61" t="n"/>
+      <c r="E30" s="61" t="n"/>
+      <c r="F30" s="61" t="n"/>
+      <c r="G30" s="62" t="inlineStr"/>
+      <c r="H30" s="61" t="n"/>
+      <c r="I30" s="61" t="n"/>
+      <c r="J30" s="61" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="55" t="inlineStr">
+      <c r="A31" s="59" t="inlineStr">
         <is>
           <t>ZV</t>
         </is>
       </c>
-      <c r="B31" s="56" t="inlineStr">
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>DATE DE SIGNATURE</t>
         </is>
       </c>
-      <c r="C31" s="57" t="n"/>
-      <c r="D31" s="57" t="n"/>
-      <c r="E31" s="57" t="n"/>
-      <c r="F31" s="57" t="n"/>
-      <c r="G31" s="58" t="inlineStr"/>
-      <c r="H31" s="57" t="n"/>
-      <c r="I31" s="57" t="n"/>
-      <c r="J31" s="57" t="n"/>
+      <c r="C31" s="61" t="n"/>
+      <c r="D31" s="61" t="n"/>
+      <c r="E31" s="61" t="n"/>
+      <c r="F31" s="61" t="n"/>
+      <c r="G31" s="62" t="inlineStr"/>
+      <c r="H31" s="61" t="n"/>
+      <c r="I31" s="61" t="n"/>
+      <c r="J31" s="61" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="55" t="inlineStr">
+      <c r="A32" s="59" t="inlineStr">
         <is>
           <t>ZW</t>
         </is>
       </c>
-      <c r="B32" s="56" t="inlineStr">
+      <c r="B32" s="60" t="inlineStr">
         <is>
           <t>DOMICILIATIONS BANCAIRES (BANQUE ET NUMERO DE COMPTE)</t>
         </is>
       </c>
-      <c r="C32" s="57" t="n"/>
-      <c r="D32" s="57" t="n"/>
-      <c r="E32" s="57" t="n"/>
-      <c r="F32" s="57" t="n"/>
-      <c r="G32" s="58" t="inlineStr"/>
-      <c r="H32" s="57" t="n"/>
-      <c r="I32" s="57" t="n"/>
-      <c r="J32" s="57" t="n"/>
+      <c r="C32" s="61" t="n"/>
+      <c r="D32" s="61" t="n"/>
+      <c r="E32" s="61" t="n"/>
+      <c r="F32" s="61" t="n"/>
+      <c r="G32" s="62" t="inlineStr"/>
+      <c r="H32" s="61" t="n"/>
+      <c r="I32" s="61" t="n"/>
+      <c r="J32" s="61" t="n"/>
     </row>
     <row r="33"/>
     <row r="34">
-      <c r="B34" s="59" t="inlineStr">
+      <c r="B34" s="63" t="inlineStr">
         <is>
           <t>Signature</t>
         </is>
       </c>
-      <c r="C34" s="60" t="n"/>
-      <c r="D34" s="60" t="n"/>
-      <c r="E34" s="60" t="n"/>
+      <c r="C34" s="64" t="n"/>
+      <c r="D34" s="64" t="n"/>
+      <c r="E34" s="64" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="51">
@@ -6285,79 +6209,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 2 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="I2" s="49" t="inlineStr">
+      <c r="I2" s="53" t="inlineStr">
         <is>
           <t>FICHE 2</t>
         </is>
       </c>
-      <c r="J2" s="50" t="n"/>
+      <c r="J2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="C4" s="39" t="n"/>
-      <c r="D4" s="39" t="n"/>
-      <c r="E4" s="39" t="n"/>
-      <c r="F4" s="39" t="n"/>
-      <c r="G4" s="39" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="43" t="n"/>
+      <c r="I4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr"/>
+      <c r="J4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="G5" s="37" t="inlineStr">
+      <c r="G5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="I5" s="37" t="inlineStr">
+      <c r="I5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="65" t="inlineStr">
         <is>
           <t>FICHE D'IDENTIFICATION ET RENSEIGNEMENTS DIVERS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="66" t="inlineStr">
         <is>
           <t>DIRIGEANTS ET RESPONSABLES DE L'ENTITE</t>
         </is>
@@ -6401,248 +6325,248 @@
       <c r="J10" s="3" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="45" t="n"/>
-      <c r="B11" s="45" t="n"/>
-      <c r="C11" s="45" t="n"/>
-      <c r="D11" s="45" t="n"/>
-      <c r="E11" s="45" t="n"/>
-      <c r="F11" s="45" t="n"/>
-      <c r="G11" s="45" t="n"/>
-      <c r="H11" s="45" t="n"/>
-      <c r="I11" s="45" t="n"/>
-      <c r="J11" s="45" t="n"/>
+      <c r="A11" s="49" t="n"/>
+      <c r="B11" s="49" t="n"/>
+      <c r="C11" s="49" t="n"/>
+      <c r="D11" s="49" t="n"/>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="49" t="n"/>
+      <c r="I11" s="49" t="n"/>
+      <c r="J11" s="49" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="45" t="n"/>
-      <c r="B12" s="45" t="n"/>
-      <c r="C12" s="45" t="n"/>
-      <c r="D12" s="45" t="n"/>
-      <c r="E12" s="45" t="n"/>
-      <c r="F12" s="45" t="n"/>
-      <c r="G12" s="45" t="n"/>
-      <c r="H12" s="45" t="n"/>
-      <c r="I12" s="45" t="n"/>
-      <c r="J12" s="45" t="n"/>
+      <c r="A12" s="49" t="n"/>
+      <c r="B12" s="49" t="n"/>
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="49" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="49" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="45" t="n"/>
-      <c r="B13" s="45" t="n"/>
-      <c r="C13" s="45" t="n"/>
-      <c r="D13" s="45" t="n"/>
-      <c r="E13" s="45" t="n"/>
-      <c r="F13" s="45" t="n"/>
-      <c r="G13" s="45" t="n"/>
-      <c r="H13" s="45" t="n"/>
-      <c r="I13" s="45" t="n"/>
-      <c r="J13" s="45" t="n"/>
+      <c r="A13" s="49" t="n"/>
+      <c r="B13" s="49" t="n"/>
+      <c r="C13" s="49" t="n"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="49" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="49" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="45" t="n"/>
-      <c r="B14" s="45" t="n"/>
-      <c r="C14" s="45" t="n"/>
-      <c r="D14" s="45" t="n"/>
-      <c r="E14" s="45" t="n"/>
-      <c r="F14" s="45" t="n"/>
-      <c r="G14" s="45" t="n"/>
-      <c r="H14" s="45" t="n"/>
-      <c r="I14" s="45" t="n"/>
-      <c r="J14" s="45" t="n"/>
+      <c r="A14" s="49" t="n"/>
+      <c r="B14" s="49" t="n"/>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="49" t="n"/>
+      <c r="F14" s="49" t="n"/>
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="49" t="n"/>
+      <c r="I14" s="49" t="n"/>
+      <c r="J14" s="49" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="45" t="n"/>
-      <c r="B15" s="45" t="n"/>
-      <c r="C15" s="45" t="n"/>
-      <c r="D15" s="45" t="n"/>
-      <c r="E15" s="45" t="n"/>
-      <c r="F15" s="45" t="n"/>
-      <c r="G15" s="45" t="n"/>
-      <c r="H15" s="45" t="n"/>
-      <c r="I15" s="45" t="n"/>
-      <c r="J15" s="45" t="n"/>
+      <c r="A15" s="49" t="n"/>
+      <c r="B15" s="49" t="n"/>
+      <c r="C15" s="49" t="n"/>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="49" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="49" t="n"/>
+      <c r="I15" s="49" t="n"/>
+      <c r="J15" s="49" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="45" t="n"/>
-      <c r="B16" s="45" t="n"/>
-      <c r="C16" s="45" t="n"/>
-      <c r="D16" s="45" t="n"/>
-      <c r="E16" s="45" t="n"/>
-      <c r="F16" s="45" t="n"/>
-      <c r="G16" s="45" t="n"/>
-      <c r="H16" s="45" t="n"/>
-      <c r="I16" s="45" t="n"/>
-      <c r="J16" s="45" t="n"/>
+      <c r="A16" s="49" t="n"/>
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="49" t="n"/>
+      <c r="I16" s="49" t="n"/>
+      <c r="J16" s="49" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="45" t="n"/>
-      <c r="B17" s="45" t="n"/>
-      <c r="C17" s="45" t="n"/>
-      <c r="D17" s="45" t="n"/>
-      <c r="E17" s="45" t="n"/>
-      <c r="F17" s="45" t="n"/>
-      <c r="G17" s="45" t="n"/>
-      <c r="H17" s="45" t="n"/>
-      <c r="I17" s="45" t="n"/>
-      <c r="J17" s="45" t="n"/>
+      <c r="A17" s="49" t="n"/>
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="49" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="49" t="n"/>
+      <c r="H17" s="49" t="n"/>
+      <c r="I17" s="49" t="n"/>
+      <c r="J17" s="49" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="45" t="n"/>
-      <c r="B18" s="45" t="n"/>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
-      <c r="G18" s="45" t="n"/>
-      <c r="H18" s="45" t="n"/>
-      <c r="I18" s="45" t="n"/>
-      <c r="J18" s="45" t="n"/>
+      <c r="A18" s="49" t="n"/>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="49" t="n"/>
+      <c r="I18" s="49" t="n"/>
+      <c r="J18" s="49" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="45" t="n"/>
-      <c r="B19" s="45" t="n"/>
-      <c r="C19" s="45" t="n"/>
-      <c r="D19" s="45" t="n"/>
-      <c r="E19" s="45" t="n"/>
-      <c r="F19" s="45" t="n"/>
-      <c r="G19" s="45" t="n"/>
-      <c r="H19" s="45" t="n"/>
-      <c r="I19" s="45" t="n"/>
-      <c r="J19" s="45" t="n"/>
+      <c r="A19" s="49" t="n"/>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="49" t="n"/>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="49" t="n"/>
+      <c r="J19" s="49" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="45" t="n"/>
-      <c r="B20" s="45" t="n"/>
-      <c r="C20" s="45" t="n"/>
-      <c r="D20" s="45" t="n"/>
-      <c r="E20" s="45" t="n"/>
-      <c r="F20" s="45" t="n"/>
-      <c r="G20" s="45" t="n"/>
-      <c r="H20" s="45" t="n"/>
-      <c r="I20" s="45" t="n"/>
-      <c r="J20" s="45" t="n"/>
+      <c r="A20" s="49" t="n"/>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="49" t="n"/>
+      <c r="I20" s="49" t="n"/>
+      <c r="J20" s="49" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="45" t="n"/>
-      <c r="B21" s="45" t="n"/>
-      <c r="C21" s="45" t="n"/>
-      <c r="D21" s="45" t="n"/>
-      <c r="E21" s="45" t="n"/>
-      <c r="F21" s="45" t="n"/>
-      <c r="G21" s="45" t="n"/>
-      <c r="H21" s="45" t="n"/>
-      <c r="I21" s="45" t="n"/>
-      <c r="J21" s="45" t="n"/>
+      <c r="A21" s="49" t="n"/>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="49" t="n"/>
+      <c r="I21" s="49" t="n"/>
+      <c r="J21" s="49" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="45" t="n"/>
-      <c r="B22" s="45" t="n"/>
-      <c r="C22" s="45" t="n"/>
-      <c r="D22" s="45" t="n"/>
-      <c r="E22" s="45" t="n"/>
-      <c r="F22" s="45" t="n"/>
-      <c r="G22" s="45" t="n"/>
-      <c r="H22" s="45" t="n"/>
-      <c r="I22" s="45" t="n"/>
-      <c r="J22" s="45" t="n"/>
+      <c r="A22" s="49" t="n"/>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="49" t="n"/>
+      <c r="J22" s="49" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="45" t="n"/>
-      <c r="B23" s="45" t="n"/>
-      <c r="C23" s="45" t="n"/>
-      <c r="D23" s="45" t="n"/>
-      <c r="E23" s="45" t="n"/>
-      <c r="F23" s="45" t="n"/>
-      <c r="G23" s="45" t="n"/>
-      <c r="H23" s="45" t="n"/>
-      <c r="I23" s="45" t="n"/>
-      <c r="J23" s="45" t="n"/>
+      <c r="A23" s="49" t="n"/>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="49" t="n"/>
+      <c r="J23" s="49" t="n"/>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="45" t="n"/>
-      <c r="B24" s="45" t="n"/>
-      <c r="C24" s="45" t="n"/>
-      <c r="D24" s="45" t="n"/>
-      <c r="E24" s="45" t="n"/>
-      <c r="F24" s="45" t="n"/>
-      <c r="G24" s="45" t="n"/>
-      <c r="H24" s="45" t="n"/>
-      <c r="I24" s="45" t="n"/>
-      <c r="J24" s="45" t="n"/>
+      <c r="A24" s="49" t="n"/>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="49" t="n"/>
+      <c r="I24" s="49" t="n"/>
+      <c r="J24" s="49" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="45" t="n"/>
-      <c r="B25" s="45" t="n"/>
-      <c r="C25" s="45" t="n"/>
-      <c r="D25" s="45" t="n"/>
-      <c r="E25" s="45" t="n"/>
-      <c r="F25" s="45" t="n"/>
-      <c r="G25" s="45" t="n"/>
-      <c r="H25" s="45" t="n"/>
-      <c r="I25" s="45" t="n"/>
-      <c r="J25" s="45" t="n"/>
+      <c r="A25" s="49" t="n"/>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="49" t="n"/>
+      <c r="J25" s="49" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="45" t="n"/>
-      <c r="B26" s="45" t="n"/>
-      <c r="C26" s="45" t="n"/>
-      <c r="D26" s="45" t="n"/>
-      <c r="E26" s="45" t="n"/>
-      <c r="F26" s="45" t="n"/>
-      <c r="G26" s="45" t="n"/>
-      <c r="H26" s="45" t="n"/>
-      <c r="I26" s="45" t="n"/>
-      <c r="J26" s="45" t="n"/>
+      <c r="A26" s="49" t="n"/>
+      <c r="B26" s="49" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="49" t="n"/>
+      <c r="I26" s="49" t="n"/>
+      <c r="J26" s="49" t="n"/>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="45" t="n"/>
-      <c r="B27" s="45" t="n"/>
-      <c r="C27" s="45" t="n"/>
-      <c r="D27" s="45" t="n"/>
-      <c r="E27" s="45" t="n"/>
-      <c r="F27" s="45" t="n"/>
-      <c r="G27" s="45" t="n"/>
-      <c r="H27" s="45" t="n"/>
-      <c r="I27" s="45" t="n"/>
-      <c r="J27" s="45" t="n"/>
+      <c r="A27" s="49" t="n"/>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="49" t="n"/>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="49" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="49" t="n"/>
+      <c r="J27" s="49" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="45" t="n"/>
-      <c r="B28" s="45" t="n"/>
-      <c r="C28" s="45" t="n"/>
-      <c r="D28" s="45" t="n"/>
-      <c r="E28" s="45" t="n"/>
-      <c r="F28" s="45" t="n"/>
-      <c r="G28" s="45" t="n"/>
-      <c r="H28" s="45" t="n"/>
-      <c r="I28" s="45" t="n"/>
-      <c r="J28" s="45" t="n"/>
+      <c r="A28" s="49" t="n"/>
+      <c r="B28" s="49" t="n"/>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+      <c r="E28" s="49" t="n"/>
+      <c r="F28" s="49" t="n"/>
+      <c r="G28" s="49" t="n"/>
+      <c r="H28" s="49" t="n"/>
+      <c r="I28" s="49" t="n"/>
+      <c r="J28" s="49" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="45" t="n"/>
-      <c r="B29" s="45" t="n"/>
-      <c r="C29" s="45" t="n"/>
-      <c r="D29" s="45" t="n"/>
-      <c r="E29" s="45" t="n"/>
-      <c r="F29" s="45" t="n"/>
-      <c r="G29" s="45" t="n"/>
-      <c r="H29" s="45" t="n"/>
-      <c r="I29" s="45" t="n"/>
-      <c r="J29" s="45" t="n"/>
+      <c r="A29" s="49" t="n"/>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="49" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="49" t="n"/>
+      <c r="J29" s="49" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="45" t="n"/>
-      <c r="B30" s="45" t="n"/>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
-      <c r="G30" s="45" t="n"/>
-      <c r="H30" s="45" t="n"/>
-      <c r="I30" s="45" t="n"/>
-      <c r="J30" s="45" t="n"/>
+      <c r="A30" s="49" t="n"/>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="49" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="49" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="49" t="n"/>
+      <c r="J30" s="49" t="n"/>
     </row>
     <row r="31"/>
     <row r="32">
-      <c r="A32" s="63" t="inlineStr">
+      <c r="A32" s="67" t="inlineStr">
         <is>
           <t>(2) Mentionner les autres nationalités le cas échéant.</t>
         </is>
@@ -6744,367 +6668,367 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 3 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="I2" s="49" t="inlineStr">
+      <c r="I2" s="53" t="inlineStr">
         <is>
           <t>BILAN SYSCOHADA - SMT
 PAGE 1/1</t>
         </is>
       </c>
-      <c r="J2" s="50" t="n"/>
+      <c r="J2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="C4" s="39" t="n"/>
-      <c r="D4" s="39" t="n"/>
-      <c r="E4" s="39" t="n"/>
-      <c r="F4" s="39" t="n"/>
-      <c r="G4" s="39" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="43" t="n"/>
+      <c r="E4" s="43" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="43" t="n"/>
+      <c r="I4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr"/>
+      <c r="J4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="G5" s="37" t="inlineStr">
+      <c r="G5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="I5" s="37" t="inlineStr">
+      <c r="I5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="C7" s="64" t="inlineStr">
+      <c r="C7" s="68" t="inlineStr">
         <is>
           <t>BILAN</t>
         </is>
       </c>
-      <c r="D7" s="65" t="n"/>
-      <c r="E7" s="65" t="n"/>
-      <c r="F7" s="65" t="n"/>
-      <c r="G7" s="65" t="n"/>
-      <c r="H7" s="65" t="n"/>
+      <c r="D7" s="69" t="n"/>
+      <c r="E7" s="69" t="n"/>
+      <c r="F7" s="69" t="n"/>
+      <c r="G7" s="69" t="n"/>
+      <c r="H7" s="69" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="66" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>REF</t>
         </is>
       </c>
-      <c r="B8" s="67" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>ACTIF</t>
         </is>
       </c>
-      <c r="C8" s="67" t="inlineStr">
+      <c r="C8" s="71" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="D8" s="67" t="inlineStr">
+      <c r="D8" s="71" t="inlineStr">
         <is>
           <t>EXERCICE N</t>
         </is>
       </c>
-      <c r="E8" s="68" t="inlineStr">
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>EXERCICE N-1</t>
         </is>
       </c>
-      <c r="F8" s="66" t="inlineStr">
+      <c r="F8" s="70" t="inlineStr">
         <is>
           <t>REF</t>
         </is>
       </c>
-      <c r="G8" s="67" t="inlineStr">
+      <c r="G8" s="71" t="inlineStr">
         <is>
           <t>PASSIF</t>
         </is>
       </c>
-      <c r="H8" s="67" t="inlineStr">
+      <c r="H8" s="71" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="I8" s="67" t="inlineStr">
+      <c r="I8" s="71" t="inlineStr">
         <is>
           <t>EXERCICE N</t>
         </is>
       </c>
-      <c r="J8" s="68" t="inlineStr">
+      <c r="J8" s="72" t="inlineStr">
         <is>
           <t>EXERCICE N-1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="69" t="n"/>
-      <c r="B9" s="70" t="n"/>
-      <c r="C9" s="70" t="n"/>
-      <c r="D9" s="70" t="n"/>
-      <c r="E9" s="71" t="n"/>
-      <c r="F9" s="69" t="n"/>
-      <c r="G9" s="70" t="n"/>
-      <c r="H9" s="70" t="n"/>
-      <c r="I9" s="70" t="n"/>
-      <c r="J9" s="71" t="n"/>
+      <c r="A9" s="73" t="n"/>
+      <c r="B9" s="74" t="n"/>
+      <c r="C9" s="74" t="n"/>
+      <c r="D9" s="74" t="n"/>
+      <c r="E9" s="75" t="n"/>
+      <c r="F9" s="73" t="n"/>
+      <c r="G9" s="74" t="n"/>
+      <c r="H9" s="74" t="n"/>
+      <c r="I9" s="74" t="n"/>
+      <c r="J9" s="75" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="72" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>SA1</t>
         </is>
       </c>
-      <c r="B10" s="73" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Immobilisations (1)</t>
         </is>
       </c>
-      <c r="C10" s="73" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="5">
         <f>'Bilan-Actif'!D9</f>
         <v/>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="77">
         <f>'Bilan-Actif'!E9</f>
         <v/>
       </c>
-      <c r="F10" s="72" t="inlineStr">
+      <c r="F10" s="76" t="inlineStr">
         <is>
           <t>SP1</t>
         </is>
       </c>
-      <c r="G10" s="73" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Compte exploitant</t>
         </is>
       </c>
-      <c r="H10" s="73" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I10" s="74">
+      <c r="I10" s="5">
         <f>'Bilan-Passif'!D9</f>
         <v/>
       </c>
-      <c r="J10" s="75">
+      <c r="J10" s="77">
         <f>'Bilan-Passif'!E9</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="76" t="inlineStr">
         <is>
           <t>SA2</t>
         </is>
       </c>
-      <c r="B11" s="73" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Stocks</t>
         </is>
       </c>
-      <c r="C11" s="73" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="74">
+      <c r="D11" s="5">
         <f>'Bilan-Actif'!D10</f>
         <v/>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="77">
         <f>'Bilan-Actif'!E10</f>
         <v/>
       </c>
-      <c r="F11" s="72" t="inlineStr">
+      <c r="F11" s="76" t="inlineStr">
         <is>
           <t>SP2</t>
         </is>
       </c>
-      <c r="G11" s="73" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Résultat de l'exercice (en + ou en -)</t>
         </is>
       </c>
-      <c r="H11" s="73" t="inlineStr"/>
-      <c r="I11" s="74">
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="5">
         <f>'Bilan-Passif'!D10</f>
         <v/>
       </c>
-      <c r="J11" s="75">
+      <c r="J11" s="77">
         <f>'Bilan-Passif'!E10</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="72" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>SA3</t>
         </is>
       </c>
-      <c r="B12" s="73" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Clients et débiteurs divers</t>
         </is>
       </c>
-      <c r="C12" s="73" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="74">
+      <c r="D12" s="5">
         <f>'Bilan-Actif'!D11</f>
         <v/>
       </c>
-      <c r="E12" s="75">
+      <c r="E12" s="77">
         <f>'Bilan-Actif'!E11</f>
         <v/>
       </c>
-      <c r="F12" s="72" t="inlineStr">
+      <c r="F12" s="76" t="inlineStr">
         <is>
           <t>SP3</t>
         </is>
       </c>
-      <c r="G12" s="73" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Emprunt</t>
         </is>
       </c>
-      <c r="H12" s="73" t="inlineStr"/>
-      <c r="I12" s="74">
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="5">
         <f>'Bilan-Passif'!D11</f>
         <v/>
       </c>
-      <c r="J12" s="75">
+      <c r="J12" s="77">
         <f>'Bilan-Passif'!E11</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="72" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr">
         <is>
           <t>SA4</t>
         </is>
       </c>
-      <c r="B13" s="73" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Caisse</t>
         </is>
       </c>
-      <c r="C13" s="73" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="74">
+      <c r="D13" s="5">
         <f>'Bilan-Actif'!D12</f>
         <v/>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="77">
         <f>'Bilan-Actif'!E12</f>
         <v/>
       </c>
-      <c r="F13" s="72" t="inlineStr">
+      <c r="F13" s="76" t="inlineStr">
         <is>
           <t>SP4</t>
         </is>
       </c>
-      <c r="G13" s="73" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Fournisseurs et créditeurs divers</t>
         </is>
       </c>
-      <c r="H13" s="73" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I13" s="74">
+      <c r="I13" s="5">
         <f>'Bilan-Passif'!D12</f>
         <v/>
       </c>
-      <c r="J13" s="75">
+      <c r="J13" s="77">
         <f>'Bilan-Passif'!E12</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="72" t="inlineStr">
+      <c r="A14" s="76" t="inlineStr">
         <is>
           <t>SA5</t>
         </is>
       </c>
-      <c r="B14" s="73" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Banque (en + ou en -)</t>
         </is>
       </c>
-      <c r="C14" s="73" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="74">
+      <c r="D14" s="5">
         <f>'Bilan-Actif'!D13</f>
         <v/>
       </c>
-      <c r="E14" s="75">
+      <c r="E14" s="77">
         <f>'Bilan-Actif'!E13</f>
         <v/>
       </c>
-      <c r="F14" s="76" t="inlineStr">
+      <c r="F14" s="78" t="inlineStr">
         <is>
           <t>SPZ</t>
         </is>
       </c>
-      <c r="G14" s="77" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>TOTAL PASSIF</t>
         </is>
       </c>
-      <c r="H14" s="77" t="n"/>
-      <c r="I14" s="78">
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="7">
         <f>'Bilan-Passif'!D13</f>
         <v/>
       </c>
@@ -7114,18 +7038,18 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="76" t="inlineStr">
+      <c r="A15" s="78" t="inlineStr">
         <is>
           <t>SAZ</t>
         </is>
       </c>
-      <c r="B15" s="77" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>TOTAL ACTIF</t>
         </is>
       </c>
-      <c r="C15" s="77" t="n"/>
-      <c r="D15" s="78">
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="7">
         <f>'Bilan-Actif'!D14</f>
         <v/>
       </c>
@@ -7133,11 +7057,11 @@
         <f>'Bilan-Actif'!E14</f>
         <v/>
       </c>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="28" t="n"/>
-      <c r="H15" s="28" t="n"/>
-      <c r="I15" s="28" t="n"/>
-      <c r="J15" s="29" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="32" t="n"/>
+      <c r="H15" s="32" t="n"/>
+      <c r="I15" s="32" t="n"/>
+      <c r="J15" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -7176,76 +7100,76 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 4 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>BILAN SYSCOHADA - SMT
 PAGE 1/2</t>
         </is>
       </c>
-      <c r="E2" s="50" t="n"/>
+      <c r="E2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr"/>
+      <c r="E4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>BILAN</t>
         </is>
       </c>
-      <c r="B7" s="65" t="n"/>
-      <c r="C7" s="65" t="n"/>
-      <c r="D7" s="65" t="n"/>
-      <c r="E7" s="65" t="n"/>
+      <c r="B7" s="69" t="n"/>
+      <c r="C7" s="69" t="n"/>
+      <c r="D7" s="69" t="n"/>
+      <c r="E7" s="69" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -7275,128 +7199,128 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>SA1</t>
         </is>
       </c>
-      <c r="B9" s="73" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Immobilisations (1)</t>
         </is>
       </c>
-      <c r="C9" s="73" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"2*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"2*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="E9" s="75" t="n"/>
+      <c r="D9" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"2*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"2*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="E9" s="77" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="72" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>SA2</t>
         </is>
       </c>
-      <c r="B10" s="73" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Stocks</t>
         </is>
       </c>
-      <c r="C10" s="73" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"3*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"3*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="E10" s="75" t="n"/>
+      <c r="D10" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"3*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"3*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="E10" s="77" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="76" t="inlineStr">
         <is>
           <t>SA3</t>
         </is>
       </c>
-      <c r="B11" s="73" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Clients et débiteurs divers</t>
         </is>
       </c>
-      <c r="C11" s="73" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$F$2:$F$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"49*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"590*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"591*",'BALANCE N'!$G$2:$G$50))+(SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$G$2:$G$50))</f>
-        <v/>
-      </c>
-      <c r="E11" s="75" t="n"/>
+      <c r="D11" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"49*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"591*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"590*",'BALANCE N'!$H$2:$H$50))+(SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$H$2:$H$50))</f>
+        <v/>
+      </c>
+      <c r="E11" s="77" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="72" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>SA4</t>
         </is>
       </c>
-      <c r="B12" s="73" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Caisse</t>
         </is>
       </c>
-      <c r="C12" s="73" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D12" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"57*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"57*",'BALANCE N'!$G$2:$G$50)</f>
-        <v/>
-      </c>
-      <c r="E12" s="75" t="n"/>
+      <c r="D12" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"57*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"57*",'BALANCE N'!$H$2:$H$50)</f>
+        <v/>
+      </c>
+      <c r="E12" s="77" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="72" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr">
         <is>
           <t>SA5</t>
         </is>
       </c>
-      <c r="B13" s="73" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Banque (en + ou en -)</t>
         </is>
       </c>
-      <c r="C13" s="73" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$F$2:$F$50)-SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$G$2:$G$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"592*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"593*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"594*",'BALANCE N'!$G$2:$G$50))</f>
-        <v/>
-      </c>
-      <c r="E13" s="75" t="n"/>
+      <c r="D13" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$H$2:$H$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"594*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"593*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"592*",'BALANCE N'!$H$2:$H$50))</f>
+        <v/>
+      </c>
+      <c r="E13" s="77" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="76" t="inlineStr">
+      <c r="A14" s="78" t="inlineStr">
         <is>
           <t>SAZ</t>
         </is>
       </c>
-      <c r="B14" s="77" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>TOTAL ACTIF</t>
         </is>
       </c>
-      <c r="C14" s="77" t="n"/>
-      <c r="D14" s="78">
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="7">
         <f>SUM(D9:D13)</f>
         <v/>
       </c>
@@ -7404,7 +7328,7 @@
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>(1) À faire figurer à l'actif si montants significatifs (AUDCIF Titre X). Registre des immobilisations : NOTE 1.</t>
         </is>
@@ -7436,76 +7360,76 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>- 5 -</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>BILAN SYSCOHADA - SMT
 PAGE 2/2</t>
         </is>
       </c>
-      <c r="E2" s="50" t="n"/>
+      <c r="E2" s="54" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Dénomination sociale : ETS EXEMPLE COMMERCE</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Adresse :</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="B4" s="55" t="inlineStr"/>
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>Sigle usuel :</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr"/>
+      <c r="E4" s="55" t="inlineStr"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>N° de compte contribuable (NCC) : RCCM-2022-A-567</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>Exercice clos le 31-12-2025</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>Durée (en mois) : 12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>N° de télédéclarant (NTD) :</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="64" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>BILAN</t>
         </is>
       </c>
-      <c r="B7" s="65" t="n"/>
-      <c r="C7" s="65" t="n"/>
-      <c r="D7" s="65" t="n"/>
-      <c r="E7" s="65" t="n"/>
+      <c r="B7" s="69" t="n"/>
+      <c r="C7" s="69" t="n"/>
+      <c r="D7" s="69" t="n"/>
+      <c r="E7" s="69" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -7535,98 +7459,98 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>SP1</t>
         </is>
       </c>
-      <c r="B9" s="73" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Compte exploitant</t>
         </is>
       </c>
-      <c r="C9" s="73" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$F$2:$F$50)</f>
-        <v/>
-      </c>
-      <c r="E9" s="75" t="n"/>
+      <c r="D9" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$G$2:$G$50)</f>
+        <v/>
+      </c>
+      <c r="E9" s="77" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="72" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>SP2</t>
         </is>
       </c>
-      <c r="B10" s="73" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Résultat de l'exercice (en + ou en -)</t>
         </is>
       </c>
-      <c r="C10" s="73" t="inlineStr"/>
-      <c r="D10" s="74">
-        <f>'Résultat'!D24+(SUMIF('BALANCE N'!$A$2:$A$50,"13*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"13*",'BALANCE N'!$F$2:$F$50))</f>
-        <v/>
-      </c>
-      <c r="E10" s="75" t="n"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="5">
+        <f>'Résultat'!D24+(SUMIF('BALANCE N'!$A$2:$A$50,"13*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"13*",'BALANCE N'!$G$2:$G$50))</f>
+        <v/>
+      </c>
+      <c r="E10" s="77" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="76" t="inlineStr">
         <is>
           <t>SP3</t>
         </is>
       </c>
-      <c r="B11" s="73" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Emprunt</t>
         </is>
       </c>
-      <c r="C11" s="73" t="inlineStr"/>
-      <c r="D11" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$F$2:$F$50)+SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$F$2:$F$50)</f>
-        <v/>
-      </c>
-      <c r="E11" s="75" t="n"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$G$2:$G$50)</f>
+        <v/>
+      </c>
+      <c r="E11" s="77" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="72" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>SP4</t>
         </is>
       </c>
-      <c r="B12" s="73" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Fournisseurs et créditeurs divers</t>
         </is>
       </c>
-      <c r="C12" s="73" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="74">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"49*",'BALANCE N'!$G$2:$G$50)+(SUMIF('BALANCE N'!$A$2:$A$50,"599*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"599*",'BALANCE N'!$F$2:$F$50))</f>
-        <v/>
-      </c>
-      <c r="E12" s="75" t="n"/>
+      <c r="D12" s="5">
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"49*",'BALANCE N'!$H$2:$H$50)+(SUMIF('BALANCE N'!$A$2:$A$50,"599*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"599*",'BALANCE N'!$G$2:$G$50))</f>
+        <v/>
+      </c>
+      <c r="E12" s="77" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="76" t="inlineStr">
+      <c r="A13" s="78" t="inlineStr">
         <is>
           <t>SPZ</t>
         </is>
       </c>
-      <c r="B13" s="77" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>TOTAL PASSIF</t>
         </is>
       </c>
-      <c r="C13" s="77" t="n"/>
-      <c r="D13" s="78">
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="7">
         <f>SUM(D9:D12)</f>
         <v/>
       </c>
@@ -7634,7 +7558,7 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>Le compte exploitant regroupe apports, prélèvements et réserves de l'exploitant (comptes 10, 11, 12, 14, 15).</t>
         </is>

--- a/.claude/skills/syscohada/liasse/exemples/exemple-etats-smt.xlsx
+++ b/.claude/skills/syscohada/liasse/exemples/exemple-etats-smt.xlsx
@@ -37,7 +37,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,6 +167,12 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Arial Black"/>
+      <b val="1"/>
+      <color rgb="00D9D9D9"/>
+      <sz val="26"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <color theme="1"/>
       <sz val="9"/>
@@ -603,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -821,13 +827,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="15"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1988,7 +1997,7 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E10" s="77" t="n"/>
@@ -2094,7 +2103,7 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$H$2:$H$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="E15" s="77" t="n"/>
@@ -2134,7 +2143,7 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$H$2:$H$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="E17" s="77" t="n"/>
@@ -2252,7 +2261,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr"/>
       <c r="D23" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$H$2:$H$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="E23" s="77" t="n"/>
@@ -2298,7 +2307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.5" customWidth="1" min="1" max="1"/>
@@ -2572,10 +2581,21 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="95" t="inlineStr">
+        <is>
+          <t>NOTE À COMPLÉTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1"/>
+    <row r="23" ht="26" customHeight="1"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A21:J23"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="A18:J18"/>
@@ -2599,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2719,56 +2739,56 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="95" t="inlineStr">
+      <c r="A9" s="96" t="inlineStr">
         <is>
           <t>2441</t>
         </is>
       </c>
-      <c r="B9" s="95" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Matériel et mobilier</t>
         </is>
       </c>
-      <c r="C9" s="96">
+      <c r="C9" s="97">
         <f>SUMIF('BALANCE N'!$A$2:$A$50,"2441*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"2441*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
-      <c r="D9" s="95" t="n"/>
-      <c r="E9" s="95" t="n"/>
-      <c r="F9" s="95" t="n"/>
-      <c r="G9" s="96" t="n"/>
+      <c r="D9" s="96" t="n"/>
+      <c r="E9" s="96" t="n"/>
+      <c r="F9" s="96" t="n"/>
+      <c r="G9" s="97" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="95" t="n"/>
-      <c r="B10" s="95" t="inlineStr">
+      <c r="A10" s="96" t="n"/>
+      <c r="B10" s="96" t="inlineStr">
         <is>
           <t>TOTAL IMMOBILISATIONS BRUTES</t>
         </is>
       </c>
-      <c r="C10" s="96">
+      <c r="C10" s="97">
         <f>SUM(C9:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="95" t="n"/>
-      <c r="E10" s="95" t="n"/>
-      <c r="F10" s="95" t="n"/>
-      <c r="G10" s="96" t="n"/>
+      <c r="D10" s="96" t="n"/>
+      <c r="E10" s="96" t="n"/>
+      <c r="F10" s="96" t="n"/>
+      <c r="G10" s="97" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="95" t="n"/>
-      <c r="B11" s="95" t="inlineStr">
+      <c r="A11" s="96" t="n"/>
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>Amortissements et dépréciations cumulés (28/29)</t>
         </is>
       </c>
-      <c r="C11" s="96">
+      <c r="C11" s="97">
         <f>SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
-      <c r="D11" s="95" t="n"/>
-      <c r="E11" s="95" t="n"/>
-      <c r="F11" s="95" t="n"/>
-      <c r="G11" s="96" t="n"/>
+      <c r="D11" s="96" t="n"/>
+      <c r="E11" s="96" t="n"/>
+      <c r="F11" s="96" t="n"/>
+      <c r="G11" s="97" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
@@ -2784,18 +2804,28 @@
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
-      <c r="G12" s="97" t="n"/>
+      <c r="G12" s="98" t="n"/>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="98" t="inlineStr">
+      <c r="A14" s="99" t="inlineStr">
         <is>
           <t>Compléter dates, durées et sorties depuis le registre : la balance ne porte que les montants.</t>
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="95">
+        <f>IF(SUM(C9:C12,G9:G12)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1"/>
+    <row r="18" ht="26" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A16:G18"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="B4:D4"/>
@@ -2810,7 +2840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2916,43 +2946,43 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="95" t="inlineStr">
+      <c r="A9" s="96" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="B9" s="95" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Stocks d'autres approvisionnements</t>
         </is>
       </c>
-      <c r="C9" s="95" t="n"/>
-      <c r="D9" s="95" t="n"/>
-      <c r="E9" s="96">
+      <c r="C9" s="96" t="n"/>
+      <c r="D9" s="96" t="n"/>
+      <c r="E9" s="97">
         <f>SUMIF('BALANCE N'!$A$2:$A$50,"33*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"33*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="95" t="n"/>
-      <c r="B10" s="95" t="n"/>
-      <c r="C10" s="95" t="n"/>
-      <c r="D10" s="95" t="n"/>
-      <c r="E10" s="96" t="n"/>
+      <c r="A10" s="96" t="n"/>
+      <c r="B10" s="96" t="n"/>
+      <c r="C10" s="96" t="n"/>
+      <c r="D10" s="96" t="n"/>
+      <c r="E10" s="97" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="95" t="n"/>
-      <c r="B11" s="95" t="n"/>
-      <c r="C11" s="95" t="n"/>
-      <c r="D11" s="95" t="n"/>
-      <c r="E11" s="96" t="n"/>
+      <c r="A11" s="96" t="n"/>
+      <c r="B11" s="96" t="n"/>
+      <c r="C11" s="96" t="n"/>
+      <c r="D11" s="96" t="n"/>
+      <c r="E11" s="97" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="95" t="n"/>
-      <c r="B12" s="95" t="n"/>
-      <c r="C12" s="95" t="n"/>
-      <c r="D12" s="95" t="n"/>
-      <c r="E12" s="96" t="n"/>
+      <c r="A12" s="96" t="n"/>
+      <c r="B12" s="96" t="n"/>
+      <c r="C12" s="96" t="n"/>
+      <c r="D12" s="96" t="n"/>
+      <c r="E12" s="97" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -2995,8 +3025,18 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="95">
+        <f>IF(SUM(E9:E15)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1"/>
+    <row r="19" ht="26" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A17:E19"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="D2:E2"/>
   </mergeCells>
@@ -3010,7 +3050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3130,85 +3170,85 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="95" t="n"/>
-      <c r="B10" s="95" t="n"/>
-      <c r="C10" s="96" t="n"/>
-      <c r="D10" s="96" t="n"/>
-      <c r="E10" s="96">
+      <c r="A10" s="96" t="n"/>
+      <c r="B10" s="96" t="n"/>
+      <c r="C10" s="97" t="n"/>
+      <c r="D10" s="97" t="n"/>
+      <c r="E10" s="97">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="96">
         <f>IF(D10=0,"",(C10-D10)/D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="95" t="n"/>
-      <c r="B11" s="95" t="n"/>
-      <c r="C11" s="96" t="n"/>
-      <c r="D11" s="96" t="n"/>
-      <c r="E11" s="96">
+      <c r="A11" s="96" t="n"/>
+      <c r="B11" s="96" t="n"/>
+      <c r="C11" s="97" t="n"/>
+      <c r="D11" s="97" t="n"/>
+      <c r="E11" s="97">
         <f>C11-D11</f>
         <v/>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="96">
         <f>IF(D11=0,"",(C11-D11)/D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="95" t="n"/>
-      <c r="B12" s="95" t="n"/>
-      <c r="C12" s="96" t="n"/>
-      <c r="D12" s="96" t="n"/>
-      <c r="E12" s="96">
+      <c r="A12" s="96" t="n"/>
+      <c r="B12" s="96" t="n"/>
+      <c r="C12" s="97" t="n"/>
+      <c r="D12" s="97" t="n"/>
+      <c r="E12" s="97">
         <f>C12-D12</f>
         <v/>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="96">
         <f>IF(D12=0,"",(C12-D12)/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="95" t="n"/>
-      <c r="B13" s="95" t="n"/>
-      <c r="C13" s="96" t="n"/>
-      <c r="D13" s="96" t="n"/>
-      <c r="E13" s="96">
+      <c r="A13" s="96" t="n"/>
+      <c r="B13" s="96" t="n"/>
+      <c r="C13" s="97" t="n"/>
+      <c r="D13" s="97" t="n"/>
+      <c r="E13" s="97">
         <f>C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="96">
         <f>IF(D13=0,"",(C13-D13)/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="95" t="n"/>
-      <c r="B14" s="95" t="n"/>
-      <c r="C14" s="96" t="n"/>
-      <c r="D14" s="96" t="n"/>
-      <c r="E14" s="96">
+      <c r="A14" s="96" t="n"/>
+      <c r="B14" s="96" t="n"/>
+      <c r="C14" s="97" t="n"/>
+      <c r="D14" s="97" t="n"/>
+      <c r="E14" s="97">
         <f>C14-D14</f>
         <v/>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="96">
         <f>IF(D14=0,"",(C14-D14)/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="95" t="n"/>
-      <c r="B15" s="95" t="n"/>
-      <c r="C15" s="96" t="n"/>
-      <c r="D15" s="96" t="n"/>
-      <c r="E15" s="96">
+      <c r="A15" s="96" t="n"/>
+      <c r="B15" s="96" t="n"/>
+      <c r="C15" s="97" t="n"/>
+      <c r="D15" s="97" t="n"/>
+      <c r="E15" s="97">
         <f>C15-D15</f>
         <v/>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="96">
         <f>IF(D15=0,"",(C15-D15)/D15)</f>
         <v/>
       </c>
@@ -3235,16 +3275,16 @@
       <c r="F16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="98" t="inlineStr">
+      <c r="B17" s="99" t="inlineStr">
         <is>
           <t>Rappel balance (classe 4, soldes débiteurs) - contrôle</t>
         </is>
       </c>
-      <c r="C17" s="99">
+      <c r="C17" s="100">
         <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
-      <c r="D17" s="99">
+      <c r="D17" s="100">
         <f>0</f>
         <v/>
       </c>
@@ -3291,85 +3331,85 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="95" t="n"/>
-      <c r="B22" s="95" t="n"/>
-      <c r="C22" s="96" t="n"/>
-      <c r="D22" s="96" t="n"/>
-      <c r="E22" s="96">
+      <c r="A22" s="96" t="n"/>
+      <c r="B22" s="96" t="n"/>
+      <c r="C22" s="97" t="n"/>
+      <c r="D22" s="97" t="n"/>
+      <c r="E22" s="97">
         <f>C22-D22</f>
         <v/>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="96">
         <f>IF(D22=0,"",(C22-D22)/D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="95" t="n"/>
-      <c r="B23" s="95" t="n"/>
-      <c r="C23" s="96" t="n"/>
-      <c r="D23" s="96" t="n"/>
-      <c r="E23" s="96">
+      <c r="A23" s="96" t="n"/>
+      <c r="B23" s="96" t="n"/>
+      <c r="C23" s="97" t="n"/>
+      <c r="D23" s="97" t="n"/>
+      <c r="E23" s="97">
         <f>C23-D23</f>
         <v/>
       </c>
-      <c r="F23" s="95">
+      <c r="F23" s="96">
         <f>IF(D23=0,"",(C23-D23)/D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="95" t="n"/>
-      <c r="B24" s="95" t="n"/>
-      <c r="C24" s="96" t="n"/>
-      <c r="D24" s="96" t="n"/>
-      <c r="E24" s="96">
+      <c r="A24" s="96" t="n"/>
+      <c r="B24" s="96" t="n"/>
+      <c r="C24" s="97" t="n"/>
+      <c r="D24" s="97" t="n"/>
+      <c r="E24" s="97">
         <f>C24-D24</f>
         <v/>
       </c>
-      <c r="F24" s="95">
+      <c r="F24" s="96">
         <f>IF(D24=0,"",(C24-D24)/D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="95" t="n"/>
-      <c r="B25" s="95" t="n"/>
-      <c r="C25" s="96" t="n"/>
-      <c r="D25" s="96" t="n"/>
-      <c r="E25" s="96">
+      <c r="A25" s="96" t="n"/>
+      <c r="B25" s="96" t="n"/>
+      <c r="C25" s="97" t="n"/>
+      <c r="D25" s="97" t="n"/>
+      <c r="E25" s="97">
         <f>C25-D25</f>
         <v/>
       </c>
-      <c r="F25" s="95">
+      <c r="F25" s="96">
         <f>IF(D25=0,"",(C25-D25)/D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="95" t="n"/>
-      <c r="B26" s="95" t="n"/>
-      <c r="C26" s="96" t="n"/>
-      <c r="D26" s="96" t="n"/>
-      <c r="E26" s="96">
+      <c r="A26" s="96" t="n"/>
+      <c r="B26" s="96" t="n"/>
+      <c r="C26" s="97" t="n"/>
+      <c r="D26" s="97" t="n"/>
+      <c r="E26" s="97">
         <f>C26-D26</f>
         <v/>
       </c>
-      <c r="F26" s="95">
+      <c r="F26" s="96">
         <f>IF(D26=0,"",(C26-D26)/D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="95" t="n"/>
-      <c r="B27" s="95" t="n"/>
-      <c r="C27" s="96" t="n"/>
-      <c r="D27" s="96" t="n"/>
-      <c r="E27" s="96">
+      <c r="A27" s="96" t="n"/>
+      <c r="B27" s="96" t="n"/>
+      <c r="C27" s="97" t="n"/>
+      <c r="D27" s="97" t="n"/>
+      <c r="E27" s="97">
         <f>C27-D27</f>
         <v/>
       </c>
-      <c r="F27" s="95">
+      <c r="F27" s="96">
         <f>IF(D27=0,"",(C27-D27)/D27)</f>
         <v/>
       </c>
@@ -3396,16 +3436,16 @@
       <c r="F28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="98" t="inlineStr">
+      <c r="B29" s="99" t="inlineStr">
         <is>
           <t>Rappel balance (classe 4, soldes créditeurs) - contrôle</t>
         </is>
       </c>
-      <c r="C29" s="99">
+      <c r="C29" s="100">
         <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
-      <c r="D29" s="99">
+      <c r="D29" s="100">
         <f>0</f>
         <v/>
       </c>
@@ -3413,14 +3453,24 @@
     <row r="30"/>
     <row r="31"/>
     <row r="32">
-      <c r="A32" s="98" t="inlineStr">
+      <c r="A32" s="99" t="inlineStr">
         <is>
           <t>Reporter la variation des créances en VB et celle des dettes en VC du compte de résultat.</t>
         </is>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="95">
+        <f>IF(SUM(C10:C29,D10:D29,E10:E28)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1"/>
+    <row r="36" ht="26" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A34:F36"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="A7:F7"/>
@@ -3435,7 +3485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3583,245 +3633,245 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="95" t="n"/>
-      <c r="B9" s="95" t="inlineStr">
+      <c r="A9" s="96" t="n"/>
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Report à nouveau</t>
         </is>
       </c>
-      <c r="C9" s="96" t="n"/>
-      <c r="D9" s="96" t="n"/>
-      <c r="E9" s="96" t="n"/>
-      <c r="F9" s="96" t="n"/>
-      <c r="G9" s="96" t="n"/>
-      <c r="H9" s="96" t="n"/>
-      <c r="I9" s="96" t="n"/>
-      <c r="J9" s="96" t="n"/>
-      <c r="K9" s="96" t="n"/>
+      <c r="C9" s="97" t="n"/>
+      <c r="D9" s="97" t="n"/>
+      <c r="E9" s="97" t="n"/>
+      <c r="F9" s="97" t="n"/>
+      <c r="G9" s="97" t="n"/>
+      <c r="H9" s="97" t="n"/>
+      <c r="I9" s="97" t="n"/>
+      <c r="J9" s="97" t="n"/>
+      <c r="K9" s="97" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="95" t="n"/>
-      <c r="B10" s="95" t="n"/>
-      <c r="C10" s="96" t="n"/>
-      <c r="D10" s="96" t="n"/>
-      <c r="E10" s="96">
+      <c r="A10" s="96" t="n"/>
+      <c r="B10" s="96" t="n"/>
+      <c r="C10" s="97" t="n"/>
+      <c r="D10" s="97" t="n"/>
+      <c r="E10" s="97">
         <f>E9+C10-D10</f>
         <v/>
       </c>
-      <c r="F10" s="96" t="n"/>
-      <c r="G10" s="96" t="n"/>
-      <c r="H10" s="96" t="n"/>
-      <c r="I10" s="96" t="n"/>
-      <c r="J10" s="96" t="n"/>
-      <c r="K10" s="96" t="n"/>
+      <c r="F10" s="97" t="n"/>
+      <c r="G10" s="97" t="n"/>
+      <c r="H10" s="97" t="n"/>
+      <c r="I10" s="97" t="n"/>
+      <c r="J10" s="97" t="n"/>
+      <c r="K10" s="97" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="95" t="n"/>
-      <c r="B11" s="95" t="n"/>
-      <c r="C11" s="96" t="n"/>
-      <c r="D11" s="96" t="n"/>
-      <c r="E11" s="96">
+      <c r="A11" s="96" t="n"/>
+      <c r="B11" s="96" t="n"/>
+      <c r="C11" s="97" t="n"/>
+      <c r="D11" s="97" t="n"/>
+      <c r="E11" s="97">
         <f>E10+C11-D11</f>
         <v/>
       </c>
-      <c r="F11" s="96" t="n"/>
-      <c r="G11" s="96" t="n"/>
-      <c r="H11" s="96" t="n"/>
-      <c r="I11" s="96" t="n"/>
-      <c r="J11" s="96" t="n"/>
-      <c r="K11" s="96" t="n"/>
+      <c r="F11" s="97" t="n"/>
+      <c r="G11" s="97" t="n"/>
+      <c r="H11" s="97" t="n"/>
+      <c r="I11" s="97" t="n"/>
+      <c r="J11" s="97" t="n"/>
+      <c r="K11" s="97" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="95" t="n"/>
-      <c r="B12" s="95" t="n"/>
-      <c r="C12" s="96" t="n"/>
-      <c r="D12" s="96" t="n"/>
-      <c r="E12" s="96">
+      <c r="A12" s="96" t="n"/>
+      <c r="B12" s="96" t="n"/>
+      <c r="C12" s="97" t="n"/>
+      <c r="D12" s="97" t="n"/>
+      <c r="E12" s="97">
         <f>E11+C12-D12</f>
         <v/>
       </c>
-      <c r="F12" s="96" t="n"/>
-      <c r="G12" s="96" t="n"/>
-      <c r="H12" s="96" t="n"/>
-      <c r="I12" s="96" t="n"/>
-      <c r="J12" s="96" t="n"/>
-      <c r="K12" s="96" t="n"/>
+      <c r="F12" s="97" t="n"/>
+      <c r="G12" s="97" t="n"/>
+      <c r="H12" s="97" t="n"/>
+      <c r="I12" s="97" t="n"/>
+      <c r="J12" s="97" t="n"/>
+      <c r="K12" s="97" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="95" t="n"/>
-      <c r="B13" s="95" t="n"/>
-      <c r="C13" s="96" t="n"/>
-      <c r="D13" s="96" t="n"/>
-      <c r="E13" s="96">
+      <c r="A13" s="96" t="n"/>
+      <c r="B13" s="96" t="n"/>
+      <c r="C13" s="97" t="n"/>
+      <c r="D13" s="97" t="n"/>
+      <c r="E13" s="97">
         <f>E12+C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="96" t="n"/>
-      <c r="G13" s="96" t="n"/>
-      <c r="H13" s="96" t="n"/>
-      <c r="I13" s="96" t="n"/>
-      <c r="J13" s="96" t="n"/>
-      <c r="K13" s="96" t="n"/>
+      <c r="F13" s="97" t="n"/>
+      <c r="G13" s="97" t="n"/>
+      <c r="H13" s="97" t="n"/>
+      <c r="I13" s="97" t="n"/>
+      <c r="J13" s="97" t="n"/>
+      <c r="K13" s="97" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="95" t="n"/>
-      <c r="B14" s="95" t="n"/>
-      <c r="C14" s="96" t="n"/>
-      <c r="D14" s="96" t="n"/>
-      <c r="E14" s="96">
+      <c r="A14" s="96" t="n"/>
+      <c r="B14" s="96" t="n"/>
+      <c r="C14" s="97" t="n"/>
+      <c r="D14" s="97" t="n"/>
+      <c r="E14" s="97">
         <f>E13+C14-D14</f>
         <v/>
       </c>
-      <c r="F14" s="96" t="n"/>
-      <c r="G14" s="96" t="n"/>
-      <c r="H14" s="96" t="n"/>
-      <c r="I14" s="96" t="n"/>
-      <c r="J14" s="96" t="n"/>
-      <c r="K14" s="96" t="n"/>
+      <c r="F14" s="97" t="n"/>
+      <c r="G14" s="97" t="n"/>
+      <c r="H14" s="97" t="n"/>
+      <c r="I14" s="97" t="n"/>
+      <c r="J14" s="97" t="n"/>
+      <c r="K14" s="97" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="95" t="n"/>
-      <c r="B15" s="95" t="n"/>
-      <c r="C15" s="96" t="n"/>
-      <c r="D15" s="96" t="n"/>
-      <c r="E15" s="96">
+      <c r="A15" s="96" t="n"/>
+      <c r="B15" s="96" t="n"/>
+      <c r="C15" s="97" t="n"/>
+      <c r="D15" s="97" t="n"/>
+      <c r="E15" s="97">
         <f>E14+C15-D15</f>
         <v/>
       </c>
-      <c r="F15" s="96" t="n"/>
-      <c r="G15" s="96" t="n"/>
-      <c r="H15" s="96" t="n"/>
-      <c r="I15" s="96" t="n"/>
-      <c r="J15" s="96" t="n"/>
-      <c r="K15" s="96" t="n"/>
+      <c r="F15" s="97" t="n"/>
+      <c r="G15" s="97" t="n"/>
+      <c r="H15" s="97" t="n"/>
+      <c r="I15" s="97" t="n"/>
+      <c r="J15" s="97" t="n"/>
+      <c r="K15" s="97" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="95" t="n"/>
-      <c r="B16" s="95" t="n"/>
-      <c r="C16" s="96" t="n"/>
-      <c r="D16" s="96" t="n"/>
-      <c r="E16" s="96">
+      <c r="A16" s="96" t="n"/>
+      <c r="B16" s="96" t="n"/>
+      <c r="C16" s="97" t="n"/>
+      <c r="D16" s="97" t="n"/>
+      <c r="E16" s="97">
         <f>E15+C16-D16</f>
         <v/>
       </c>
-      <c r="F16" s="96" t="n"/>
-      <c r="G16" s="96" t="n"/>
-      <c r="H16" s="96" t="n"/>
-      <c r="I16" s="96" t="n"/>
-      <c r="J16" s="96" t="n"/>
-      <c r="K16" s="96" t="n"/>
+      <c r="F16" s="97" t="n"/>
+      <c r="G16" s="97" t="n"/>
+      <c r="H16" s="97" t="n"/>
+      <c r="I16" s="97" t="n"/>
+      <c r="J16" s="97" t="n"/>
+      <c r="K16" s="97" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="95" t="n"/>
-      <c r="B17" s="95" t="n"/>
-      <c r="C17" s="96" t="n"/>
-      <c r="D17" s="96" t="n"/>
-      <c r="E17" s="96">
+      <c r="A17" s="96" t="n"/>
+      <c r="B17" s="96" t="n"/>
+      <c r="C17" s="97" t="n"/>
+      <c r="D17" s="97" t="n"/>
+      <c r="E17" s="97">
         <f>E16+C17-D17</f>
         <v/>
       </c>
-      <c r="F17" s="96" t="n"/>
-      <c r="G17" s="96" t="n"/>
-      <c r="H17" s="96" t="n"/>
-      <c r="I17" s="96" t="n"/>
-      <c r="J17" s="96" t="n"/>
-      <c r="K17" s="96" t="n"/>
+      <c r="F17" s="97" t="n"/>
+      <c r="G17" s="97" t="n"/>
+      <c r="H17" s="97" t="n"/>
+      <c r="I17" s="97" t="n"/>
+      <c r="J17" s="97" t="n"/>
+      <c r="K17" s="97" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="95" t="n"/>
-      <c r="B18" s="95" t="n"/>
-      <c r="C18" s="96" t="n"/>
-      <c r="D18" s="96" t="n"/>
-      <c r="E18" s="96">
+      <c r="A18" s="96" t="n"/>
+      <c r="B18" s="96" t="n"/>
+      <c r="C18" s="97" t="n"/>
+      <c r="D18" s="97" t="n"/>
+      <c r="E18" s="97">
         <f>E17+C18-D18</f>
         <v/>
       </c>
-      <c r="F18" s="96" t="n"/>
-      <c r="G18" s="96" t="n"/>
-      <c r="H18" s="96" t="n"/>
-      <c r="I18" s="96" t="n"/>
-      <c r="J18" s="96" t="n"/>
-      <c r="K18" s="96" t="n"/>
+      <c r="F18" s="97" t="n"/>
+      <c r="G18" s="97" t="n"/>
+      <c r="H18" s="97" t="n"/>
+      <c r="I18" s="97" t="n"/>
+      <c r="J18" s="97" t="n"/>
+      <c r="K18" s="97" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="95" t="n"/>
-      <c r="B19" s="95" t="n"/>
-      <c r="C19" s="96" t="n"/>
-      <c r="D19" s="96" t="n"/>
-      <c r="E19" s="96">
+      <c r="A19" s="96" t="n"/>
+      <c r="B19" s="96" t="n"/>
+      <c r="C19" s="97" t="n"/>
+      <c r="D19" s="97" t="n"/>
+      <c r="E19" s="97">
         <f>E18+C19-D19</f>
         <v/>
       </c>
-      <c r="F19" s="96" t="n"/>
-      <c r="G19" s="96" t="n"/>
-      <c r="H19" s="96" t="n"/>
-      <c r="I19" s="96" t="n"/>
-      <c r="J19" s="96" t="n"/>
-      <c r="K19" s="96" t="n"/>
+      <c r="F19" s="97" t="n"/>
+      <c r="G19" s="97" t="n"/>
+      <c r="H19" s="97" t="n"/>
+      <c r="I19" s="97" t="n"/>
+      <c r="J19" s="97" t="n"/>
+      <c r="K19" s="97" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="95" t="n"/>
-      <c r="B20" s="95" t="n"/>
-      <c r="C20" s="96" t="n"/>
-      <c r="D20" s="96" t="n"/>
-      <c r="E20" s="96">
+      <c r="A20" s="96" t="n"/>
+      <c r="B20" s="96" t="n"/>
+      <c r="C20" s="97" t="n"/>
+      <c r="D20" s="97" t="n"/>
+      <c r="E20" s="97">
         <f>E19+C20-D20</f>
         <v/>
       </c>
-      <c r="F20" s="96" t="n"/>
-      <c r="G20" s="96" t="n"/>
-      <c r="H20" s="96" t="n"/>
-      <c r="I20" s="96" t="n"/>
-      <c r="J20" s="96" t="n"/>
-      <c r="K20" s="96" t="n"/>
+      <c r="F20" s="97" t="n"/>
+      <c r="G20" s="97" t="n"/>
+      <c r="H20" s="97" t="n"/>
+      <c r="I20" s="97" t="n"/>
+      <c r="J20" s="97" t="n"/>
+      <c r="K20" s="97" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="95" t="n"/>
-      <c r="B21" s="95" t="n"/>
-      <c r="C21" s="96" t="n"/>
-      <c r="D21" s="96" t="n"/>
-      <c r="E21" s="96">
+      <c r="A21" s="96" t="n"/>
+      <c r="B21" s="96" t="n"/>
+      <c r="C21" s="97" t="n"/>
+      <c r="D21" s="97" t="n"/>
+      <c r="E21" s="97">
         <f>E20+C21-D21</f>
         <v/>
       </c>
-      <c r="F21" s="96" t="n"/>
-      <c r="G21" s="96" t="n"/>
-      <c r="H21" s="96" t="n"/>
-      <c r="I21" s="96" t="n"/>
-      <c r="J21" s="96" t="n"/>
-      <c r="K21" s="96" t="n"/>
+      <c r="F21" s="97" t="n"/>
+      <c r="G21" s="97" t="n"/>
+      <c r="H21" s="97" t="n"/>
+      <c r="I21" s="97" t="n"/>
+      <c r="J21" s="97" t="n"/>
+      <c r="K21" s="97" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="95" t="n"/>
-      <c r="B22" s="95" t="n"/>
-      <c r="C22" s="96" t="n"/>
-      <c r="D22" s="96" t="n"/>
-      <c r="E22" s="96">
+      <c r="A22" s="96" t="n"/>
+      <c r="B22" s="96" t="n"/>
+      <c r="C22" s="97" t="n"/>
+      <c r="D22" s="97" t="n"/>
+      <c r="E22" s="97">
         <f>E21+C22-D22</f>
         <v/>
       </c>
-      <c r="F22" s="96" t="n"/>
-      <c r="G22" s="96" t="n"/>
-      <c r="H22" s="96" t="n"/>
-      <c r="I22" s="96" t="n"/>
-      <c r="J22" s="96" t="n"/>
-      <c r="K22" s="96" t="n"/>
+      <c r="F22" s="97" t="n"/>
+      <c r="G22" s="97" t="n"/>
+      <c r="H22" s="97" t="n"/>
+      <c r="I22" s="97" t="n"/>
+      <c r="J22" s="97" t="n"/>
+      <c r="K22" s="97" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="95" t="n"/>
-      <c r="B23" s="95" t="n"/>
-      <c r="C23" s="96" t="n"/>
-      <c r="D23" s="96" t="n"/>
-      <c r="E23" s="96">
+      <c r="A23" s="96" t="n"/>
+      <c r="B23" s="96" t="n"/>
+      <c r="C23" s="97" t="n"/>
+      <c r="D23" s="97" t="n"/>
+      <c r="E23" s="97">
         <f>E22+C23-D23</f>
         <v/>
       </c>
-      <c r="F23" s="96" t="n"/>
-      <c r="G23" s="96" t="n"/>
-      <c r="H23" s="96" t="n"/>
-      <c r="I23" s="96" t="n"/>
-      <c r="J23" s="96" t="n"/>
-      <c r="K23" s="96" t="n"/>
+      <c r="F23" s="97" t="n"/>
+      <c r="G23" s="97" t="n"/>
+      <c r="H23" s="97" t="n"/>
+      <c r="I23" s="97" t="n"/>
+      <c r="J23" s="97" t="n"/>
+      <c r="K23" s="97" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n"/>
@@ -3830,24 +3880,34 @@
           <t>Solde à reporter</t>
         </is>
       </c>
-      <c r="C24" s="97" t="n"/>
-      <c r="D24" s="97" t="n"/>
+      <c r="C24" s="98" t="n"/>
+      <c r="D24" s="98" t="n"/>
       <c r="E24" s="9">
         <f>E23</f>
         <v/>
       </c>
-      <c r="F24" s="97" t="n"/>
-      <c r="G24" s="97" t="n"/>
-      <c r="H24" s="97" t="n"/>
-      <c r="I24" s="97" t="n"/>
-      <c r="J24" s="97" t="n"/>
-      <c r="K24" s="97" t="n"/>
-    </row>
+      <c r="F24" s="98" t="n"/>
+      <c r="G24" s="98" t="n"/>
+      <c r="H24" s="98" t="n"/>
+      <c r="I24" s="98" t="n"/>
+      <c r="J24" s="98" t="n"/>
+      <c r="K24" s="98" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="95">
+        <f>IF(SUM(C9:C24,D9:D24,E9:E24,F9:F24,G9:G24,H9:H24,I9:I24,J9:J24,K9:K24)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1"/>
+    <row r="28" ht="26" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A26:K28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3859,7 +3919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3972,53 +4032,53 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="95" t="n"/>
-      <c r="B10" s="95" t="n"/>
-      <c r="C10" s="95" t="n"/>
-      <c r="D10" s="96" t="n"/>
-      <c r="E10" s="95" t="n"/>
+      <c r="A10" s="96" t="n"/>
+      <c r="B10" s="96" t="n"/>
+      <c r="C10" s="96" t="n"/>
+      <c r="D10" s="97" t="n"/>
+      <c r="E10" s="96" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="95" t="n"/>
-      <c r="B11" s="95" t="n"/>
-      <c r="C11" s="95" t="n"/>
-      <c r="D11" s="96" t="n"/>
-      <c r="E11" s="95" t="n"/>
+      <c r="A11" s="96" t="n"/>
+      <c r="B11" s="96" t="n"/>
+      <c r="C11" s="96" t="n"/>
+      <c r="D11" s="97" t="n"/>
+      <c r="E11" s="96" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="95" t="n"/>
-      <c r="B12" s="95" t="n"/>
-      <c r="C12" s="95" t="n"/>
-      <c r="D12" s="96" t="n"/>
-      <c r="E12" s="95" t="n"/>
+      <c r="A12" s="96" t="n"/>
+      <c r="B12" s="96" t="n"/>
+      <c r="C12" s="96" t="n"/>
+      <c r="D12" s="97" t="n"/>
+      <c r="E12" s="96" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="95" t="n"/>
-      <c r="B13" s="95" t="n"/>
-      <c r="C13" s="95" t="n"/>
-      <c r="D13" s="96" t="n"/>
-      <c r="E13" s="95" t="n"/>
+      <c r="A13" s="96" t="n"/>
+      <c r="B13" s="96" t="n"/>
+      <c r="C13" s="96" t="n"/>
+      <c r="D13" s="97" t="n"/>
+      <c r="E13" s="96" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="95" t="n"/>
-      <c r="B14" s="95" t="n"/>
-      <c r="C14" s="95" t="n"/>
-      <c r="D14" s="96" t="n"/>
-      <c r="E14" s="95" t="n"/>
+      <c r="A14" s="96" t="n"/>
+      <c r="B14" s="96" t="n"/>
+      <c r="C14" s="96" t="n"/>
+      <c r="D14" s="97" t="n"/>
+      <c r="E14" s="96" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="95" t="n"/>
-      <c r="B15" s="95" t="n"/>
-      <c r="C15" s="95" t="n"/>
-      <c r="D15" s="96" t="n"/>
-      <c r="E15" s="95" t="n"/>
+      <c r="A15" s="96" t="n"/>
+      <c r="B15" s="96" t="n"/>
+      <c r="C15" s="96" t="n"/>
+      <c r="D15" s="97" t="n"/>
+      <c r="E15" s="96" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="95" t="n"/>
-      <c r="B16" s="95" t="n"/>
-      <c r="C16" s="95" t="n"/>
-      <c r="D16" s="96" t="n"/>
-      <c r="E16" s="95" t="n"/>
+      <c r="A16" s="96" t="n"/>
+      <c r="B16" s="96" t="n"/>
+      <c r="C16" s="96" t="n"/>
+      <c r="D16" s="97" t="n"/>
+      <c r="E16" s="96" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -4071,53 +4131,53 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="95" t="n"/>
-      <c r="B22" s="95" t="n"/>
-      <c r="C22" s="95" t="n"/>
-      <c r="D22" s="96" t="n"/>
-      <c r="E22" s="95" t="n"/>
+      <c r="A22" s="96" t="n"/>
+      <c r="B22" s="96" t="n"/>
+      <c r="C22" s="96" t="n"/>
+      <c r="D22" s="97" t="n"/>
+      <c r="E22" s="96" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="95" t="n"/>
-      <c r="B23" s="95" t="n"/>
-      <c r="C23" s="95" t="n"/>
-      <c r="D23" s="96" t="n"/>
-      <c r="E23" s="95" t="n"/>
+      <c r="A23" s="96" t="n"/>
+      <c r="B23" s="96" t="n"/>
+      <c r="C23" s="96" t="n"/>
+      <c r="D23" s="97" t="n"/>
+      <c r="E23" s="96" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="95" t="n"/>
-      <c r="B24" s="95" t="n"/>
-      <c r="C24" s="95" t="n"/>
-      <c r="D24" s="96" t="n"/>
-      <c r="E24" s="95" t="n"/>
+      <c r="A24" s="96" t="n"/>
+      <c r="B24" s="96" t="n"/>
+      <c r="C24" s="96" t="n"/>
+      <c r="D24" s="97" t="n"/>
+      <c r="E24" s="96" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="95" t="n"/>
-      <c r="B25" s="95" t="n"/>
-      <c r="C25" s="95" t="n"/>
-      <c r="D25" s="96" t="n"/>
-      <c r="E25" s="95" t="n"/>
+      <c r="A25" s="96" t="n"/>
+      <c r="B25" s="96" t="n"/>
+      <c r="C25" s="96" t="n"/>
+      <c r="D25" s="97" t="n"/>
+      <c r="E25" s="96" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="95" t="n"/>
-      <c r="B26" s="95" t="n"/>
-      <c r="C26" s="95" t="n"/>
-      <c r="D26" s="96" t="n"/>
-      <c r="E26" s="95" t="n"/>
+      <c r="A26" s="96" t="n"/>
+      <c r="B26" s="96" t="n"/>
+      <c r="C26" s="96" t="n"/>
+      <c r="D26" s="97" t="n"/>
+      <c r="E26" s="96" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="95" t="n"/>
-      <c r="B27" s="95" t="n"/>
-      <c r="C27" s="95" t="n"/>
-      <c r="D27" s="96" t="n"/>
-      <c r="E27" s="95" t="n"/>
+      <c r="A27" s="96" t="n"/>
+      <c r="B27" s="96" t="n"/>
+      <c r="C27" s="96" t="n"/>
+      <c r="D27" s="97" t="n"/>
+      <c r="E27" s="96" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="95" t="n"/>
-      <c r="B28" s="95" t="n"/>
-      <c r="C28" s="95" t="n"/>
-      <c r="D28" s="96" t="n"/>
-      <c r="E28" s="95" t="n"/>
+      <c r="A28" s="96" t="n"/>
+      <c r="B28" s="96" t="n"/>
+      <c r="C28" s="96" t="n"/>
+      <c r="D28" s="97" t="n"/>
+      <c r="E28" s="96" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -4133,9 +4193,19 @@
       </c>
       <c r="E29" s="8" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="95">
+        <f>IF(SUM(D10:D29)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1"/>
+    <row r="33" ht="26" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A31:E33"/>
     <mergeCell ref="D2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4167,7 +4237,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G1" s="100" t="inlineStr">
+      <c r="G1" s="101" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 1/2</t>
@@ -4219,26 +4289,26 @@
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="101" t="inlineStr">
+      <c r="A6" s="102" t="inlineStr">
         <is>
           <t>Partie 1 : Notes sur le bilan</t>
         </is>
       </c>
-      <c r="B6" s="102" t="n"/>
-      <c r="C6" s="102" t="n"/>
-      <c r="D6" s="102" t="n"/>
-      <c r="E6" s="102" t="n"/>
-      <c r="F6" s="102" t="n"/>
-      <c r="G6" s="102" t="n"/>
-      <c r="H6" s="102" t="n"/>
+      <c r="B6" s="103" t="n"/>
+      <c r="C6" s="103" t="n"/>
+      <c r="D6" s="103" t="n"/>
+      <c r="E6" s="103" t="n"/>
+      <c r="F6" s="103" t="n"/>
+      <c r="G6" s="103" t="n"/>
+      <c r="H6" s="103" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="103" t="inlineStr">
+      <c r="A7" s="104" t="inlineStr">
         <is>
           <t>NOTE 1</t>
         </is>
       </c>
-      <c r="B7" s="104" t="inlineStr">
+      <c r="B7" s="105" t="inlineStr">
         <is>
           <t>Tableau SMT de suivi du matériel, du mobilier et des cautions</t>
         </is>
@@ -4251,7 +4321,7 @@
       <c r="H7" s="49" t="n"/>
     </row>
     <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="105" t="n"/>
+      <c r="A8" s="106" t="n"/>
       <c r="B8" s="49" t="n"/>
       <c r="C8" s="49" t="n"/>
       <c r="D8" s="49" t="n"/>
@@ -4261,12 +4331,12 @@
       <c r="H8" s="49" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="103" t="inlineStr">
+      <c r="A9" s="104" t="inlineStr">
         <is>
           <t>NOTE 2</t>
         </is>
       </c>
-      <c r="B9" s="104" t="inlineStr">
+      <c r="B9" s="105" t="inlineStr">
         <is>
           <t>État des stocks</t>
         </is>
@@ -4279,7 +4349,7 @@
       <c r="H9" s="49" t="n"/>
     </row>
     <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="105" t="n"/>
+      <c r="A10" s="106" t="n"/>
       <c r="B10" s="49" t="n"/>
       <c r="C10" s="49" t="n"/>
       <c r="D10" s="49" t="n"/>
@@ -4289,12 +4359,12 @@
       <c r="H10" s="49" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="103" t="inlineStr">
+      <c r="A11" s="104" t="inlineStr">
         <is>
           <t>NOTE 3</t>
         </is>
       </c>
-      <c r="B11" s="104" t="inlineStr">
+      <c r="B11" s="105" t="inlineStr">
         <is>
           <t>État des créances et des dettes non échues</t>
         </is>
@@ -4307,7 +4377,7 @@
       <c r="H11" s="49" t="n"/>
     </row>
     <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="105" t="n"/>
+      <c r="A12" s="106" t="n"/>
       <c r="B12" s="49" t="n"/>
       <c r="C12" s="49" t="n"/>
       <c r="D12" s="49" t="n"/>
@@ -4317,26 +4387,26 @@
       <c r="H12" s="49" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="101" t="inlineStr">
+      <c r="A13" s="102" t="inlineStr">
         <is>
           <t>Partie 2 : Notes sur le compte de résultat et pièces de tenue</t>
         </is>
       </c>
-      <c r="B13" s="102" t="n"/>
-      <c r="C13" s="102" t="n"/>
-      <c r="D13" s="102" t="n"/>
-      <c r="E13" s="102" t="n"/>
-      <c r="F13" s="102" t="n"/>
-      <c r="G13" s="102" t="n"/>
-      <c r="H13" s="102" t="n"/>
+      <c r="B13" s="103" t="n"/>
+      <c r="C13" s="103" t="n"/>
+      <c r="D13" s="103" t="n"/>
+      <c r="E13" s="103" t="n"/>
+      <c r="F13" s="103" t="n"/>
+      <c r="G13" s="103" t="n"/>
+      <c r="H13" s="103" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="103" t="inlineStr">
+      <c r="A14" s="104" t="inlineStr">
         <is>
           <t>NOTE 4</t>
         </is>
       </c>
-      <c r="B14" s="104" t="inlineStr">
+      <c r="B14" s="105" t="inlineStr">
         <is>
           <t>Journal de trésorerie SMT</t>
         </is>
@@ -4349,7 +4419,7 @@
       <c r="H14" s="49" t="n"/>
     </row>
     <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="105" t="n"/>
+      <c r="A15" s="106" t="n"/>
       <c r="B15" s="49" t="n"/>
       <c r="C15" s="49" t="n"/>
       <c r="D15" s="49" t="n"/>
@@ -4364,7 +4434,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G16" s="100" t="inlineStr">
+      <c r="G16" s="101" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 2/2</t>
@@ -4416,8 +4486,8 @@
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="103" t="inlineStr"/>
-      <c r="B21" s="104" t="inlineStr">
+      <c r="A21" s="104" t="inlineStr"/>
+      <c r="B21" s="105" t="inlineStr">
         <is>
           <t>Journal de suivi des créances impayées</t>
         </is>
@@ -4430,7 +4500,7 @@
       <c r="H21" s="49" t="n"/>
     </row>
     <row r="22" ht="110" customHeight="1">
-      <c r="A22" s="105" t="n"/>
+      <c r="A22" s="106" t="n"/>
       <c r="B22" s="49" t="n"/>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
@@ -4440,8 +4510,8 @@
       <c r="H22" s="49" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="103" t="inlineStr"/>
-      <c r="B23" s="104" t="inlineStr">
+      <c r="A23" s="104" t="inlineStr"/>
+      <c r="B23" s="105" t="inlineStr">
         <is>
           <t>Journal de suivi des dettes à payer</t>
         </is>
@@ -4454,7 +4524,7 @@
       <c r="H23" s="49" t="n"/>
     </row>
     <row r="24" ht="110" customHeight="1">
-      <c r="A24" s="105" t="n"/>
+      <c r="A24" s="106" t="n"/>
       <c r="B24" s="49" t="n"/>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
@@ -4520,92 +4590,92 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="95" t="inlineStr">
+      <c r="A2" s="96" t="inlineStr">
         <is>
           <t>Total solde de clôture débit balance</t>
         </is>
       </c>
-      <c r="B2" s="96">
+      <c r="B2" s="97">
         <f>SUM('BALANCE N'!G2:G18)</f>
         <v/>
       </c>
-      <c r="C2" s="95" t="inlineStr"/>
+      <c r="C2" s="96" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="95" t="inlineStr">
+      <c r="A3" s="96" t="inlineStr">
         <is>
           <t>Total solde de clôture crédit balance</t>
         </is>
       </c>
-      <c r="B3" s="96">
+      <c r="B3" s="97">
         <f>SUM('BALANCE N'!H2:H18)</f>
         <v/>
       </c>
-      <c r="C3" s="95" t="inlineStr"/>
+      <c r="C3" s="96" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="95" t="inlineStr">
+      <c r="A4" s="96" t="inlineStr">
         <is>
           <t>Écart balance (doit être 0)</t>
         </is>
       </c>
-      <c r="B4" s="96">
+      <c r="B4" s="97">
         <f>B2-B3</f>
         <v/>
       </c>
-      <c r="C4" s="95" t="n">
+      <c r="C4" s="96" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="95" t="inlineStr">
+      <c r="A5" s="96" t="inlineStr">
         <is>
           <t>Total actif</t>
         </is>
       </c>
-      <c r="B5" s="96">
+      <c r="B5" s="97">
         <f>'Bilan-Actif'!D14</f>
         <v/>
       </c>
-      <c r="C5" s="95" t="inlineStr"/>
+      <c r="C5" s="96" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="95" t="inlineStr">
+      <c r="A6" s="96" t="inlineStr">
         <is>
           <t>Total passif</t>
         </is>
       </c>
-      <c r="B6" s="96">
+      <c r="B6" s="97">
         <f>'Bilan-Passif'!D13</f>
         <v/>
       </c>
-      <c r="C6" s="95" t="inlineStr"/>
+      <c r="C6" s="96" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="95" t="inlineStr">
+      <c r="A7" s="96" t="inlineStr">
         <is>
           <t>Écart actif - passif (doit être 0)</t>
         </is>
       </c>
-      <c r="B7" s="96">
+      <c r="B7" s="97">
         <f>B5-B6</f>
         <v/>
       </c>
-      <c r="C7" s="95" t="n">
+      <c r="C7" s="96" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="95" t="inlineStr">
+      <c r="A8" s="96" t="inlineStr">
         <is>
           <t>Résultat (compte de résultat, G)</t>
         </is>
       </c>
-      <c r="B8" s="96">
+      <c r="B8" s="97">
         <f>'Résultat'!D24</f>
         <v/>
       </c>
-      <c r="C8" s="95" t="inlineStr"/>
+      <c r="C8" s="96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4656,46 +4726,46 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="95" t="inlineStr">
+      <c r="A2" s="96" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B2" s="95" t="inlineStr"/>
-      <c r="C2" s="95" t="inlineStr">
+      <c r="B2" s="96" t="inlineStr"/>
+      <c r="C2" s="96" t="inlineStr">
         <is>
           <t>Classe 4</t>
         </is>
       </c>
-      <c r="D2" s="95" t="inlineStr">
+      <c r="D2" s="96" t="inlineStr">
         <is>
           <t>La balance porte des comptes de tiers : recettes et dépenses incluent alors des montants non encaissés/décaissés (base engagement).</t>
         </is>
       </c>
-      <c r="E2" s="95" t="inlineStr">
+      <c r="E2" s="96" t="inlineStr">
         <is>
           <t>Dans ce cas, laisser VB et VC à zéro : le résultat est déjà en base engagement. Ne les servir que pour une balance de trésorerie pure, depuis l'inventaire extra-comptable (NOTE 3).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="95" t="inlineStr">
+      <c r="A3" s="96" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B3" s="95" t="inlineStr"/>
-      <c r="C3" s="95" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr"/>
+      <c r="C3" s="96" t="inlineStr">
         <is>
           <t>SMT - seuils</t>
         </is>
       </c>
-      <c r="D3" s="95" t="inlineStr">
+      <c r="D3" s="96" t="inlineStr">
         <is>
           <t>Vérifier l'assujettissement au SMT : CA HT ≤ 60 M FCFA (négoce), 40 M (artisanat), 30 M (services) - AUDCIF art. 13.</t>
         </is>
       </c>
-      <c r="E3" s="95" t="inlineStr">
+      <c r="E3" s="96" t="inlineStr">
         <is>
           <t>Au-delà des seuils, monter la liasse du Système normal (monter_liasse.py).</t>
         </is>
@@ -7259,7 +7329,7 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"49*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"591*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"590*",'BALANCE N'!$H$2:$H$50))+(SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$H$2:$H$50))</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"49*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"590*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"591*",'BALANCE N'!$H$2:$H$50))+(SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$H$2:$H$50))</f>
         <v/>
       </c>
       <c r="E11" s="77" t="n"/>
@@ -7303,7 +7373,7 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$H$2:$H$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"594*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"593*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"592*",'BALANCE N'!$H$2:$H$50))</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$H$2:$H$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"594*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"593*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"592*",'BALANCE N'!$H$2:$H$50))</f>
         <v/>
       </c>
       <c r="E13" s="77" t="n"/>
@@ -7475,7 +7545,7 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E9" s="77" t="n"/>
@@ -7511,7 +7581,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E11" s="77" t="n"/>

--- a/.claude/skills/syscohada/liasse/exemples/exemple-etats-smt.xlsx
+++ b/.claude/skills/syscohada/liasse/exemples/exemple-etats-smt.xlsx
@@ -37,7 +37,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -173,6 +173,12 @@
       <sz val="26"/>
     </font>
     <font>
+      <name val="Arial Black"/>
+      <b val="1"/>
+      <color rgb="00D9D9D9"/>
+      <sz val="48"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <color theme="1"/>
       <sz val="9"/>
@@ -609,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -835,8 +841,11 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="15"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1997,7 +2006,7 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E10" s="77" t="n"/>
@@ -2143,7 +2152,7 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$H$2:$H$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="E17" s="77" t="n"/>
@@ -2261,7 +2270,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr"/>
       <c r="D23" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$H$2:$H$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="E23" s="77" t="n"/>
@@ -2815,14 +2824,14 @@
       </c>
     </row>
     <row r="15"/>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="95">
-        <f>IF(SUM(C9:C12,G9:G12)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1"/>
-    <row r="18" ht="26" customHeight="1"/>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="100">
+        <f>IF(SUM(C9:C12,G9:G12)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1"/>
+    <row r="18" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A16:G18"/>
@@ -3026,14 +3035,14 @@
       </c>
     </row>
     <row r="16"/>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="95">
-        <f>IF(SUM(E9:E15)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1"/>
-    <row r="19" ht="26" customHeight="1"/>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="100">
+        <f>IF(SUM(E9:E15)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A17:E19"/>
@@ -3280,11 +3289,11 @@
           <t>Rappel balance (classe 4, soldes débiteurs) - contrôle</t>
         </is>
       </c>
-      <c r="C17" s="100">
+      <c r="C17" s="101">
         <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
-      <c r="D17" s="100">
+      <c r="D17" s="101">
         <f>0</f>
         <v/>
       </c>
@@ -3441,11 +3450,11 @@
           <t>Rappel balance (classe 4, soldes créditeurs) - contrôle</t>
         </is>
       </c>
-      <c r="C29" s="100">
+      <c r="C29" s="101">
         <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
-      <c r="D29" s="100">
+      <c r="D29" s="101">
         <f>0</f>
         <v/>
       </c>
@@ -3460,14 +3469,14 @@
       </c>
     </row>
     <row r="33"/>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="95">
-        <f>IF(SUM(C10:C29,D10:D29,E10:E28)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="26" customHeight="1"/>
-    <row r="36" ht="26" customHeight="1"/>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="100">
+        <f>IF(SUM(C10:C29,D10:D29,E10:E28)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1"/>
+    <row r="36" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A34:F36"/>
@@ -3894,14 +3903,14 @@
       <c r="K24" s="98" t="n"/>
     </row>
     <row r="25"/>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="95">
-        <f>IF(SUM(C9:C24,D9:D24,E9:E24,F9:F24,G9:G24,H9:H24,I9:I24,J9:J24,K9:K24)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1"/>
-    <row r="28" ht="26" customHeight="1"/>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="100">
+        <f>IF(SUM(C9:C24,D9:D24,E9:E24,F9:F24,G9:G24,H9:H24,I9:I24,J9:J24,K9:K24)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1"/>
+    <row r="28" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B4:H4"/>
@@ -4194,14 +4203,14 @@
       <c r="E29" s="8" t="n"/>
     </row>
     <row r="30"/>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="95">
-        <f>IF(SUM(D10:D29)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="26" customHeight="1"/>
-    <row r="33" ht="26" customHeight="1"/>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="100">
+        <f>IF(SUM(D10:D29)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1"/>
+    <row r="33" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -4237,7 +4246,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G1" s="101" t="inlineStr">
+      <c r="G1" s="102" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 1/2</t>
@@ -4289,26 +4298,26 @@
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="102" t="inlineStr">
+      <c r="A6" s="103" t="inlineStr">
         <is>
           <t>Partie 1 : Notes sur le bilan</t>
         </is>
       </c>
-      <c r="B6" s="103" t="n"/>
-      <c r="C6" s="103" t="n"/>
-      <c r="D6" s="103" t="n"/>
-      <c r="E6" s="103" t="n"/>
-      <c r="F6" s="103" t="n"/>
-      <c r="G6" s="103" t="n"/>
-      <c r="H6" s="103" t="n"/>
+      <c r="B6" s="104" t="n"/>
+      <c r="C6" s="104" t="n"/>
+      <c r="D6" s="104" t="n"/>
+      <c r="E6" s="104" t="n"/>
+      <c r="F6" s="104" t="n"/>
+      <c r="G6" s="104" t="n"/>
+      <c r="H6" s="104" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="104" t="inlineStr">
+      <c r="A7" s="105" t="inlineStr">
         <is>
           <t>NOTE 1</t>
         </is>
       </c>
-      <c r="B7" s="105" t="inlineStr">
+      <c r="B7" s="106" t="inlineStr">
         <is>
           <t>Tableau SMT de suivi du matériel, du mobilier et des cautions</t>
         </is>
@@ -4321,7 +4330,7 @@
       <c r="H7" s="49" t="n"/>
     </row>
     <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="106" t="n"/>
+      <c r="A8" s="107" t="n"/>
       <c r="B8" s="49" t="n"/>
       <c r="C8" s="49" t="n"/>
       <c r="D8" s="49" t="n"/>
@@ -4331,12 +4340,12 @@
       <c r="H8" s="49" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="104" t="inlineStr">
+      <c r="A9" s="105" t="inlineStr">
         <is>
           <t>NOTE 2</t>
         </is>
       </c>
-      <c r="B9" s="105" t="inlineStr">
+      <c r="B9" s="106" t="inlineStr">
         <is>
           <t>État des stocks</t>
         </is>
@@ -4349,7 +4358,7 @@
       <c r="H9" s="49" t="n"/>
     </row>
     <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="106" t="n"/>
+      <c r="A10" s="107" t="n"/>
       <c r="B10" s="49" t="n"/>
       <c r="C10" s="49" t="n"/>
       <c r="D10" s="49" t="n"/>
@@ -4359,12 +4368,12 @@
       <c r="H10" s="49" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="104" t="inlineStr">
+      <c r="A11" s="105" t="inlineStr">
         <is>
           <t>NOTE 3</t>
         </is>
       </c>
-      <c r="B11" s="105" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>État des créances et des dettes non échues</t>
         </is>
@@ -4377,7 +4386,7 @@
       <c r="H11" s="49" t="n"/>
     </row>
     <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="106" t="n"/>
+      <c r="A12" s="107" t="n"/>
       <c r="B12" s="49" t="n"/>
       <c r="C12" s="49" t="n"/>
       <c r="D12" s="49" t="n"/>
@@ -4387,26 +4396,26 @@
       <c r="H12" s="49" t="n"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="102" t="inlineStr">
+      <c r="A13" s="103" t="inlineStr">
         <is>
           <t>Partie 2 : Notes sur le compte de résultat et pièces de tenue</t>
         </is>
       </c>
-      <c r="B13" s="103" t="n"/>
-      <c r="C13" s="103" t="n"/>
-      <c r="D13" s="103" t="n"/>
-      <c r="E13" s="103" t="n"/>
-      <c r="F13" s="103" t="n"/>
-      <c r="G13" s="103" t="n"/>
-      <c r="H13" s="103" t="n"/>
+      <c r="B13" s="104" t="n"/>
+      <c r="C13" s="104" t="n"/>
+      <c r="D13" s="104" t="n"/>
+      <c r="E13" s="104" t="n"/>
+      <c r="F13" s="104" t="n"/>
+      <c r="G13" s="104" t="n"/>
+      <c r="H13" s="104" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="104" t="inlineStr">
+      <c r="A14" s="105" t="inlineStr">
         <is>
           <t>NOTE 4</t>
         </is>
       </c>
-      <c r="B14" s="105" t="inlineStr">
+      <c r="B14" s="106" t="inlineStr">
         <is>
           <t>Journal de trésorerie SMT</t>
         </is>
@@ -4419,7 +4428,7 @@
       <c r="H14" s="49" t="n"/>
     </row>
     <row r="15" ht="110" customHeight="1">
-      <c r="A15" s="106" t="n"/>
+      <c r="A15" s="107" t="n"/>
       <c r="B15" s="49" t="n"/>
       <c r="C15" s="49" t="n"/>
       <c r="D15" s="49" t="n"/>
@@ -4434,7 +4443,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G16" s="101" t="inlineStr">
+      <c r="G16" s="102" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 2/2</t>
@@ -4486,8 +4495,8 @@
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="104" t="inlineStr"/>
-      <c r="B21" s="105" t="inlineStr">
+      <c r="A21" s="105" t="inlineStr"/>
+      <c r="B21" s="106" t="inlineStr">
         <is>
           <t>Journal de suivi des créances impayées</t>
         </is>
@@ -4500,7 +4509,7 @@
       <c r="H21" s="49" t="n"/>
     </row>
     <row r="22" ht="110" customHeight="1">
-      <c r="A22" s="106" t="n"/>
+      <c r="A22" s="107" t="n"/>
       <c r="B22" s="49" t="n"/>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
@@ -4510,8 +4519,8 @@
       <c r="H22" s="49" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="104" t="inlineStr"/>
-      <c r="B23" s="105" t="inlineStr">
+      <c r="A23" s="105" t="inlineStr"/>
+      <c r="B23" s="106" t="inlineStr">
         <is>
           <t>Journal de suivi des dettes à payer</t>
         </is>
@@ -4524,7 +4533,7 @@
       <c r="H23" s="49" t="n"/>
     </row>
     <row r="24" ht="110" customHeight="1">
-      <c r="A24" s="106" t="n"/>
+      <c r="A24" s="107" t="n"/>
       <c r="B24" s="49" t="n"/>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
@@ -5737,7 +5746,7 @@
       <c r="F10" s="61" t="n"/>
       <c r="G10" s="62" t="inlineStr">
         <is>
-          <t>DU : 01-01-2025    AU : 31-12-2025</t>
+          <t>DU :     AU : 31-12-2025</t>
         </is>
       </c>
       <c r="H10" s="61" t="n"/>
@@ -7329,7 +7338,7 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"49*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"590*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"591*",'BALANCE N'!$H$2:$H$50))+(SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$H$2:$H$50))</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"49*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"591*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"590*",'BALANCE N'!$H$2:$H$50))+(SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$H$2:$H$50))</f>
         <v/>
       </c>
       <c r="E11" s="77" t="n"/>
@@ -7373,7 +7382,7 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$H$2:$H$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"594*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"593*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"592*",'BALANCE N'!$H$2:$H$50))</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$H$2:$H$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"594*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"593*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"592*",'BALANCE N'!$H$2:$H$50))</f>
         <v/>
       </c>
       <c r="E13" s="77" t="n"/>
@@ -7545,7 +7554,7 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E9" s="77" t="n"/>
@@ -7581,7 +7590,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E11" s="77" t="n"/>

--- a/.claude/skills/syscohada/liasse/exemples/exemple-etats-smt.xlsx
+++ b/.claude/skills/syscohada/liasse/exemples/exemple-etats-smt.xlsx
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E10" s="77" t="n"/>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$H$2:$H$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="E15" s="77" t="n"/>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$H$2:$H$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="E17" s="77" t="n"/>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr"/>
       <c r="D23" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$H$2:$H$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"68*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"69*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"85*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="E23" s="77" t="n"/>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="C11" s="97">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="D11" s="96" t="n"/>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$H$2:$H$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"594*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"593*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"592*",'BALANCE N'!$H$2:$H$50))</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$H$2:$H$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"592*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"594*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"593*",'BALANCE N'!$H$2:$H$50))</f>
         <v/>
       </c>
       <c r="E13" s="77" t="n"/>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E9" s="77" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E11" s="77" t="n"/>

--- a/.claude/skills/syscohada/liasse/exemples/exemple-etats-smt.xlsx
+++ b/.claude/skills/syscohada/liasse/exemples/exemple-etats-smt.xlsx
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"71*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"72*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"75*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"77*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"78*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"79*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"82*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"84*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"86*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"88*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E10" s="77" t="n"/>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$H$2:$H$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"64*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"89*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="E15" s="77" t="n"/>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$H$2:$H$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"61*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"62*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"63*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"65*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"81*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"83*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"87*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"622*",'BALANCE N'!$H$2:$H$50)</f>
         <v/>
       </c>
       <c r="E17" s="77" t="n"/>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="C11" s="97">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"28*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"29*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="D11" s="96" t="n"/>
@@ -7338,7 +7338,7 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"49*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"591*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"590*",'BALANCE N'!$H$2:$H$50))+(SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$H$2:$H$50))</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"4*",'BALANCE N'!$G$2:$G$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"49*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"590*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"591*",'BALANCE N'!$H$2:$H$50))+(SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"50*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"51*",'BALANCE N'!$H$2:$H$50))</f>
         <v/>
       </c>
       <c r="E11" s="77" t="n"/>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$H$2:$H$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"592*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"594*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"593*",'BALANCE N'!$H$2:$H$50))</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"52*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"53*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"54*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"55*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"56*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$G$2:$G$50)-SUMIF('BALANCE N'!$A$2:$A$50,"58*",'BALANCE N'!$H$2:$H$50)-(SUMIF('BALANCE N'!$A$2:$A$50,"592*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"593*",'BALANCE N'!$H$2:$H$50)+SUMIF('BALANCE N'!$A$2:$A$50,"594*",'BALANCE N'!$H$2:$H$50))</f>
         <v/>
       </c>
       <c r="E13" s="77" t="n"/>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"10*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"11*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"12*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"14*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"15*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E9" s="77" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="5">
-        <f>SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$G$2:$G$50)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"16*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"17*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"18*",'BALANCE N'!$G$2:$G$50)+SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$H$2:$H$50)-SUMIF('BALANCE N'!$A$2:$A$50,"19*",'BALANCE N'!$G$2:$G$50)</f>
         <v/>
       </c>
       <c r="E11" s="77" t="n"/>
